--- a/FondosMutuos/BaseFFMM.xlsx
+++ b/FondosMutuos/BaseFFMM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\FondosMutuos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBED335B-88B5-4F76-887C-767804A4F5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F597DE0-6FCD-4C38-86E8-DB53B038B9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{837DD3E0-4F9E-4033-A113-A4241C8EE115}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{837DD3E0-4F9E-4033-A113-A4241C8EE115}"/>
   </bookViews>
   <sheets>
     <sheet name="Fondos" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -160,6 +160,15 @@
   </si>
   <si>
     <t>Partícipes</t>
+  </si>
+  <si>
+    <t>ETFPESOV</t>
+  </si>
+  <si>
+    <t>EL DORADO</t>
+  </si>
+  <si>
+    <t>ETF</t>
   </si>
 </sst>
 </file>
@@ -532,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F308AD8F-04BE-402F-BA65-8F192711C1BA}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -760,6 +769,23 @@
         <v>38856</v>
       </c>
     </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="1">
+        <v>45747</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -767,7 +793,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E90F8A8D-E010-4622-BBF4-8117B763A2FF}">
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E180"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1596,19 +1622,19 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B50" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C50">
-        <v>167.64956842999999</v>
+        <v>104.077</v>
       </c>
       <c r="D50">
-        <v>3078642149.5</v>
+        <v>160538836</v>
       </c>
       <c r="E50">
-        <v>81044</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1616,16 +1642,16 @@
         <v>45869</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C51">
-        <v>204.37856231999999</v>
+        <v>167.64956842999999</v>
       </c>
       <c r="D51">
-        <v>799486379.04999995</v>
+        <v>3078642149.5</v>
       </c>
       <c r="E51">
-        <v>7016</v>
+        <v>81044</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1633,16 +1659,16 @@
         <v>45869</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C52">
-        <v>129.42988886000001</v>
+        <v>204.37856231999999</v>
       </c>
       <c r="D52">
-        <v>294789962.27999997</v>
+        <v>799486379.04999995</v>
       </c>
       <c r="E52">
-        <v>576</v>
+        <v>7016</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1650,16 +1676,16 @@
         <v>45869</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C53">
-        <v>158.988519</v>
+        <v>129.42988886000001</v>
       </c>
       <c r="D53">
-        <v>1031033582.17</v>
+        <v>294789962.27999997</v>
       </c>
       <c r="E53">
-        <v>11947</v>
+        <v>576</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1667,16 +1693,16 @@
         <v>45869</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C54">
-        <v>345.110997</v>
+        <v>158.988519</v>
       </c>
       <c r="D54">
-        <v>2536105970.04</v>
+        <v>1031033582.17</v>
       </c>
       <c r="E54">
-        <v>35699</v>
+        <v>11947</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1684,16 +1710,16 @@
         <v>45869</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C55">
-        <v>11.63921322</v>
+        <v>345.110997</v>
       </c>
       <c r="D55">
-        <v>1251580814.6700001</v>
+        <v>2536105970.04</v>
       </c>
       <c r="E55">
-        <v>17766</v>
+        <v>35699</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -1701,16 +1727,16 @@
         <v>45869</v>
       </c>
       <c r="B56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C56">
-        <v>195.18316189999999</v>
+        <v>11.63921322</v>
       </c>
       <c r="D56">
-        <v>229817708.03</v>
+        <v>1251580814.6700001</v>
       </c>
       <c r="E56">
-        <v>920</v>
+        <v>17766</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1718,16 +1744,16 @@
         <v>45869</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C57">
-        <v>167.79395239999999</v>
+        <v>195.18316189999999</v>
       </c>
       <c r="D57">
-        <v>1396545851.9300001</v>
+        <v>229817708.03</v>
       </c>
       <c r="E57">
-        <v>2244</v>
+        <v>920</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1735,16 +1761,16 @@
         <v>45869</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C58">
-        <v>390.59586528</v>
+        <v>167.79395239999999</v>
       </c>
       <c r="D58">
-        <v>320206500.63999999</v>
+        <v>1396545851.9300001</v>
       </c>
       <c r="E58">
-        <v>8295</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -1752,16 +1778,16 @@
         <v>45869</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C59">
-        <v>216.53612899999999</v>
+        <v>390.59586528</v>
       </c>
       <c r="D59">
-        <v>646898858.19000006</v>
+        <v>320206500.63999999</v>
       </c>
       <c r="E59">
-        <v>6459</v>
+        <v>8295</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -1769,16 +1795,16 @@
         <v>45869</v>
       </c>
       <c r="B60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C60">
-        <v>225.9716</v>
+        <v>216.53612899999999</v>
       </c>
       <c r="D60">
-        <v>85025969.689999998</v>
+        <v>646898858.19000006</v>
       </c>
       <c r="E60">
-        <v>3704</v>
+        <v>6459</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -1786,50 +1812,50 @@
         <v>45869</v>
       </c>
       <c r="B61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C61">
-        <v>232.6416213</v>
+        <v>225.9716</v>
       </c>
       <c r="D61">
-        <v>112822044.2</v>
+        <v>85025969.689999998</v>
       </c>
       <c r="E61">
-        <v>874</v>
+        <v>3704</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B62" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C62">
-        <v>168.23558263000001</v>
+        <v>232.6416213</v>
       </c>
       <c r="D62">
-        <v>3015298835.8299999</v>
+        <v>112822044.2</v>
       </c>
       <c r="E62">
-        <v>80761</v>
+        <v>874</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B63" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C63">
-        <v>205.39002556</v>
+        <v>104.78189999999999</v>
       </c>
       <c r="D63">
-        <v>897991417.98000002</v>
+        <v>161626065.99000001</v>
       </c>
       <c r="E63">
-        <v>7099</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -1837,16 +1863,16 @@
         <v>45900</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C64">
-        <v>129.88868518000001</v>
+        <v>168.23558263000001</v>
       </c>
       <c r="D64">
-        <v>301790271.91000003</v>
+        <v>3015298835.8299999</v>
       </c>
       <c r="E64">
-        <v>562</v>
+        <v>80761</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -1854,16 +1880,16 @@
         <v>45900</v>
       </c>
       <c r="B65" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C65">
-        <v>159.74084300000001</v>
+        <v>205.39002556</v>
       </c>
       <c r="D65">
-        <v>1076884783.3499999</v>
+        <v>897991417.98000002</v>
       </c>
       <c r="E65">
-        <v>12131</v>
+        <v>7099</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -1871,16 +1897,16 @@
         <v>45900</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C66">
-        <v>346.30228299999999</v>
+        <v>129.88868518000001</v>
       </c>
       <c r="D66">
-        <v>2617465131.8000002</v>
+        <v>301790271.91000003</v>
       </c>
       <c r="E66">
-        <v>35775</v>
+        <v>562</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -1888,16 +1914,16 @@
         <v>45900</v>
       </c>
       <c r="B67" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C67">
-        <v>11.681476330000001</v>
+        <v>159.74084300000001</v>
       </c>
       <c r="D67">
-        <v>1217600708.01</v>
+        <v>1076884783.3499999</v>
       </c>
       <c r="E67">
-        <v>17560</v>
+        <v>12131</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -1905,16 +1931,16 @@
         <v>45900</v>
       </c>
       <c r="B68" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C68">
-        <v>195.87096030000001</v>
+        <v>346.30228299999999</v>
       </c>
       <c r="D68">
-        <v>277996661.42000002</v>
+        <v>2617465131.8000002</v>
       </c>
       <c r="E68">
-        <v>940</v>
+        <v>35775</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -1922,16 +1948,16 @@
         <v>45900</v>
       </c>
       <c r="B69" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C69">
-        <v>168.4135532</v>
+        <v>11.681476330000001</v>
       </c>
       <c r="D69">
-        <v>1473308890.9300001</v>
+        <v>1217600708.01</v>
       </c>
       <c r="E69">
-        <v>2207</v>
+        <v>17560</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -1939,16 +1965,16 @@
         <v>45900</v>
       </c>
       <c r="B70" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C70">
-        <v>393.76626654</v>
+        <v>195.87096030000001</v>
       </c>
       <c r="D70">
-        <v>349904163.51999998</v>
+        <v>277996661.42000002</v>
       </c>
       <c r="E70">
-        <v>8460</v>
+        <v>940</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -1956,16 +1982,16 @@
         <v>45900</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C71">
-        <v>217.83012500000001</v>
+        <v>168.4135532</v>
       </c>
       <c r="D71">
-        <v>676057856.75999999</v>
+        <v>1473308890.9300001</v>
       </c>
       <c r="E71">
-        <v>6674</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -1973,16 +1999,16 @@
         <v>45900</v>
       </c>
       <c r="B72" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C72">
-        <v>227.23140000000001</v>
+        <v>393.76626654</v>
       </c>
       <c r="D72">
-        <v>91608131.040000007</v>
+        <v>349904163.51999998</v>
       </c>
       <c r="E72">
-        <v>3783</v>
+        <v>8460</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -1990,67 +2016,67 @@
         <v>45900</v>
       </c>
       <c r="B73" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C73">
-        <v>234.08105040000001</v>
+        <v>217.83012500000001</v>
       </c>
       <c r="D73">
-        <v>119077037.17</v>
+        <v>676057856.75999999</v>
       </c>
       <c r="E73">
-        <v>887</v>
+        <v>6674</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B74" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C74">
-        <v>168.79042254999999</v>
+        <v>227.23140000000001</v>
       </c>
       <c r="D74">
-        <v>2918602637.7800002</v>
+        <v>91608131.040000007</v>
       </c>
       <c r="E74">
-        <v>80189</v>
+        <v>3783</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B75" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C75">
-        <v>206.33787049</v>
+        <v>234.08105040000001</v>
       </c>
       <c r="D75">
-        <v>916202232.72000003</v>
+        <v>119077037.17</v>
       </c>
       <c r="E75">
-        <v>7193</v>
+        <v>887</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C76">
-        <v>130.33427861000001</v>
+        <v>105.94927979000001</v>
       </c>
       <c r="D76">
-        <v>271823785.62</v>
+        <v>138263810.13</v>
       </c>
       <c r="E76">
-        <v>552</v>
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -2058,16 +2084,16 @@
         <v>45930</v>
       </c>
       <c r="B77" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C77">
-        <v>160.29543200000001</v>
+        <v>168.79042254999999</v>
       </c>
       <c r="D77">
-        <v>1186789207.8</v>
+        <v>2918602637.7800002</v>
       </c>
       <c r="E77">
-        <v>12368</v>
+        <v>80189</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -2075,16 +2101,16 @@
         <v>45930</v>
       </c>
       <c r="B78" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C78">
-        <v>347.43418400000002</v>
+        <v>206.33787049</v>
       </c>
       <c r="D78">
-        <v>2712754224.9499998</v>
+        <v>916202232.72000003</v>
       </c>
       <c r="E78">
-        <v>36031</v>
+        <v>7193</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -2092,16 +2118,16 @@
         <v>45930</v>
       </c>
       <c r="B79" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C79">
-        <v>11.72061527</v>
+        <v>130.33427861000001</v>
       </c>
       <c r="D79">
-        <v>1201267646.29</v>
+        <v>271823785.62</v>
       </c>
       <c r="E79">
-        <v>17223</v>
+        <v>552</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -2109,16 +2135,16 @@
         <v>45930</v>
       </c>
       <c r="B80" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C80">
-        <v>196.5501486</v>
+        <v>160.29543200000001</v>
       </c>
       <c r="D80">
-        <v>330152510.06999999</v>
+        <v>1186789207.8</v>
       </c>
       <c r="E80">
-        <v>942</v>
+        <v>12368</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -2126,16 +2152,16 @@
         <v>45930</v>
       </c>
       <c r="B81" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C81">
-        <v>169.00409590000001</v>
+        <v>347.43418400000002</v>
       </c>
       <c r="D81">
-        <v>1416869051.3599999</v>
+        <v>2712754224.9499998</v>
       </c>
       <c r="E81">
-        <v>2160</v>
+        <v>36031</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -2143,16 +2169,16 @@
         <v>45930</v>
       </c>
       <c r="B82" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C82">
-        <v>397.25437890000001</v>
+        <v>11.72061527</v>
       </c>
       <c r="D82">
-        <v>379870300.24000001</v>
+        <v>1201267646.29</v>
       </c>
       <c r="E82">
-        <v>8738</v>
+        <v>17223</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -2160,16 +2186,16 @@
         <v>45930</v>
       </c>
       <c r="B83" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C83">
-        <v>219.155531</v>
+        <v>196.5501486</v>
       </c>
       <c r="D83">
-        <v>712552235.21000004</v>
+        <v>330152510.06999999</v>
       </c>
       <c r="E83">
-        <v>6856</v>
+        <v>942</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -2177,16 +2203,16 @@
         <v>45930</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C84">
-        <v>228.79310000000001</v>
+        <v>169.00409590000001</v>
       </c>
       <c r="D84">
-        <v>97265531.599999994</v>
+        <v>1416869051.3599999</v>
       </c>
       <c r="E84">
-        <v>3924</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2194,84 +2220,84 @@
         <v>45930</v>
       </c>
       <c r="B85" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C85">
-        <v>235.7956131</v>
+        <v>397.25437890000001</v>
       </c>
       <c r="D85">
-        <v>124571303.27</v>
+        <v>379870300.24000001</v>
       </c>
       <c r="E85">
-        <v>897</v>
+        <v>8738</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B86" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C86">
-        <v>169.34801067999999</v>
+        <v>219.155531</v>
       </c>
       <c r="D86">
-        <v>2881515647.71</v>
+        <v>712552235.21000004</v>
       </c>
       <c r="E86">
-        <v>79413</v>
+        <v>6856</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B87" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C87">
-        <v>206.89603886</v>
+        <v>228.79310000000001</v>
       </c>
       <c r="D87">
-        <v>972485492.37</v>
+        <v>97265531.599999994</v>
       </c>
       <c r="E87">
-        <v>7201</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C88">
-        <v>130.78976039</v>
+        <v>235.7956131</v>
       </c>
       <c r="D88">
-        <v>256081799.15000001</v>
+        <v>124571303.27</v>
       </c>
       <c r="E88">
-        <v>539</v>
+        <v>897</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B89" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C89">
-        <v>160.68935400000001</v>
+        <v>107.84736325999999</v>
       </c>
       <c r="D89">
-        <v>1188379776.6099999</v>
+        <v>163658374</v>
       </c>
       <c r="E89">
-        <v>12553</v>
+        <v>225</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -2279,16 +2305,16 @@
         <v>45961</v>
       </c>
       <c r="B90" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C90">
-        <v>348.520308</v>
+        <v>169.34801067999999</v>
       </c>
       <c r="D90">
-        <v>2661416365.75</v>
+        <v>2881515647.71</v>
       </c>
       <c r="E90">
-        <v>36809</v>
+        <v>79413</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -2296,16 +2322,16 @@
         <v>45961</v>
       </c>
       <c r="B91" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C91">
-        <v>11.75824705</v>
+        <v>206.89603886</v>
       </c>
       <c r="D91">
-        <v>1156942034.77</v>
+        <v>972485492.37</v>
       </c>
       <c r="E91">
-        <v>16847</v>
+        <v>7201</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -2313,16 +2339,16 @@
         <v>45961</v>
       </c>
       <c r="B92" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C92">
-        <v>197.17737410000001</v>
+        <v>130.78976039</v>
       </c>
       <c r="D92">
-        <v>309110107.35000002</v>
+        <v>256081799.15000001</v>
       </c>
       <c r="E92">
-        <v>928</v>
+        <v>539</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -2330,16 +2356,16 @@
         <v>45961</v>
       </c>
       <c r="B93" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C93">
-        <v>169.5712072</v>
+        <v>160.68935400000001</v>
       </c>
       <c r="D93">
-        <v>1504501508</v>
+        <v>1188379776.6099999</v>
       </c>
       <c r="E93">
-        <v>2132</v>
+        <v>12553</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -2347,16 +2373,16 @@
         <v>45961</v>
       </c>
       <c r="B94" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C94">
-        <v>398.47251691000002</v>
+        <v>348.520308</v>
       </c>
       <c r="D94">
-        <v>396705750.75</v>
+        <v>2661416365.75</v>
       </c>
       <c r="E94">
-        <v>8860</v>
+        <v>36809</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -2364,16 +2390,16 @@
         <v>45961</v>
       </c>
       <c r="B95" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C95">
-        <v>219.630042</v>
+        <v>11.75824705</v>
       </c>
       <c r="D95">
-        <v>734812669.24000001</v>
+        <v>1156942034.77</v>
       </c>
       <c r="E95">
-        <v>6997</v>
+        <v>16847</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -2381,16 +2407,16 @@
         <v>45961</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C96">
-        <v>229.2867</v>
+        <v>197.17737410000001</v>
       </c>
       <c r="D96">
-        <v>103939528.25</v>
+        <v>309110107.35000002</v>
       </c>
       <c r="E96">
-        <v>3972</v>
+        <v>928</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -2398,101 +2424,101 @@
         <v>45961</v>
       </c>
       <c r="B97" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C97">
-        <v>236.33786749999999</v>
+        <v>169.5712072</v>
       </c>
       <c r="D97">
-        <v>125768006.2</v>
+        <v>1504501508</v>
       </c>
       <c r="E97">
-        <v>892</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B98" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C98">
-        <v>169.89725994</v>
+        <v>398.47251691000002</v>
       </c>
       <c r="D98">
-        <v>2774755450.3899999</v>
+        <v>396705750.75</v>
       </c>
       <c r="E98">
-        <v>78693</v>
+        <v>8860</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B99" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C99">
-        <v>207.59373528</v>
+        <v>219.630042</v>
       </c>
       <c r="D99">
-        <v>927872648.64999998</v>
+        <v>734812669.24000001</v>
       </c>
       <c r="E99">
-        <v>7160</v>
+        <v>6997</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B100" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C100">
-        <v>131.23363684</v>
+        <v>229.2867</v>
       </c>
       <c r="D100">
-        <v>251796267.63</v>
+        <v>103939528.25</v>
       </c>
       <c r="E100">
-        <v>535</v>
+        <v>3972</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B101" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C101">
-        <v>161.28463400000001</v>
+        <v>236.33786749999999</v>
       </c>
       <c r="D101">
-        <v>1187961385.03</v>
+        <v>125768006.2</v>
       </c>
       <c r="E101">
-        <v>12776</v>
+        <v>892</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B102" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C102">
-        <v>349.62951199999998</v>
+        <v>108.20357921</v>
       </c>
       <c r="D102">
-        <v>2707411558.3099999</v>
+        <v>164469440</v>
       </c>
       <c r="E102">
-        <v>37790</v>
+        <v>240</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -2500,16 +2526,16 @@
         <v>45991</v>
       </c>
       <c r="B103" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C103">
-        <v>11.79905789</v>
+        <v>169.89725994</v>
       </c>
       <c r="D103">
-        <v>1148623015.5899999</v>
+        <v>2774755450.3899999</v>
       </c>
       <c r="E103">
-        <v>16641</v>
+        <v>78693</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -2517,16 +2543,16 @@
         <v>45991</v>
       </c>
       <c r="B104" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C104">
-        <v>197.84052919999999</v>
+        <v>207.59373528</v>
       </c>
       <c r="D104">
-        <v>270640934.47000003</v>
+        <v>927872648.64999998</v>
       </c>
       <c r="E104">
-        <v>916</v>
+        <v>7160</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -2534,16 +2560,16 @@
         <v>45991</v>
       </c>
       <c r="B105" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C105">
-        <v>170.1964116</v>
+        <v>131.23363684</v>
       </c>
       <c r="D105">
-        <v>1402076867.8699999</v>
+        <v>251796267.63</v>
       </c>
       <c r="E105">
-        <v>2103</v>
+        <v>535</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -2551,16 +2577,16 @@
         <v>45991</v>
       </c>
       <c r="B106" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C106">
-        <v>400.43885283999998</v>
+        <v>161.28463400000001</v>
       </c>
       <c r="D106">
-        <v>413932498.5</v>
+        <v>1187961385.03</v>
       </c>
       <c r="E106">
-        <v>8911</v>
+        <v>12776</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -2568,16 +2594,16 @@
         <v>45991</v>
       </c>
       <c r="B107" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C107">
-        <v>220.76745099999999</v>
+        <v>349.62951199999998</v>
       </c>
       <c r="D107">
-        <v>761136369.88999999</v>
+        <v>2707411558.3099999</v>
       </c>
       <c r="E107">
-        <v>7209</v>
+        <v>37790</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
@@ -2585,16 +2611,16 @@
         <v>45991</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C108">
-        <v>230.49469999999999</v>
+        <v>11.79905789</v>
       </c>
       <c r="D108">
-        <v>109662203.91</v>
+        <v>1148623015.5899999</v>
       </c>
       <c r="E108">
-        <v>4140</v>
+        <v>16641</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -2602,118 +2628,118 @@
         <v>45991</v>
       </c>
       <c r="B109" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C109">
-        <v>237.84235090000001</v>
+        <v>197.84052919999999</v>
       </c>
       <c r="D109">
-        <v>127028257.98999999</v>
+        <v>270640934.47000003</v>
       </c>
       <c r="E109">
-        <v>905</v>
+        <v>916</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B110" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C110">
-        <v>170.46159245999999</v>
+        <v>170.1964116</v>
       </c>
       <c r="D110">
-        <v>2757505401.1999998</v>
+        <v>1402076867.8699999</v>
       </c>
       <c r="E110">
-        <v>78091</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B111" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C111">
-        <v>208.31806234999999</v>
+        <v>400.43885283999998</v>
       </c>
       <c r="D111">
-        <v>918868055.85000002</v>
+        <v>413932498.5</v>
       </c>
       <c r="E111">
-        <v>7149</v>
+        <v>8911</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C112">
-        <v>131.6919245</v>
+        <v>220.76745099999999</v>
       </c>
       <c r="D112">
-        <v>256864855.19</v>
+        <v>761136369.88999999</v>
       </c>
       <c r="E112">
-        <v>519</v>
+        <v>7209</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B113" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C113">
-        <v>161.838584</v>
+        <v>230.49469999999999</v>
       </c>
       <c r="D113">
-        <v>1215687489.1700001</v>
+        <v>109662203.91</v>
       </c>
       <c r="E113">
-        <v>12994</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B114" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C114">
-        <v>350.75661400000001</v>
+        <v>237.84235090000001</v>
       </c>
       <c r="D114">
-        <v>2704117777.5900002</v>
+        <v>127028257.98999999</v>
       </c>
       <c r="E114">
-        <v>38857</v>
+        <v>905</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B115" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C115">
-        <v>11.838826660000001</v>
+        <v>109.71508005</v>
       </c>
       <c r="D115">
-        <v>1133807674.1700001</v>
+        <v>167041209</v>
       </c>
       <c r="E115">
-        <v>16495</v>
+        <v>294</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -2721,16 +2747,16 @@
         <v>46022</v>
       </c>
       <c r="B116" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C116">
-        <v>198.572138</v>
+        <v>170.46159245999999</v>
       </c>
       <c r="D116">
-        <v>284653202.20999998</v>
+        <v>2757505401.1999998</v>
       </c>
       <c r="E116">
-        <v>908</v>
+        <v>78091</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -2738,16 +2764,16 @@
         <v>46022</v>
       </c>
       <c r="B117" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C117">
-        <v>170.7741771</v>
+        <v>208.31806234999999</v>
       </c>
       <c r="D117">
-        <v>1440431627.4200001</v>
+        <v>918868055.85000002</v>
       </c>
       <c r="E117">
-        <v>2065</v>
+        <v>7149</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -2755,16 +2781,16 @@
         <v>46022</v>
       </c>
       <c r="B118" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C118">
-        <v>402.45125322000001</v>
+        <v>131.6919245</v>
       </c>
       <c r="D118">
-        <v>435072515.97000003</v>
+        <v>256864855.19</v>
       </c>
       <c r="E118">
-        <v>8934</v>
+        <v>519</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -2772,16 +2798,16 @@
         <v>46022</v>
       </c>
       <c r="B119" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C119">
-        <v>221.85736299999999</v>
+        <v>161.838584</v>
       </c>
       <c r="D119">
-        <v>798725071.94000006</v>
+        <v>1215687489.1700001</v>
       </c>
       <c r="E119">
-        <v>7502</v>
+        <v>12994</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -2789,16 +2815,16 @@
         <v>46022</v>
       </c>
       <c r="B120" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C120">
-        <v>231.2962</v>
+        <v>350.75661400000001</v>
       </c>
       <c r="D120">
-        <v>113809087.08</v>
+        <v>2704117777.5900002</v>
       </c>
       <c r="E120">
-        <v>4383</v>
+        <v>38857</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -2806,135 +2832,135 @@
         <v>46022</v>
       </c>
       <c r="B121" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C121">
-        <v>239.07441919999999</v>
+        <v>11.838826660000001</v>
       </c>
       <c r="D121">
-        <v>130310931.52</v>
+        <v>1133807674.1700001</v>
       </c>
       <c r="E121">
-        <v>915</v>
+        <v>16495</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
-        <v>46203</v>
+        <v>46022</v>
       </c>
       <c r="B122" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C122">
-        <v>173.72934685999999</v>
+        <v>198.572138</v>
       </c>
       <c r="D122">
-        <v>2755029376.04</v>
+        <v>284653202.20999998</v>
       </c>
       <c r="E122">
-        <v>76508</v>
+        <v>908</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
-        <v>46203</v>
+        <v>46022</v>
       </c>
       <c r="B123" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C123">
-        <v>212.78308894</v>
+        <v>170.7741771</v>
       </c>
       <c r="D123">
-        <v>913729885.00999999</v>
+        <v>1440431627.4200001</v>
       </c>
       <c r="E123">
-        <v>7226</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
-        <v>46203</v>
+        <v>46022</v>
       </c>
       <c r="B124" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C124">
-        <v>134.35108005000001</v>
+        <v>402.45125322000001</v>
       </c>
       <c r="D124">
-        <v>294070137.10000002</v>
+        <v>435072515.97000003</v>
       </c>
       <c r="E124">
-        <v>559</v>
+        <v>8934</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
-        <v>46203</v>
+        <v>46022</v>
       </c>
       <c r="B125" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C125">
-        <v>165.161753</v>
+        <v>221.85736299999999</v>
       </c>
       <c r="D125">
-        <v>1273986251.6199999</v>
+        <v>798725071.94000006</v>
       </c>
       <c r="E125">
-        <v>13634</v>
+        <v>7502</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
-        <v>46203</v>
+        <v>46022</v>
       </c>
       <c r="B126" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C126">
-        <v>357.63221700000003</v>
+        <v>231.2962</v>
       </c>
       <c r="D126">
-        <v>3155428348.3099999</v>
+        <v>113809087.08</v>
       </c>
       <c r="E126">
-        <v>44078</v>
+        <v>4383</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
-        <v>46203</v>
+        <v>46022</v>
       </c>
       <c r="B127" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C127">
-        <v>12.079791739999999</v>
+        <v>239.07441919999999</v>
       </c>
       <c r="D127">
-        <v>1239412685.3499999</v>
+        <v>130310931.52</v>
       </c>
       <c r="E127">
-        <v>16616</v>
+        <v>915</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
-        <v>46203</v>
+        <v>46022</v>
       </c>
       <c r="B128" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C128">
-        <v>202.4793817</v>
+        <v>110.61604921999999</v>
       </c>
       <c r="D128">
-        <v>268981492.00999999</v>
+        <v>167859855</v>
       </c>
       <c r="E128">
-        <v>909</v>
+        <v>328</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
@@ -2942,16 +2968,16 @@
         <v>46203</v>
       </c>
       <c r="B129" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C129">
-        <v>174.30474280000001</v>
+        <v>173.72934685999999</v>
       </c>
       <c r="D129">
-        <v>1415523875.99</v>
+        <v>2755029376.04</v>
       </c>
       <c r="E129">
-        <v>2017</v>
+        <v>76508</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
@@ -2959,16 +2985,16 @@
         <v>46203</v>
       </c>
       <c r="B130" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C130">
-        <v>410.65932354</v>
+        <v>212.78308894</v>
       </c>
       <c r="D130">
-        <v>461143127.45999998</v>
+        <v>913729885.00999999</v>
       </c>
       <c r="E130">
-        <v>8438</v>
+        <v>7226</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
@@ -2976,16 +3002,16 @@
         <v>46203</v>
       </c>
       <c r="B131" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C131">
-        <v>227.20659000000001</v>
+        <v>134.35108005000001</v>
       </c>
       <c r="D131">
-        <v>841428969.15999997</v>
+        <v>294070137.10000002</v>
       </c>
       <c r="E131">
-        <v>8102</v>
+        <v>559</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
@@ -2993,16 +3019,16 @@
         <v>46203</v>
       </c>
       <c r="B132" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C132">
-        <v>235.39359999999999</v>
+        <v>165.161753</v>
       </c>
       <c r="D132">
-        <v>104979969.55</v>
+        <v>1273986251.6199999</v>
       </c>
       <c r="E132">
-        <v>4508</v>
+        <v>13634</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -3010,152 +3036,152 @@
         <v>46203</v>
       </c>
       <c r="B133" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C133">
-        <v>243.78792050000001</v>
+        <v>357.63221700000003</v>
       </c>
       <c r="D133">
-        <v>127233613.86</v>
+        <v>3155428348.3099999</v>
       </c>
       <c r="E133">
-        <v>888</v>
+        <v>44078</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B134" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C134">
-        <v>174.31846501999999</v>
+        <v>12.079791739999999</v>
       </c>
       <c r="D134">
-        <v>2714460737.9899998</v>
+        <v>1239412685.3499999</v>
       </c>
       <c r="E134">
-        <v>76158</v>
+        <v>16616</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B135" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C135">
-        <v>213.58180999000001</v>
+        <v>202.4793817</v>
       </c>
       <c r="D135">
-        <v>927883838.01999998</v>
+        <v>268981492.00999999</v>
       </c>
       <c r="E135">
-        <v>7251</v>
+        <v>909</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B136" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C136">
-        <v>134.82905649</v>
+        <v>174.30474280000001</v>
       </c>
       <c r="D136">
-        <v>309635566.69</v>
+        <v>1415523875.99</v>
       </c>
       <c r="E136">
-        <v>564</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B137" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C137">
-        <v>165.67208099999999</v>
+        <v>410.65932354</v>
       </c>
       <c r="D137">
-        <v>1300155400.52</v>
+        <v>461143127.45999998</v>
       </c>
       <c r="E137">
-        <v>13863</v>
+        <v>8438</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B138" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C138">
-        <v>358.82808499999999</v>
+        <v>227.20659000000001</v>
       </c>
       <c r="D138">
-        <v>3281456302.8499999</v>
+        <v>841428969.15999997</v>
       </c>
       <c r="E138">
-        <v>44950</v>
+        <v>8102</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B139" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C139">
-        <v>12.122606530000001</v>
+        <v>235.39359999999999</v>
       </c>
       <c r="D139">
-        <v>1234798460.1099999</v>
+        <v>104979969.55</v>
       </c>
       <c r="E139">
-        <v>16736</v>
+        <v>4508</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B140" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C140">
-        <v>203.14380349999999</v>
+        <v>243.78792050000001</v>
       </c>
       <c r="D140">
-        <v>194957198.62</v>
+        <v>127233613.86</v>
       </c>
       <c r="E140">
-        <v>909</v>
+        <v>888</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="B141" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C141">
-        <v>174.92875620000001</v>
+        <v>112.56613378999999</v>
       </c>
       <c r="D141">
-        <v>1240583547.5899999</v>
+        <v>202337625.49000001</v>
       </c>
       <c r="E141">
-        <v>1987</v>
+        <v>449</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
@@ -3163,16 +3189,16 @@
         <v>46234</v>
       </c>
       <c r="B142" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C142">
-        <v>411.87582773999998</v>
+        <v>174.31846501999999</v>
       </c>
       <c r="D142">
-        <v>472879276.06</v>
+        <v>2714460737.9899998</v>
       </c>
       <c r="E142">
-        <v>8522</v>
+        <v>76158</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
@@ -3180,16 +3206,16 @@
         <v>46234</v>
       </c>
       <c r="B143" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C143">
-        <v>228.37178800000001</v>
+        <v>213.58180999000001</v>
       </c>
       <c r="D143">
-        <v>859777580.77999997</v>
+        <v>927883838.01999998</v>
       </c>
       <c r="E143">
-        <v>8250</v>
+        <v>7251</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -3197,16 +3223,16 @@
         <v>46234</v>
       </c>
       <c r="B144" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C144">
-        <v>235.62559999999999</v>
+        <v>134.82905649</v>
       </c>
       <c r="D144">
-        <v>105017921.93000001</v>
+        <v>309635566.69</v>
       </c>
       <c r="E144">
-        <v>4553</v>
+        <v>564</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
@@ -3214,169 +3240,169 @@
         <v>46234</v>
       </c>
       <c r="B145" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C145">
-        <v>244.45138560000001</v>
+        <v>165.67208099999999</v>
       </c>
       <c r="D145">
-        <v>129245461.34999999</v>
+        <v>1300155400.52</v>
       </c>
       <c r="E145">
-        <v>882</v>
+        <v>13863</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B146" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C146">
-        <v>174.92760867999999</v>
+        <v>358.82808499999999</v>
       </c>
       <c r="D146">
-        <v>2696336296.1199999</v>
+        <v>3281456302.8499999</v>
       </c>
       <c r="E146">
-        <v>75749</v>
+        <v>44950</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B147" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C147">
-        <v>214.56994126000001</v>
+        <v>12.122606530000001</v>
       </c>
       <c r="D147">
-        <v>926049973</v>
+        <v>1234798460.1099999</v>
       </c>
       <c r="E147">
-        <v>7226</v>
+        <v>16736</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B148" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C148">
-        <v>135.32540791</v>
+        <v>203.14380349999999</v>
       </c>
       <c r="D148">
-        <v>326176641.60000002</v>
+        <v>194957198.62</v>
       </c>
       <c r="E148">
-        <v>566</v>
+        <v>909</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B149" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C149">
-        <v>166.32631599999999</v>
+        <v>174.92875620000001</v>
       </c>
       <c r="D149">
-        <v>1330545100.6300001</v>
+        <v>1240583547.5899999</v>
       </c>
       <c r="E149">
-        <v>13990</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B150" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C150">
-        <v>360.02621199999999</v>
+        <v>411.87582773999998</v>
       </c>
       <c r="D150">
-        <v>3386119097.6900001</v>
+        <v>472879276.06</v>
       </c>
       <c r="E150">
-        <v>45517</v>
+        <v>8522</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B151" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C151">
-        <v>12.165339700000001</v>
+        <v>228.37178800000001</v>
       </c>
       <c r="D151">
-        <v>1247745597.73</v>
+        <v>859777580.77999997</v>
       </c>
       <c r="E151">
-        <v>16809</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B152" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C152">
-        <v>203.8672832</v>
+        <v>235.62559999999999</v>
       </c>
       <c r="D152">
-        <v>184350138.22</v>
+        <v>105017921.93000001</v>
       </c>
       <c r="E152">
-        <v>890</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B153" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C153">
-        <v>175.55553359999999</v>
+        <v>244.45138560000001</v>
       </c>
       <c r="D153">
-        <v>1372214285.01</v>
+        <v>129245461.34999999</v>
       </c>
       <c r="E153">
-        <v>1957</v>
+        <v>882</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="B154" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C154">
-        <v>413.52704188000001</v>
+        <v>113.10807698000001</v>
       </c>
       <c r="D154">
-        <v>476906604.38999999</v>
+        <v>152695903.91999999</v>
       </c>
       <c r="E154">
-        <v>8499</v>
+        <v>449</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
@@ -3384,16 +3410,16 @@
         <v>46265</v>
       </c>
       <c r="B155" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C155">
-        <v>228.46783600000001</v>
+        <v>174.92760867999999</v>
       </c>
       <c r="D155">
-        <v>846675540.86000001</v>
+        <v>2696336296.1199999</v>
       </c>
       <c r="E155">
-        <v>8334</v>
+        <v>75749</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
@@ -3401,16 +3427,16 @@
         <v>46265</v>
       </c>
       <c r="B156" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C156">
-        <v>235.76259999999999</v>
+        <v>214.56994126000001</v>
       </c>
       <c r="D156">
-        <v>99791086.439999998</v>
+        <v>926049973</v>
       </c>
       <c r="E156">
-        <v>4511</v>
+        <v>7226</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
@@ -3418,186 +3444,186 @@
         <v>46265</v>
       </c>
       <c r="B157" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C157">
-        <v>244.73786240000001</v>
+        <v>135.32540791</v>
       </c>
       <c r="D157">
-        <v>128349607.03</v>
+        <v>326176641.60000002</v>
       </c>
       <c r="E157">
-        <v>859</v>
+        <v>566</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B158" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C158">
-        <v>175.50838275999999</v>
+        <v>166.32631599999999</v>
       </c>
       <c r="D158">
-        <v>2705529159.8099999</v>
+        <v>1330545100.6300001</v>
       </c>
       <c r="E158">
-        <v>75292</v>
+        <v>13990</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B159" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C159">
-        <v>214.47442111000001</v>
+        <v>360.02621199999999</v>
       </c>
       <c r="D159">
-        <v>917635044.80999994</v>
+        <v>3386119097.6900001</v>
       </c>
       <c r="E159">
-        <v>7147</v>
+        <v>45517</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B160" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C160">
-        <v>135.79414928</v>
+        <v>12.165339700000001</v>
       </c>
       <c r="D160">
-        <v>359423998.38</v>
+        <v>1247745597.73</v>
       </c>
       <c r="E160">
-        <v>597</v>
+        <v>16809</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B161" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C161">
-        <v>166.12638113</v>
+        <v>203.8672832</v>
       </c>
       <c r="D161">
-        <v>1320047031.1900001</v>
+        <v>184350138.22</v>
       </c>
       <c r="E161">
-        <v>13880</v>
+        <v>890</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B162" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C162">
-        <v>361.10296736999999</v>
+        <v>175.55553359999999</v>
       </c>
       <c r="D162">
-        <v>3358169486.3899999</v>
+        <v>1372214285.01</v>
       </c>
       <c r="E162">
-        <v>45627</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B163" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C163">
-        <v>12.203462500000001</v>
+        <v>413.52704188000001</v>
       </c>
       <c r="D163">
-        <v>1253304551.1400001</v>
+        <v>476906604.38999999</v>
       </c>
       <c r="E163">
-        <v>16925</v>
+        <v>8499</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B164" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C164">
-        <v>203.7424178</v>
+        <v>228.46783600000001</v>
       </c>
       <c r="D164">
-        <v>186504024.28999999</v>
+        <v>846675540.86000001</v>
       </c>
       <c r="E164">
-        <v>881</v>
+        <v>8334</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B165" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C165">
-        <v>176.1565659</v>
+        <v>235.76259999999999</v>
       </c>
       <c r="D165">
-        <v>1543437489.8199999</v>
+        <v>99791086.439999998</v>
       </c>
       <c r="E165">
-        <v>1953</v>
+        <v>4511</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B166" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C166">
-        <v>409.07142088000001</v>
+        <v>244.73786240000001</v>
       </c>
       <c r="D166">
-        <v>445717202.87</v>
+        <v>128349607.03</v>
       </c>
       <c r="E166">
-        <v>8243</v>
+        <v>859</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="B167" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C167">
-        <v>226.09731866999999</v>
+        <v>112.50574435</v>
       </c>
       <c r="D167">
-        <v>783883688.35000002</v>
+        <v>152164019.24000001</v>
       </c>
       <c r="E167">
-        <v>8119</v>
+        <v>518</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
@@ -3605,16 +3631,16 @@
         <v>46295</v>
       </c>
       <c r="B168" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C168">
-        <v>233.64169999999999</v>
+        <v>175.50838275999999</v>
       </c>
       <c r="D168">
-        <v>91765003.560000002</v>
+        <v>2705529159.8099999</v>
       </c>
       <c r="E168">
-        <v>4360</v>
+        <v>75292</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
@@ -3622,16 +3648,203 @@
         <v>46295</v>
       </c>
       <c r="B169" t="s">
+        <v>23</v>
+      </c>
+      <c r="C169">
+        <v>214.47442111000001</v>
+      </c>
+      <c r="D169">
+        <v>917635044.80999994</v>
+      </c>
+      <c r="E169">
+        <v>7147</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B170" t="s">
+        <v>24</v>
+      </c>
+      <c r="C170">
+        <v>135.79414928</v>
+      </c>
+      <c r="D170">
+        <v>359423998.38</v>
+      </c>
+      <c r="E170">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B171" t="s">
+        <v>25</v>
+      </c>
+      <c r="C171">
+        <v>166.12638113</v>
+      </c>
+      <c r="D171">
+        <v>1320047031.1900001</v>
+      </c>
+      <c r="E171">
+        <v>13880</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B172" t="s">
+        <v>26</v>
+      </c>
+      <c r="C172">
+        <v>361.10296736999999</v>
+      </c>
+      <c r="D172">
+        <v>3358169486.3899999</v>
+      </c>
+      <c r="E172">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B173" t="s">
+        <v>27</v>
+      </c>
+      <c r="C173">
+        <v>12.203462500000001</v>
+      </c>
+      <c r="D173">
+        <v>1253304551.1400001</v>
+      </c>
+      <c r="E173">
+        <v>16925</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B174" t="s">
+        <v>28</v>
+      </c>
+      <c r="C174">
+        <v>203.7424178</v>
+      </c>
+      <c r="D174">
+        <v>186504024.28999999</v>
+      </c>
+      <c r="E174">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B175" t="s">
+        <v>29</v>
+      </c>
+      <c r="C175">
+        <v>176.1565659</v>
+      </c>
+      <c r="D175">
+        <v>1543437489.8199999</v>
+      </c>
+      <c r="E175">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B176" t="s">
+        <v>32</v>
+      </c>
+      <c r="C176">
+        <v>409.07142088000001</v>
+      </c>
+      <c r="D176">
+        <v>445717202.87</v>
+      </c>
+      <c r="E176">
+        <v>8243</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B177" t="s">
+        <v>33</v>
+      </c>
+      <c r="C177">
+        <v>226.09731866999999</v>
+      </c>
+      <c r="D177">
+        <v>783883688.35000002</v>
+      </c>
+      <c r="E177">
+        <v>8119</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B178" t="s">
+        <v>34</v>
+      </c>
+      <c r="C178">
+        <v>233.64169999999999</v>
+      </c>
+      <c r="D178">
+        <v>91765003.560000002</v>
+      </c>
+      <c r="E178">
+        <v>4360</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B179" t="s">
         <v>35</v>
       </c>
-      <c r="C169">
+      <c r="C179">
         <v>242.900756</v>
       </c>
-      <c r="D169">
+      <c r="D179">
         <v>120721586.34</v>
       </c>
-      <c r="E169">
+      <c r="E179">
         <v>838</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B180" t="s">
+        <v>40</v>
+      </c>
+      <c r="C180">
+        <v>110.04027514086383</v>
+      </c>
+      <c r="D180">
+        <v>148829472.12801832</v>
+      </c>
+      <c r="E180">
+        <v>547</v>
       </c>
     </row>
   </sheetData>

--- a/FondosMutuos/BaseFFMM.xlsx
+++ b/FondosMutuos/BaseFFMM.xlsx
@@ -2,23 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\FondosMutuos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4C45F9-F376-4A46-B365-AA1C94AF390A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE771B8-2A24-44EF-8CFB-69D8E3D877FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{837DD3E0-4F9E-4033-A113-A4241C8EE115}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{837DD3E0-4F9E-4033-A113-A4241C8EE115}"/>
   </bookViews>
   <sheets>
     <sheet name="Fondos" sheetId="1" r:id="rId1"/>
-    <sheet name="Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Hoja1" sheetId="3" r:id="rId3"/>
-    <sheet name="Hoja2" sheetId="4" r:id="rId4"/>
+    <sheet name="Hoja3" sheetId="5" r:id="rId2"/>
+    <sheet name="Data" sheetId="2" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="3" r:id="rId4"/>
+    <sheet name="Hoja2" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="9" r:id="rId6"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="406">
   <si>
     <t>ID</t>
   </si>
@@ -1239,13 +1243,44 @@
   </si>
   <si>
     <t>Base SMV</t>
+  </si>
+  <si>
+    <t>Etiquetas de fila</t>
+  </si>
+  <si>
+    <t>Total general</t>
+  </si>
+  <si>
+    <t>Suma de Valor Cuota</t>
+  </si>
+  <si>
+    <t>Suma de Patrimonio</t>
+  </si>
+  <si>
+    <t>Muy Corto Plazo</t>
+  </si>
+  <si>
+    <t>Corto Plazo</t>
+  </si>
+  <si>
+    <t>MCP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0000000000000000%"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1356,50 +1391,62 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1412,6 +1459,1765 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="LENOVO" refreshedDate="46311.469485069443" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="205" xr:uid="{52DEB751-7A25-4BD3-836B-51C73697F048}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E206" sheet="Data"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="Fecha" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2022-12-31T00:00:00" maxDate="2026-10-10T00:00:00" count="16">
+        <d v="2022-12-31T00:00:00"/>
+        <d v="2023-12-31T00:00:00"/>
+        <d v="2024-12-31T00:00:00"/>
+        <d v="2025-06-30T00:00:00"/>
+        <d v="2025-07-31T00:00:00"/>
+        <d v="2025-08-31T00:00:00"/>
+        <d v="2025-09-30T00:00:00"/>
+        <d v="2025-10-09T00:00:00"/>
+        <d v="2025-10-31T00:00:00"/>
+        <d v="2025-11-30T00:00:00"/>
+        <d v="2025-12-31T00:00:00"/>
+        <d v="2026-06-30T00:00:00"/>
+        <d v="2026-07-31T00:00:00"/>
+        <d v="2026-08-31T00:00:00"/>
+        <d v="2026-09-30T00:00:00"/>
+        <d v="2026-10-09T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="7"/>
+    </cacheField>
+    <cacheField name="ID" numFmtId="0">
+      <sharedItems count="13">
+        <s v="BBVACASH"/>
+        <s v="BBVARENTACORTOPLAZO"/>
+        <s v="BBVATESORERIASOLES"/>
+        <s v="CREDCONSERCORTOPLAZO"/>
+        <s v="CREDCONSERVADLIQUIDEZ"/>
+        <s v="SFLiquidez"/>
+        <s v="SURACORTOPLAZOSOLES"/>
+        <s v="SURAULTRACASHSOLES"/>
+        <s v="BBVARENTAMEDPLAZO"/>
+        <s v="CCMEDPLAZO"/>
+        <s v="IFMEDIANOPLAZO"/>
+        <s v="SURARENTASOLES"/>
+        <s v="ETFPESOV"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Valor Cuota" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="10.79655926" maxValue="413.52704188000001"/>
+    </cacheField>
+    <cacheField name="Patrimonio" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="47421040.450000003" maxValue="3451869354.6100001"/>
+    </cacheField>
+    <cacheField name="Partícipes" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="178" maxValue="81044"/>
+    </cacheField>
+    <cacheField name="Meses (Fecha)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="months" startDate="2022-12-31T00:00:00" endDate="2026-10-10T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;31/12/2022"/>
+          <s v="Ene"/>
+          <s v="Feb"/>
+          <s v="Mar"/>
+          <s v="Abr"/>
+          <s v="May"/>
+          <s v="Jun"/>
+          <s v="Jul"/>
+          <s v="Ago"/>
+          <s v="Set"/>
+          <s v="Oct"/>
+          <s v="Nov"/>
+          <s v="Dic"/>
+          <s v="&gt;10/10/2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Trimestres (Fecha)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="quarters" startDate="2022-12-31T00:00:00" endDate="2026-10-10T00:00:00"/>
+        <groupItems count="6">
+          <s v="&lt;31/12/2022"/>
+          <s v="Trim.1"/>
+          <s v="Trim.2"/>
+          <s v="Trim.3"/>
+          <s v="Trim.4"/>
+          <s v="&gt;10/10/2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Años (Fecha)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="years" startDate="2022-12-31T00:00:00" endDate="2026-10-10T00:00:00"/>
+        <groupItems count="7">
+          <s v="&lt;31/12/2022"/>
+          <s v="2022"/>
+          <s v="2023"/>
+          <s v="2024"/>
+          <s v="2025"/>
+          <s v="2026"/>
+          <s v="&gt;10/10/2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="205">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="144.59971811"/>
+    <n v="1780595701.9300001"/>
+    <n v="71633"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="173.71720182000001"/>
+    <n v="235607692.11000001"/>
+    <n v="6188"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="111.44877950999999"/>
+    <n v="164874402.99000001"/>
+    <n v="191"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="135.21020648000001"/>
+    <n v="476767647.56"/>
+    <n v="10418"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="296.69448505000003"/>
+    <n v="1497806644.1800001"/>
+    <n v="28520"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="167.8219181"/>
+    <n v="181420233.74000001"/>
+    <n v="827"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="7"/>
+    <n v="144.00388140000001"/>
+    <n v="573137696.12"/>
+    <n v="1948"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="8"/>
+    <n v="317.5136152"/>
+    <n v="75204728.650000006"/>
+    <n v="4096"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="9"/>
+    <n v="177.00756683"/>
+    <n v="329107281.64999998"/>
+    <n v="5181"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="10"/>
+    <n v="186.83269999999999"/>
+    <n v="52576790.329999998"/>
+    <n v="3251"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="11"/>
+    <n v="195.25890920000001"/>
+    <n v="47421040.450000003"/>
+    <n v="620"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="155.05096872999999"/>
+    <n v="1757718562.8199999"/>
+    <n v="67700"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="187.24948190999999"/>
+    <n v="223875481.59999999"/>
+    <n v="4845"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="119.44997167"/>
+    <n v="87141002.849999994"/>
+    <n v="178"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="145.55334999999999"/>
+    <n v="477245700.51999998"/>
+    <n v="10554"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="318.38266599999997"/>
+    <n v="1640067045.1600001"/>
+    <n v="30709"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="10.79655926"/>
+    <n v="722718733.80999994"/>
+    <n v="6888"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="6"/>
+    <n v="179.23148420000001"/>
+    <n v="75646215.840000004"/>
+    <n v="685"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <n v="154.70245499999999"/>
+    <n v="921797638.79999995"/>
+    <n v="2549"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="8"/>
+    <n v="350.77003454999999"/>
+    <n v="113231072.78"/>
+    <n v="4407"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <n v="193.46580499999999"/>
+    <n v="322695223.30000001"/>
+    <n v="4544"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="10"/>
+    <n v="204.38290000000001"/>
+    <n v="48272534.020000003"/>
+    <n v="3225"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="11"/>
+    <n v="210.82617690000001"/>
+    <n v="62212656.939999998"/>
+    <n v="605"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="163.61348584999999"/>
+    <n v="2785813379.1700001"/>
+    <n v="75933"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="197.93033137"/>
+    <n v="487072861.54000002"/>
+    <n v="5732"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="126.22174136"/>
+    <n v="291604962.11000001"/>
+    <n v="503"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="154.47121799999999"/>
+    <n v="876778097.27999997"/>
+    <n v="11126"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <n v="336.16375499999998"/>
+    <n v="2262660758.9099998"/>
+    <n v="33259"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <n v="11.34850312"/>
+    <n v="1199414211.3900001"/>
+    <n v="15968"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="6"/>
+    <n v="190.13847939999999"/>
+    <n v="229196493.75999999"/>
+    <n v="837"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="7"/>
+    <n v="163.48415209999999"/>
+    <n v="1563120388.29"/>
+    <n v="2645"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="8"/>
+    <n v="372.77834658"/>
+    <n v="236985701.34999999"/>
+    <n v="6808"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="9"/>
+    <n v="207.68079700000001"/>
+    <n v="476508901.11000001"/>
+    <n v="5366"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="10"/>
+    <n v="217.68049999999999"/>
+    <n v="59979894.689999998"/>
+    <n v="3421"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="11"/>
+    <n v="224.39302129999999"/>
+    <n v="109615940.83"/>
+    <n v="842"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="167.07511972"/>
+    <n v="3102255970.8000002"/>
+    <n v="80880"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="203.39865723"/>
+    <n v="713327723.94000006"/>
+    <n v="6867"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="128.97037555"/>
+    <n v="298446011.36000001"/>
+    <n v="586"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="158.32547199999999"/>
+    <n v="1001694254.91"/>
+    <n v="11741"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="343.86480699999998"/>
+    <n v="2766838110.2399998"/>
+    <n v="35316"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="11.597048770000001"/>
+    <n v="1266987358.23"/>
+    <n v="17865"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="6"/>
+    <n v="194.37889050000001"/>
+    <n v="210800593.33000001"/>
+    <n v="904"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="7"/>
+    <n v="167.17190740000001"/>
+    <n v="1345605629.5799999"/>
+    <n v="2282"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="8"/>
+    <n v="387.61274229999998"/>
+    <n v="301355442.52999997"/>
+    <n v="8012"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="9"/>
+    <n v="215.27327199999999"/>
+    <n v="614074843.98000002"/>
+    <n v="6226"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="10"/>
+    <n v="224.72149999999999"/>
+    <n v="76367739.25"/>
+    <n v="3607"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="11"/>
+    <n v="231.62023500000001"/>
+    <n v="108659193.23"/>
+    <n v="859"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="12"/>
+    <n v="104.077"/>
+    <n v="160538836"/>
+    <n v="195"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="167.64956842999999"/>
+    <n v="3078642149.5"/>
+    <n v="81044"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="204.37856231999999"/>
+    <n v="799486379.04999995"/>
+    <n v="7016"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="129.42988886000001"/>
+    <n v="294789962.27999997"/>
+    <n v="576"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="158.988519"/>
+    <n v="1031033582.17"/>
+    <n v="11947"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="345.110997"/>
+    <n v="2536105970.04"/>
+    <n v="35699"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="5"/>
+    <n v="11.63921322"/>
+    <n v="1251580814.6700001"/>
+    <n v="17766"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="6"/>
+    <n v="195.18316189999999"/>
+    <n v="229817708.03"/>
+    <n v="920"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="7"/>
+    <n v="167.79395239999999"/>
+    <n v="1396545851.9300001"/>
+    <n v="2244"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="8"/>
+    <n v="390.59586528"/>
+    <n v="320206500.63999999"/>
+    <n v="8295"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="9"/>
+    <n v="216.53612899999999"/>
+    <n v="646898858.19000006"/>
+    <n v="6459"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="10"/>
+    <n v="225.9716"/>
+    <n v="85025969.689999998"/>
+    <n v="3704"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="11"/>
+    <n v="232.6416213"/>
+    <n v="112822044.2"/>
+    <n v="874"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="12"/>
+    <n v="104.78189999999999"/>
+    <n v="161626065.99000001"/>
+    <n v="208"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="168.23558263000001"/>
+    <n v="3015298835.8299999"/>
+    <n v="80761"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="205.39002556"/>
+    <n v="897991417.98000002"/>
+    <n v="7099"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="2"/>
+    <n v="129.88868518000001"/>
+    <n v="301790271.91000003"/>
+    <n v="562"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="3"/>
+    <n v="159.74084300000001"/>
+    <n v="1076884783.3499999"/>
+    <n v="12131"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="4"/>
+    <n v="346.30228299999999"/>
+    <n v="2617465131.8000002"/>
+    <n v="35775"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <n v="11.681476330000001"/>
+    <n v="1217600708.01"/>
+    <n v="17560"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="6"/>
+    <n v="195.87096030000001"/>
+    <n v="277996661.42000002"/>
+    <n v="940"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="7"/>
+    <n v="168.4135532"/>
+    <n v="1473308890.9300001"/>
+    <n v="2207"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="8"/>
+    <n v="393.76626654"/>
+    <n v="349904163.51999998"/>
+    <n v="8460"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="9"/>
+    <n v="217.83012500000001"/>
+    <n v="676057856.75999999"/>
+    <n v="6674"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="10"/>
+    <n v="227.23140000000001"/>
+    <n v="91608131.040000007"/>
+    <n v="3783"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="11"/>
+    <n v="234.08105040000001"/>
+    <n v="119077037.17"/>
+    <n v="887"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="12"/>
+    <n v="105.94927979000001"/>
+    <n v="138263810.13"/>
+    <n v="213"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <n v="168.79042254999999"/>
+    <n v="2918602637.7800002"/>
+    <n v="80189"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="206.33787049"/>
+    <n v="916202232.72000003"/>
+    <n v="7193"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="2"/>
+    <n v="130.33427861000001"/>
+    <n v="271823785.62"/>
+    <n v="552"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="3"/>
+    <n v="160.29543200000001"/>
+    <n v="1186789207.8"/>
+    <n v="12368"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="4"/>
+    <n v="347.43418400000002"/>
+    <n v="2712754224.9499998"/>
+    <n v="36031"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="5"/>
+    <n v="11.72061527"/>
+    <n v="1201267646.29"/>
+    <n v="17223"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="6"/>
+    <n v="196.5501486"/>
+    <n v="330152510.06999999"/>
+    <n v="942"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="7"/>
+    <n v="169.00409590000001"/>
+    <n v="1416869051.3599999"/>
+    <n v="2160"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="8"/>
+    <n v="397.25437890000001"/>
+    <n v="379870300.24000001"/>
+    <n v="8738"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="9"/>
+    <n v="219.155531"/>
+    <n v="712552235.21000004"/>
+    <n v="6856"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="10"/>
+    <n v="228.79310000000001"/>
+    <n v="97265531.599999994"/>
+    <n v="3924"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="11"/>
+    <n v="235.7956131"/>
+    <n v="124571303.27"/>
+    <n v="897"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="12"/>
+    <n v="107.84736325999999"/>
+    <n v="163658374"/>
+    <n v="225"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="168.95558728"/>
+    <n v="2928603624.1599998"/>
+    <n v="80015"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <n v="206.46415440999999"/>
+    <n v="964581522.33000004"/>
+    <n v="7202"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="2"/>
+    <n v="130.46580786999999"/>
+    <n v="293106174.69999999"/>
+    <n v="546"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="160.45289"/>
+    <n v="1210142183.6500001"/>
+    <n v="12450"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="4"/>
+    <n v="347.74867799999998"/>
+    <n v="2695835758.3099999"/>
+    <n v="36224"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="5"/>
+    <n v="11.731005850000001"/>
+    <n v="1196654662"/>
+    <n v="17096"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="6"/>
+    <n v="196.71769019999999"/>
+    <n v="325599215.44"/>
+    <n v="936"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="7"/>
+    <n v="169.17041"/>
+    <n v="1561263617.4000001"/>
+    <n v="2168"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="8"/>
+    <n v="396.93344365000002"/>
+    <n v="386918774.95999998"/>
+    <n v="8808"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="9"/>
+    <n v="218.864071"/>
+    <n v="727217160.51999998"/>
+    <n v="6888"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="10"/>
+    <n v="228.6627"/>
+    <n v="101949300.45"/>
+    <n v="3939"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="11"/>
+    <n v="235.78312320000001"/>
+    <n v="125273127.11"/>
+    <n v="901"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="12"/>
+    <n v="107.89952589000001"/>
+    <n v="113833999.81"/>
+    <n v="216"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <n v="169.34801067999999"/>
+    <n v="2881515647.71"/>
+    <n v="79413"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="206.89603886"/>
+    <n v="972485492.37"/>
+    <n v="7201"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="2"/>
+    <n v="130.78976039"/>
+    <n v="256081799.15000001"/>
+    <n v="539"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="3"/>
+    <n v="160.68935400000001"/>
+    <n v="1188379776.6099999"/>
+    <n v="12553"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="4"/>
+    <n v="348.520308"/>
+    <n v="2661416365.75"/>
+    <n v="36809"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="5"/>
+    <n v="11.75824705"/>
+    <n v="1156942034.77"/>
+    <n v="16847"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="6"/>
+    <n v="197.17737410000001"/>
+    <n v="309110107.35000002"/>
+    <n v="928"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="7"/>
+    <n v="169.5712072"/>
+    <n v="1504501508"/>
+    <n v="2132"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="398.47251691000002"/>
+    <n v="396705750.75"/>
+    <n v="8860"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="9"/>
+    <n v="219.630042"/>
+    <n v="734812669.24000001"/>
+    <n v="6997"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="10"/>
+    <n v="229.2867"/>
+    <n v="103939528.25"/>
+    <n v="3972"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="11"/>
+    <n v="236.33786749999999"/>
+    <n v="125768006.2"/>
+    <n v="892"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="12"/>
+    <n v="108.20357921"/>
+    <n v="164469440"/>
+    <n v="240"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="0"/>
+    <n v="169.89725994"/>
+    <n v="2774755450.3899999"/>
+    <n v="78693"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="1"/>
+    <n v="207.59373528"/>
+    <n v="927872648.64999998"/>
+    <n v="7160"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="2"/>
+    <n v="131.23363684"/>
+    <n v="251796267.63"/>
+    <n v="535"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="3"/>
+    <n v="161.28463400000001"/>
+    <n v="1187961385.03"/>
+    <n v="12776"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="4"/>
+    <n v="349.62951199999998"/>
+    <n v="2707411558.3099999"/>
+    <n v="37790"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="5"/>
+    <n v="11.79905789"/>
+    <n v="1148623015.5899999"/>
+    <n v="16641"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="6"/>
+    <n v="197.84052919999999"/>
+    <n v="270640934.47000003"/>
+    <n v="916"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="7"/>
+    <n v="170.1964116"/>
+    <n v="1402076867.8699999"/>
+    <n v="2103"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="8"/>
+    <n v="400.43885283999998"/>
+    <n v="413932498.5"/>
+    <n v="8911"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="9"/>
+    <n v="220.76745099999999"/>
+    <n v="761136369.88999999"/>
+    <n v="7209"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="10"/>
+    <n v="230.49469999999999"/>
+    <n v="109662203.91"/>
+    <n v="4140"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="11"/>
+    <n v="237.84235090000001"/>
+    <n v="127028257.98999999"/>
+    <n v="905"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="12"/>
+    <n v="109.71508005"/>
+    <n v="167041209"/>
+    <n v="294"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="0"/>
+    <n v="170.46159245999999"/>
+    <n v="2757505401.1999998"/>
+    <n v="78091"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="1"/>
+    <n v="208.31806234999999"/>
+    <n v="918868055.85000002"/>
+    <n v="7149"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="2"/>
+    <n v="131.6919245"/>
+    <n v="256864855.19"/>
+    <n v="519"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="3"/>
+    <n v="161.838584"/>
+    <n v="1215687489.1700001"/>
+    <n v="12994"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="4"/>
+    <n v="350.75661400000001"/>
+    <n v="2704117777.5900002"/>
+    <n v="38857"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="5"/>
+    <n v="11.838826660000001"/>
+    <n v="1133807674.1700001"/>
+    <n v="16495"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="6"/>
+    <n v="198.572138"/>
+    <n v="284653202.20999998"/>
+    <n v="908"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="7"/>
+    <n v="170.7741771"/>
+    <n v="1440431627.4200001"/>
+    <n v="2065"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="8"/>
+    <n v="402.45125322000001"/>
+    <n v="435072515.97000003"/>
+    <n v="8934"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="9"/>
+    <n v="221.85736299999999"/>
+    <n v="798725071.94000006"/>
+    <n v="7502"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="10"/>
+    <n v="231.2962"/>
+    <n v="113809087.08"/>
+    <n v="4383"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="11"/>
+    <n v="239.07441919999999"/>
+    <n v="130310931.52"/>
+    <n v="915"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="12"/>
+    <n v="110.61604921999999"/>
+    <n v="167859855"/>
+    <n v="328"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="0"/>
+    <n v="173.72934685999999"/>
+    <n v="2755029376.04"/>
+    <n v="76508"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="1"/>
+    <n v="212.78308894"/>
+    <n v="913729885.00999999"/>
+    <n v="7226"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="2"/>
+    <n v="134.35108005000001"/>
+    <n v="294070137.10000002"/>
+    <n v="559"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="3"/>
+    <n v="165.161753"/>
+    <n v="1273986251.6199999"/>
+    <n v="13634"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="4"/>
+    <n v="357.63221700000003"/>
+    <n v="3155428348.3099999"/>
+    <n v="44078"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="5"/>
+    <n v="12.079791739999999"/>
+    <n v="1239412685.3499999"/>
+    <n v="16616"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="6"/>
+    <n v="202.4793817"/>
+    <n v="268981492.00999999"/>
+    <n v="909"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="7"/>
+    <n v="174.30474280000001"/>
+    <n v="1415523875.99"/>
+    <n v="2017"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="8"/>
+    <n v="410.65932354"/>
+    <n v="461143127.45999998"/>
+    <n v="8438"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="9"/>
+    <n v="227.20659000000001"/>
+    <n v="841428969.15999997"/>
+    <n v="8102"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="10"/>
+    <n v="235.39359999999999"/>
+    <n v="104979969.55"/>
+    <n v="4508"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="11"/>
+    <n v="243.78792050000001"/>
+    <n v="127233613.86"/>
+    <n v="888"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="12"/>
+    <n v="112.56613378999999"/>
+    <n v="202337625.49000001"/>
+    <n v="449"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="0"/>
+    <n v="174.31846501999999"/>
+    <n v="2714460737.9899998"/>
+    <n v="76158"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="1"/>
+    <n v="213.58180999000001"/>
+    <n v="927883838.01999998"/>
+    <n v="7251"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="2"/>
+    <n v="134.82905649"/>
+    <n v="309635566.69"/>
+    <n v="564"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="3"/>
+    <n v="165.67208099999999"/>
+    <n v="1300155400.52"/>
+    <n v="13863"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="4"/>
+    <n v="358.82808499999999"/>
+    <n v="3281456302.8499999"/>
+    <n v="44950"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="5"/>
+    <n v="12.122606530000001"/>
+    <n v="1234798460.1099999"/>
+    <n v="16736"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="6"/>
+    <n v="203.14380349999999"/>
+    <n v="194957198.62"/>
+    <n v="909"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="7"/>
+    <n v="174.92875620000001"/>
+    <n v="1240583547.5899999"/>
+    <n v="1987"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="8"/>
+    <n v="411.87582773999998"/>
+    <n v="472879276.06"/>
+    <n v="8522"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="9"/>
+    <n v="228.37178800000001"/>
+    <n v="859777580.77999997"/>
+    <n v="8250"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="10"/>
+    <n v="235.62559999999999"/>
+    <n v="105017921.93000001"/>
+    <n v="4553"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="11"/>
+    <n v="244.45138560000001"/>
+    <n v="129245461.34999999"/>
+    <n v="882"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="12"/>
+    <n v="113.10807698000001"/>
+    <n v="152695903.91999999"/>
+    <n v="449"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="0"/>
+    <n v="174.92760867999999"/>
+    <n v="2696336296.1199999"/>
+    <n v="75749"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="1"/>
+    <n v="214.56994126000001"/>
+    <n v="926049973"/>
+    <n v="7226"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="2"/>
+    <n v="135.32540791"/>
+    <n v="326176641.60000002"/>
+    <n v="566"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="3"/>
+    <n v="166.32631599999999"/>
+    <n v="1330545100.6300001"/>
+    <n v="13990"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="4"/>
+    <n v="360.02621199999999"/>
+    <n v="3386119097.6900001"/>
+    <n v="45517"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="5"/>
+    <n v="12.165339700000001"/>
+    <n v="1247745597.73"/>
+    <n v="16809"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="6"/>
+    <n v="203.8672832"/>
+    <n v="184350138.22"/>
+    <n v="890"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="7"/>
+    <n v="175.55553359999999"/>
+    <n v="1372214285.01"/>
+    <n v="1957"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="8"/>
+    <n v="413.52704188000001"/>
+    <n v="476906604.38999999"/>
+    <n v="8499"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="9"/>
+    <n v="228.46783600000001"/>
+    <n v="846675540.86000001"/>
+    <n v="8334"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="10"/>
+    <n v="235.76259999999999"/>
+    <n v="99791086.439999998"/>
+    <n v="4511"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="11"/>
+    <n v="244.73786240000001"/>
+    <n v="128349607.03"/>
+    <n v="859"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="12"/>
+    <n v="112.50574435"/>
+    <n v="152164019.24000001"/>
+    <n v="518"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="0"/>
+    <n v="175.50838275999999"/>
+    <n v="2705529159.8099999"/>
+    <n v="75292"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="1"/>
+    <n v="214.47442111000001"/>
+    <n v="917635044.80999994"/>
+    <n v="7147"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="2"/>
+    <n v="135.79414928"/>
+    <n v="359423998.38"/>
+    <n v="597"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="3"/>
+    <n v="166.12638113"/>
+    <n v="1320047031.1900001"/>
+    <n v="13880"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="4"/>
+    <n v="361.10296736999999"/>
+    <n v="3358169486.3899999"/>
+    <n v="45627"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="5"/>
+    <n v="12.203462500000001"/>
+    <n v="1253304551.1400001"/>
+    <n v="16925"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="6"/>
+    <n v="203.7424178"/>
+    <n v="186504024.28999999"/>
+    <n v="881"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="7"/>
+    <n v="176.1565659"/>
+    <n v="1543437489.8199999"/>
+    <n v="1953"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="8"/>
+    <n v="409.07142088000001"/>
+    <n v="445717202.87"/>
+    <n v="8243"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="9"/>
+    <n v="226.09731866999999"/>
+    <n v="783883688.35000002"/>
+    <n v="8119"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="10"/>
+    <n v="233.64169999999999"/>
+    <n v="91765003.560000002"/>
+    <n v="4360"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="11"/>
+    <n v="242.900756"/>
+    <n v="120721586.34"/>
+    <n v="838"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="12"/>
+    <n v="110.04027514086383"/>
+    <n v="148829472.12801832"/>
+    <n v="547"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="0"/>
+    <n v="175.68375476"/>
+    <n v="2705748233.4099998"/>
+    <n v="75164"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="1"/>
+    <n v="214.81611819"/>
+    <n v="897019568.54999995"/>
+    <n v="7069"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="2"/>
+    <n v="135.93525915000001"/>
+    <n v="385465944.74000001"/>
+    <n v="610"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="3"/>
+    <n v="166.41805854"/>
+    <n v="1317793069.1300001"/>
+    <n v="13802"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="4"/>
+    <n v="361.46004819000001"/>
+    <n v="3451869354.6100001"/>
+    <n v="45759"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="5"/>
+    <n v="12.21523575"/>
+    <n v="1249435239.9400001"/>
+    <n v="16986"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="6"/>
+    <n v="204.02861960000001"/>
+    <n v="194753456.19999999"/>
+    <n v="877"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="7"/>
+    <n v="176.33114180000001"/>
+    <n v="1666496529.3"/>
+    <n v="1979"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="8"/>
+    <n v="410.30980470999998"/>
+    <n v="435373898.41000003"/>
+    <n v="8142"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="9"/>
+    <n v="226.63490805999999"/>
+    <n v="768176827.78999996"/>
+    <n v="8043"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="10"/>
+    <n v="234.13839999999999"/>
+    <n v="87314060.650000006"/>
+    <n v="4305"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="11"/>
+    <n v="243.4637008"/>
+    <n v="118502088.41"/>
+    <n v="835"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="12"/>
+    <n v="110.882600109728"/>
+    <n v="149414303.64785901"/>
+    <n v="547"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9E1EE6FA-EDA0-450B-8136-69F3AB7ECB29}" name="TablaDinámica1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C32" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField axis="axisRow" numFmtId="14" showAll="0" sortType="ascending">
+      <items count="17">
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
+        <item x="7"/>
+        <item h="1" x="8"/>
+        <item h="1" x="9"/>
+        <item h="1" x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item x="15"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="8">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="29">
+    <i>
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Suma de Valor Cuota" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Patrimonio" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1766,7 +3572,7 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>405</v>
       </c>
       <c r="E2" s="1">
         <v>39784</v>
@@ -1834,7 +3640,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>405</v>
       </c>
       <c r="E6" s="1">
         <v>36622</v>
@@ -1851,7 +3657,7 @@
         <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>405</v>
       </c>
       <c r="E7" s="1">
         <v>44956</v>
@@ -1885,7 +3691,7 @@
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>405</v>
       </c>
       <c r="E9" s="1">
         <v>41038</v>
@@ -1982,3280 +3788,559 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E90F8A8D-E010-4622-BBF4-8117B763A2FF}">
-  <dimension ref="A1:E193"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA80A206-04F4-4869-BD63-B7EF3BA6EA57}">
+  <dimension ref="A3:N33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>44926</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="B3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="16">
+        <v>45939</v>
+      </c>
+      <c r="B4" s="18">
+        <v>2579.84908735</v>
+      </c>
+      <c r="C4" s="18">
+        <v>12630979120.84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C2">
-        <v>144.59971811</v>
-      </c>
-      <c r="D2">
-        <v>1780595701.9300001</v>
-      </c>
-      <c r="E2">
-        <v>71633</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>44926</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B5" s="18">
+        <v>168.95558728</v>
+      </c>
+      <c r="C5" s="18">
+        <v>2928603624.1599998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C3">
-        <v>173.71720182000001</v>
-      </c>
-      <c r="D3">
-        <v>235607692.11000001</v>
-      </c>
-      <c r="E3">
-        <v>6188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B6" s="18">
+        <v>206.46415440999999</v>
+      </c>
+      <c r="C6" s="18">
+        <v>964581522.33000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="18">
+        <v>396.93344365000002</v>
+      </c>
+      <c r="C7" s="18">
+        <v>386918774.95999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C4">
-        <v>111.44877950999999</v>
-      </c>
-      <c r="D4">
-        <v>164874402.99000001</v>
-      </c>
-      <c r="E4">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>44926</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B8" s="18">
+        <v>130.46580786999999</v>
+      </c>
+      <c r="C8" s="18">
+        <v>293106174.69999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="18">
+        <v>218.864071</v>
+      </c>
+      <c r="C9" s="18">
+        <v>727217160.51999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C5">
-        <v>135.21020648000001</v>
-      </c>
-      <c r="D5">
-        <v>476767647.56</v>
-      </c>
-      <c r="E5">
-        <v>10418</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>44926</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B10" s="18">
+        <v>160.45289</v>
+      </c>
+      <c r="C10" s="18">
+        <v>1210142183.6500001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C6">
-        <v>296.69448505000003</v>
-      </c>
-      <c r="D6">
-        <v>1497806644.1800001</v>
-      </c>
-      <c r="E6">
-        <v>28520</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>44926</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="B11" s="18">
+        <v>347.74867799999998</v>
+      </c>
+      <c r="C11" s="18">
+        <v>2695835758.3099999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="18">
+        <v>107.89952589000001</v>
+      </c>
+      <c r="C12" s="18">
+        <v>113833999.81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="18">
+        <v>228.6627</v>
+      </c>
+      <c r="C13" s="18">
+        <v>101949300.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>44926</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="B14" s="18">
+        <v>11.731005850000001</v>
+      </c>
+      <c r="C14" s="18">
+        <v>1196654662</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C8">
-        <v>167.8219181</v>
-      </c>
-      <c r="D8">
-        <v>181420233.74000001</v>
-      </c>
-      <c r="E8">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>44926</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="B15" s="18">
+        <v>196.71769019999999</v>
+      </c>
+      <c r="C15" s="18">
+        <v>325599215.44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="18">
+        <v>235.78312320000001</v>
+      </c>
+      <c r="C16" s="18">
+        <v>125273127.11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C9">
-        <v>144.00388140000001</v>
-      </c>
-      <c r="D9">
-        <v>573137696.12</v>
-      </c>
-      <c r="E9">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>44926</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B17" s="18">
+        <v>169.17041</v>
+      </c>
+      <c r="C17" s="18">
+        <v>1561263617.4000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="16">
+        <v>46304</v>
+      </c>
+      <c r="B18" s="18">
+        <v>2672.317649659728</v>
+      </c>
+      <c r="C18" s="18">
+        <v>13427362574.787859</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="18">
+        <v>175.68375476</v>
+      </c>
+      <c r="C19" s="18">
+        <v>2705748233.4099998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="18">
+        <v>214.81611819</v>
+      </c>
+      <c r="C20" s="18">
+        <v>897019568.54999995</v>
+      </c>
+      <c r="E20" t="s">
+        <v>403</v>
+      </c>
+      <c r="G20">
+        <f>SUMPRODUCT(F21:F24,G21:G24)/SUM(G21:G24)</f>
+        <v>204.05176018463229</v>
+      </c>
+      <c r="L20">
+        <f>SUMPRODUCT(K21:K24,L21:L24)/SUM(L21:L24)</f>
+        <v>223.96817101623438</v>
+      </c>
+      <c r="M20" s="19">
+        <f>SUMPRODUCT(M21:M24,L21:L24)/SUM(L21:L24)</f>
+        <v>4.0333330315490322E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C10">
-        <v>317.5136152</v>
-      </c>
-      <c r="D10">
-        <v>75204728.650000006</v>
-      </c>
-      <c r="E10">
-        <v>4096</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>44926</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B21" s="18">
+        <v>410.30980470999998</v>
+      </c>
+      <c r="C21" s="18">
+        <v>435373898.41000003</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21">
+        <v>347.74867799999998</v>
+      </c>
+      <c r="G21">
+        <v>2695835758.3099999</v>
+      </c>
+      <c r="J21" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21">
+        <v>361.46004819000001</v>
+      </c>
+      <c r="L21">
+        <v>3451869354.6100001</v>
+      </c>
+      <c r="M21" s="19">
+        <f>K21/F21-1</f>
+        <v>3.9428964241813746E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="18">
+        <v>135.93525915000001</v>
+      </c>
+      <c r="C22" s="18">
+        <v>385465944.74000001</v>
+      </c>
+      <c r="E22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22">
+        <v>11.731005850000001</v>
+      </c>
+      <c r="G22">
+        <v>1196654662</v>
+      </c>
+      <c r="J22" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22">
+        <v>12.21523575</v>
+      </c>
+      <c r="L22">
+        <v>1249435239.9400001</v>
+      </c>
+      <c r="M22" s="19">
+        <f t="shared" ref="M22:M24" si="0">K22/F22-1</f>
+        <v>4.1277781819535786E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C11">
-        <v>177.00756683</v>
-      </c>
-      <c r="D11">
-        <v>329107281.64999998</v>
-      </c>
-      <c r="E11">
-        <v>5181</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>44926</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="B23" s="18">
+        <v>226.63490805999999</v>
+      </c>
+      <c r="C23" s="18">
+        <v>768176827.78999996</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23">
+        <v>168.95558728</v>
+      </c>
+      <c r="G23">
+        <v>2928603624.1599998</v>
+      </c>
+      <c r="J23" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23">
+        <v>175.68375476</v>
+      </c>
+      <c r="L23">
+        <v>2705748233.4099998</v>
+      </c>
+      <c r="M23" s="19">
+        <f>K23/F23-1</f>
+        <v>3.9822107030114351E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="18">
+        <v>166.41805854</v>
+      </c>
+      <c r="C24" s="18">
+        <v>1317793069.1300001</v>
+      </c>
+      <c r="E24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24">
+        <v>169.17041</v>
+      </c>
+      <c r="G24">
+        <v>1561263617.4000001</v>
+      </c>
+      <c r="J24" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24">
+        <v>176.33114180000001</v>
+      </c>
+      <c r="L24">
+        <v>1666496529.3</v>
+      </c>
+      <c r="M24" s="19">
+        <f t="shared" si="0"/>
+        <v>4.2328512415380493E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="18">
+        <v>361.46004819000001</v>
+      </c>
+      <c r="C25" s="18">
+        <v>3451869354.6100001</v>
+      </c>
+      <c r="M25" s="19"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="18">
+        <v>110.882600109728</v>
+      </c>
+      <c r="C26" s="18">
+        <v>149414303.64785901</v>
+      </c>
+      <c r="E26" t="s">
+        <v>404</v>
+      </c>
+      <c r="G26">
+        <f>SUMPRODUCT(F27:F30,G27:G30)/SUM(G27:G30)</f>
+        <v>177.42128454218926</v>
+      </c>
+      <c r="L26">
+        <f>SUMPRODUCT(K27:K30,L27:L30)/SUM(L27:L30)</f>
+        <v>180.36734847229721</v>
+      </c>
+      <c r="M26" s="19">
+        <f>SUMPRODUCT(M27:M30,L27:L30)/SUM(L27:L30)</f>
+        <v>3.8881798619501286E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C12">
-        <v>186.83269999999999</v>
-      </c>
-      <c r="D12">
-        <v>52576790.329999998</v>
-      </c>
-      <c r="E12">
-        <v>3251</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>44926</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="B27" s="18">
+        <v>234.13839999999999</v>
+      </c>
+      <c r="C27" s="18">
+        <v>87314060.650000006</v>
+      </c>
+      <c r="E27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27">
+        <v>206.46415440999999</v>
+      </c>
+      <c r="G27">
+        <v>964581522.33000004</v>
+      </c>
+      <c r="J27" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27">
+        <v>214.81611819</v>
+      </c>
+      <c r="L27">
+        <v>897019568.54999995</v>
+      </c>
+      <c r="M27" s="19">
+        <f>K27/F27-1</f>
+        <v>4.045236716207179E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="18">
+        <v>12.21523575</v>
+      </c>
+      <c r="C28" s="18">
+        <v>1249435239.9400001</v>
+      </c>
+      <c r="E28" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28">
+        <v>130.46580786999999</v>
+      </c>
+      <c r="G28">
+        <v>293106174.69999999</v>
+      </c>
+      <c r="J28" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28">
+        <v>135.93525915000001</v>
+      </c>
+      <c r="L28">
+        <v>385465944.74000001</v>
+      </c>
+      <c r="M28" s="19">
+        <f t="shared" ref="M28:M30" si="1">K28/F28-1</f>
+        <v>4.1922488116196144E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="18">
+        <v>204.02861960000001</v>
+      </c>
+      <c r="C29" s="18">
+        <v>194753456.19999999</v>
+      </c>
+      <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29">
+        <v>160.45289</v>
+      </c>
+      <c r="G29">
+        <v>1210142183.6500001</v>
+      </c>
+      <c r="J29" t="s">
+        <v>25</v>
+      </c>
+      <c r="K29">
+        <v>166.41805854</v>
+      </c>
+      <c r="L29">
+        <v>1317793069.1300001</v>
+      </c>
+      <c r="M29" s="19">
+        <f t="shared" si="1"/>
+        <v>3.7177071350974256E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C13">
-        <v>195.25890920000001</v>
-      </c>
-      <c r="D13">
-        <v>47421040.450000003</v>
-      </c>
-      <c r="E13">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>45291</v>
-      </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14">
-        <v>155.05096872999999</v>
-      </c>
-      <c r="D14">
-        <v>1757718562.8199999</v>
-      </c>
-      <c r="E14">
-        <v>67700</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>45291</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15">
-        <v>187.24948190999999</v>
-      </c>
-      <c r="D15">
-        <v>223875481.59999999</v>
-      </c>
-      <c r="E15">
-        <v>4845</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>45291</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16">
-        <v>119.44997167</v>
-      </c>
-      <c r="D16">
-        <v>87141002.849999994</v>
-      </c>
-      <c r="E16">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>45291</v>
-      </c>
-      <c r="B17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17">
-        <v>145.55334999999999</v>
-      </c>
-      <c r="D17">
-        <v>477245700.51999998</v>
-      </c>
-      <c r="E17">
-        <v>10554</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>45291</v>
-      </c>
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18">
-        <v>318.38266599999997</v>
-      </c>
-      <c r="D18">
-        <v>1640067045.1600001</v>
-      </c>
-      <c r="E18">
-        <v>30709</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>45291</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19">
-        <v>10.79655926</v>
-      </c>
-      <c r="D19">
-        <v>722718733.80999994</v>
-      </c>
-      <c r="E19">
-        <v>6888</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>45291</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="B30" s="18">
+        <v>243.4637008</v>
+      </c>
+      <c r="C30" s="18">
+        <v>118502088.41</v>
+      </c>
+      <c r="E30" t="s">
         <v>28</v>
       </c>
-      <c r="C20">
-        <v>179.23148420000001</v>
-      </c>
-      <c r="D20">
-        <v>75646215.840000004</v>
-      </c>
-      <c r="E20">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>45291</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="F30">
+        <v>196.71769019999999</v>
+      </c>
+      <c r="G30">
+        <v>325599215.44</v>
+      </c>
+      <c r="J30" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30">
+        <v>204.02861960000001</v>
+      </c>
+      <c r="L30">
+        <v>194753456.19999999</v>
+      </c>
+      <c r="M30" s="19">
+        <f t="shared" si="1"/>
+        <v>3.7164575247742526E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C21">
-        <v>154.70245499999999</v>
-      </c>
-      <c r="D21">
-        <v>921797638.79999995</v>
-      </c>
-      <c r="E21">
-        <v>2549</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>45291</v>
-      </c>
-      <c r="B22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22">
-        <v>350.77003454999999</v>
-      </c>
-      <c r="D22">
-        <v>113231072.78</v>
-      </c>
-      <c r="E22">
-        <v>4407</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>45291</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23">
-        <v>193.46580499999999</v>
-      </c>
-      <c r="D23">
-        <v>322695223.30000001</v>
-      </c>
-      <c r="E23">
-        <v>4544</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>45291</v>
-      </c>
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24">
-        <v>204.38290000000001</v>
-      </c>
-      <c r="D24">
-        <v>48272534.020000003</v>
-      </c>
-      <c r="E24">
-        <v>3225</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>45291</v>
-      </c>
-      <c r="B25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25">
-        <v>210.82617690000001</v>
-      </c>
-      <c r="D25">
-        <v>62212656.939999998</v>
-      </c>
-      <c r="E25">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>45657</v>
-      </c>
-      <c r="B26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26">
-        <v>163.61348584999999</v>
-      </c>
-      <c r="D26">
-        <v>2785813379.1700001</v>
-      </c>
-      <c r="E26">
-        <v>75933</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>45657</v>
-      </c>
-      <c r="B27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27">
-        <v>197.93033137</v>
-      </c>
-      <c r="D27">
-        <v>487072861.54000002</v>
-      </c>
-      <c r="E27">
-        <v>5732</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>45657</v>
-      </c>
-      <c r="B28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28">
-        <v>126.22174136</v>
-      </c>
-      <c r="D28">
-        <v>291604962.11000001</v>
-      </c>
-      <c r="E28">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>45657</v>
-      </c>
-      <c r="B29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29">
-        <v>154.47121799999999</v>
-      </c>
-      <c r="D29">
-        <v>876778097.27999997</v>
-      </c>
-      <c r="E29">
-        <v>11126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>45657</v>
-      </c>
-      <c r="B30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30">
-        <v>336.16375499999998</v>
-      </c>
-      <c r="D30">
-        <v>2262660758.9099998</v>
-      </c>
-      <c r="E30">
-        <v>33259</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <v>45657</v>
-      </c>
-      <c r="B31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31">
-        <v>11.34850312</v>
-      </c>
-      <c r="D31">
-        <v>1199414211.3900001</v>
-      </c>
-      <c r="E31">
-        <v>15968</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
-        <v>45657</v>
-      </c>
-      <c r="B32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32">
-        <v>190.13847939999999</v>
-      </c>
-      <c r="D32">
-        <v>229196493.75999999</v>
-      </c>
-      <c r="E32">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
-        <v>45657</v>
-      </c>
-      <c r="B33" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33">
-        <v>163.48415209999999</v>
-      </c>
-      <c r="D33">
-        <v>1563120388.29</v>
-      </c>
-      <c r="E33">
-        <v>2645</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
-        <v>45657</v>
-      </c>
-      <c r="B34" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34">
-        <v>372.77834658</v>
-      </c>
-      <c r="D34">
-        <v>236985701.34999999</v>
-      </c>
-      <c r="E34">
-        <v>6808</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
-        <v>45657</v>
-      </c>
-      <c r="B35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35">
-        <v>207.68079700000001</v>
-      </c>
-      <c r="D35">
-        <v>476508901.11000001</v>
-      </c>
-      <c r="E35">
-        <v>5366</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
-        <v>45657</v>
-      </c>
-      <c r="B36" t="s">
-        <v>34</v>
-      </c>
-      <c r="C36">
-        <v>217.68049999999999</v>
-      </c>
-      <c r="D36">
-        <v>59979894.689999998</v>
-      </c>
-      <c r="E36">
-        <v>3421</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
-        <v>45657</v>
-      </c>
-      <c r="B37" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37">
-        <v>224.39302129999999</v>
-      </c>
-      <c r="D37">
-        <v>109615940.83</v>
-      </c>
-      <c r="E37">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38">
-        <v>167.07511972</v>
-      </c>
-      <c r="D38">
-        <v>3102255970.8000002</v>
-      </c>
-      <c r="E38">
-        <v>80880</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39">
-        <v>203.39865723</v>
-      </c>
-      <c r="D39">
-        <v>713327723.94000006</v>
-      </c>
-      <c r="E39">
-        <v>6867</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B40" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40">
-        <v>128.97037555</v>
-      </c>
-      <c r="D40">
-        <v>298446011.36000001</v>
-      </c>
-      <c r="E40">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B41" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41">
-        <v>158.32547199999999</v>
-      </c>
-      <c r="D41">
-        <v>1001694254.91</v>
-      </c>
-      <c r="E41">
-        <v>11741</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B42" t="s">
-        <v>26</v>
-      </c>
-      <c r="C42">
-        <v>343.86480699999998</v>
-      </c>
-      <c r="D42">
-        <v>2766838110.2399998</v>
-      </c>
-      <c r="E42">
-        <v>35316</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B43" t="s">
-        <v>27</v>
-      </c>
-      <c r="C43">
-        <v>11.597048770000001</v>
-      </c>
-      <c r="D43">
-        <v>1266987358.23</v>
-      </c>
-      <c r="E43">
-        <v>17865</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B44" t="s">
-        <v>28</v>
-      </c>
-      <c r="C44">
-        <v>194.37889050000001</v>
-      </c>
-      <c r="D44">
-        <v>210800593.33000001</v>
-      </c>
-      <c r="E44">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B45" t="s">
-        <v>29</v>
-      </c>
-      <c r="C45">
-        <v>167.17190740000001</v>
-      </c>
-      <c r="D45">
-        <v>1345605629.5799999</v>
-      </c>
-      <c r="E45">
-        <v>2282</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C46">
-        <v>387.61274229999998</v>
-      </c>
-      <c r="D46">
-        <v>301355442.52999997</v>
-      </c>
-      <c r="E46">
-        <v>8012</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B47" t="s">
-        <v>33</v>
-      </c>
-      <c r="C47">
-        <v>215.27327199999999</v>
-      </c>
-      <c r="D47">
-        <v>614074843.98000002</v>
-      </c>
-      <c r="E47">
-        <v>6226</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B48" t="s">
-        <v>34</v>
-      </c>
-      <c r="C48">
-        <v>224.72149999999999</v>
-      </c>
-      <c r="D48">
-        <v>76367739.25</v>
-      </c>
-      <c r="E48">
-        <v>3607</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B49" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49">
-        <v>231.62023500000001</v>
-      </c>
-      <c r="D49">
-        <v>108659193.23</v>
-      </c>
-      <c r="E49">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B50" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50">
-        <v>104.077</v>
-      </c>
-      <c r="D50">
-        <v>160538836</v>
-      </c>
-      <c r="E50">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B51" t="s">
-        <v>22</v>
-      </c>
-      <c r="C51">
-        <v>167.64956842999999</v>
-      </c>
-      <c r="D51">
-        <v>3078642149.5</v>
-      </c>
-      <c r="E51">
-        <v>81044</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B52" t="s">
-        <v>23</v>
-      </c>
-      <c r="C52">
-        <v>204.37856231999999</v>
-      </c>
-      <c r="D52">
-        <v>799486379.04999995</v>
-      </c>
-      <c r="E52">
-        <v>7016</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B53" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53">
-        <v>129.42988886000001</v>
-      </c>
-      <c r="D53">
-        <v>294789962.27999997</v>
-      </c>
-      <c r="E53">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B54" t="s">
-        <v>25</v>
-      </c>
-      <c r="C54">
-        <v>158.988519</v>
-      </c>
-      <c r="D54">
-        <v>1031033582.17</v>
-      </c>
-      <c r="E54">
-        <v>11947</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B55" t="s">
-        <v>26</v>
-      </c>
-      <c r="C55">
-        <v>345.110997</v>
-      </c>
-      <c r="D55">
-        <v>2536105970.04</v>
-      </c>
-      <c r="E55">
-        <v>35699</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B56" t="s">
-        <v>27</v>
-      </c>
-      <c r="C56">
-        <v>11.63921322</v>
-      </c>
-      <c r="D56">
-        <v>1251580814.6700001</v>
-      </c>
-      <c r="E56">
-        <v>17766</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B57" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57">
-        <v>195.18316189999999</v>
-      </c>
-      <c r="D57">
-        <v>229817708.03</v>
-      </c>
-      <c r="E57">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B58" t="s">
-        <v>29</v>
-      </c>
-      <c r="C58">
-        <v>167.79395239999999</v>
-      </c>
-      <c r="D58">
-        <v>1396545851.9300001</v>
-      </c>
-      <c r="E58">
-        <v>2244</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C59">
-        <v>390.59586528</v>
-      </c>
-      <c r="D59">
-        <v>320206500.63999999</v>
-      </c>
-      <c r="E59">
-        <v>8295</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B60" t="s">
-        <v>33</v>
-      </c>
-      <c r="C60">
-        <v>216.53612899999999</v>
-      </c>
-      <c r="D60">
-        <v>646898858.19000006</v>
-      </c>
-      <c r="E60">
-        <v>6459</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B61" t="s">
-        <v>34</v>
-      </c>
-      <c r="C61">
-        <v>225.9716</v>
-      </c>
-      <c r="D61">
-        <v>85025969.689999998</v>
-      </c>
-      <c r="E61">
-        <v>3704</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B62" t="s">
-        <v>35</v>
-      </c>
-      <c r="C62">
-        <v>232.6416213</v>
-      </c>
-      <c r="D62">
-        <v>112822044.2</v>
-      </c>
-      <c r="E62">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B63" t="s">
-        <v>40</v>
-      </c>
-      <c r="C63">
-        <v>104.78189999999999</v>
-      </c>
-      <c r="D63">
-        <v>161626065.99000001</v>
-      </c>
-      <c r="E63">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B64" t="s">
-        <v>22</v>
-      </c>
-      <c r="C64">
-        <v>168.23558263000001</v>
-      </c>
-      <c r="D64">
-        <v>3015298835.8299999</v>
-      </c>
-      <c r="E64">
-        <v>80761</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B65" t="s">
-        <v>23</v>
-      </c>
-      <c r="C65">
-        <v>205.39002556</v>
-      </c>
-      <c r="D65">
-        <v>897991417.98000002</v>
-      </c>
-      <c r="E65">
-        <v>7099</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B66" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66">
-        <v>129.88868518000001</v>
-      </c>
-      <c r="D66">
-        <v>301790271.91000003</v>
-      </c>
-      <c r="E66">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B67" t="s">
-        <v>25</v>
-      </c>
-      <c r="C67">
-        <v>159.74084300000001</v>
-      </c>
-      <c r="D67">
-        <v>1076884783.3499999</v>
-      </c>
-      <c r="E67">
-        <v>12131</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B68" t="s">
-        <v>26</v>
-      </c>
-      <c r="C68">
-        <v>346.30228299999999</v>
-      </c>
-      <c r="D68">
-        <v>2617465131.8000002</v>
-      </c>
-      <c r="E68">
-        <v>35775</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B69" t="s">
-        <v>27</v>
-      </c>
-      <c r="C69">
-        <v>11.681476330000001</v>
-      </c>
-      <c r="D69">
-        <v>1217600708.01</v>
-      </c>
-      <c r="E69">
-        <v>17560</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B70" t="s">
-        <v>28</v>
-      </c>
-      <c r="C70">
-        <v>195.87096030000001</v>
-      </c>
-      <c r="D70">
-        <v>277996661.42000002</v>
-      </c>
-      <c r="E70">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B71" t="s">
-        <v>29</v>
-      </c>
-      <c r="C71">
-        <v>168.4135532</v>
-      </c>
-      <c r="D71">
-        <v>1473308890.9300001</v>
-      </c>
-      <c r="E71">
-        <v>2207</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B72" t="s">
-        <v>32</v>
-      </c>
-      <c r="C72">
-        <v>393.76626654</v>
-      </c>
-      <c r="D72">
-        <v>349904163.51999998</v>
-      </c>
-      <c r="E72">
-        <v>8460</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B73" t="s">
-        <v>33</v>
-      </c>
-      <c r="C73">
-        <v>217.83012500000001</v>
-      </c>
-      <c r="D73">
-        <v>676057856.75999999</v>
-      </c>
-      <c r="E73">
-        <v>6674</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B74" t="s">
-        <v>34</v>
-      </c>
-      <c r="C74">
-        <v>227.23140000000001</v>
-      </c>
-      <c r="D74">
-        <v>91608131.040000007</v>
-      </c>
-      <c r="E74">
-        <v>3783</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B75" t="s">
-        <v>35</v>
-      </c>
-      <c r="C75">
-        <v>234.08105040000001</v>
-      </c>
-      <c r="D75">
-        <v>119077037.17</v>
-      </c>
-      <c r="E75">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B76" t="s">
-        <v>40</v>
-      </c>
-      <c r="C76">
-        <v>105.94927979000001</v>
-      </c>
-      <c r="D76">
-        <v>138263810.13</v>
-      </c>
-      <c r="E76">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B77" t="s">
-        <v>22</v>
-      </c>
-      <c r="C77">
-        <v>168.79042254999999</v>
-      </c>
-      <c r="D77">
-        <v>2918602637.7800002</v>
-      </c>
-      <c r="E77">
-        <v>80189</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B78" t="s">
-        <v>23</v>
-      </c>
-      <c r="C78">
-        <v>206.33787049</v>
-      </c>
-      <c r="D78">
-        <v>916202232.72000003</v>
-      </c>
-      <c r="E78">
-        <v>7193</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B79" t="s">
-        <v>24</v>
-      </c>
-      <c r="C79">
-        <v>130.33427861000001</v>
-      </c>
-      <c r="D79">
-        <v>271823785.62</v>
-      </c>
-      <c r="E79">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B80" t="s">
-        <v>25</v>
-      </c>
-      <c r="C80">
-        <v>160.29543200000001</v>
-      </c>
-      <c r="D80">
-        <v>1186789207.8</v>
-      </c>
-      <c r="E80">
-        <v>12368</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B81" t="s">
-        <v>26</v>
-      </c>
-      <c r="C81">
-        <v>347.43418400000002</v>
-      </c>
-      <c r="D81">
-        <v>2712754224.9499998</v>
-      </c>
-      <c r="E81">
-        <v>36031</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B82" t="s">
-        <v>27</v>
-      </c>
-      <c r="C82">
-        <v>11.72061527</v>
-      </c>
-      <c r="D82">
-        <v>1201267646.29</v>
-      </c>
-      <c r="E82">
-        <v>17223</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B83" t="s">
-        <v>28</v>
-      </c>
-      <c r="C83">
-        <v>196.5501486</v>
-      </c>
-      <c r="D83">
-        <v>330152510.06999999</v>
-      </c>
-      <c r="E83">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B84" t="s">
-        <v>29</v>
-      </c>
-      <c r="C84">
-        <v>169.00409590000001</v>
-      </c>
-      <c r="D84">
-        <v>1416869051.3599999</v>
-      </c>
-      <c r="E84">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B85" t="s">
-        <v>32</v>
-      </c>
-      <c r="C85">
-        <v>397.25437890000001</v>
-      </c>
-      <c r="D85">
-        <v>379870300.24000001</v>
-      </c>
-      <c r="E85">
-        <v>8738</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B86" t="s">
-        <v>33</v>
-      </c>
-      <c r="C86">
-        <v>219.155531</v>
-      </c>
-      <c r="D86">
-        <v>712552235.21000004</v>
-      </c>
-      <c r="E86">
-        <v>6856</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B87" t="s">
-        <v>34</v>
-      </c>
-      <c r="C87">
-        <v>228.79310000000001</v>
-      </c>
-      <c r="D87">
-        <v>97265531.599999994</v>
-      </c>
-      <c r="E87">
-        <v>3924</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B88" t="s">
-        <v>35</v>
-      </c>
-      <c r="C88">
-        <v>235.7956131</v>
-      </c>
-      <c r="D88">
-        <v>124571303.27</v>
-      </c>
-      <c r="E88">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B89" t="s">
-        <v>40</v>
-      </c>
-      <c r="C89">
-        <v>107.84736325999999</v>
-      </c>
-      <c r="D89">
-        <v>163658374</v>
-      </c>
-      <c r="E89">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B90" t="s">
-        <v>22</v>
-      </c>
-      <c r="C90">
-        <v>169.34801067999999</v>
-      </c>
-      <c r="D90">
-        <v>2881515647.71</v>
-      </c>
-      <c r="E90">
-        <v>79413</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B91" t="s">
-        <v>23</v>
-      </c>
-      <c r="C91">
-        <v>206.89603886</v>
-      </c>
-      <c r="D91">
-        <v>972485492.37</v>
-      </c>
-      <c r="E91">
-        <v>7201</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B92" t="s">
-        <v>24</v>
-      </c>
-      <c r="C92">
-        <v>130.78976039</v>
-      </c>
-      <c r="D92">
-        <v>256081799.15000001</v>
-      </c>
-      <c r="E92">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B93" t="s">
-        <v>25</v>
-      </c>
-      <c r="C93">
-        <v>160.68935400000001</v>
-      </c>
-      <c r="D93">
-        <v>1188379776.6099999</v>
-      </c>
-      <c r="E93">
-        <v>12553</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B94" t="s">
-        <v>26</v>
-      </c>
-      <c r="C94">
-        <v>348.520308</v>
-      </c>
-      <c r="D94">
-        <v>2661416365.75</v>
-      </c>
-      <c r="E94">
-        <v>36809</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B95" t="s">
-        <v>27</v>
-      </c>
-      <c r="C95">
-        <v>11.75824705</v>
-      </c>
-      <c r="D95">
-        <v>1156942034.77</v>
-      </c>
-      <c r="E95">
-        <v>16847</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B96" t="s">
-        <v>28</v>
-      </c>
-      <c r="C96">
-        <v>197.17737410000001</v>
-      </c>
-      <c r="D96">
-        <v>309110107.35000002</v>
-      </c>
-      <c r="E96">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B97" t="s">
-        <v>29</v>
-      </c>
-      <c r="C97">
-        <v>169.5712072</v>
-      </c>
-      <c r="D97">
-        <v>1504501508</v>
-      </c>
-      <c r="E97">
-        <v>2132</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B98" t="s">
-        <v>32</v>
-      </c>
-      <c r="C98">
-        <v>398.47251691000002</v>
-      </c>
-      <c r="D98">
-        <v>396705750.75</v>
-      </c>
-      <c r="E98">
-        <v>8860</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B99" t="s">
-        <v>33</v>
-      </c>
-      <c r="C99">
-        <v>219.630042</v>
-      </c>
-      <c r="D99">
-        <v>734812669.24000001</v>
-      </c>
-      <c r="E99">
-        <v>6997</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B100" t="s">
-        <v>34</v>
-      </c>
-      <c r="C100">
-        <v>229.2867</v>
-      </c>
-      <c r="D100">
-        <v>103939528.25</v>
-      </c>
-      <c r="E100">
-        <v>3972</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B101" t="s">
-        <v>35</v>
-      </c>
-      <c r="C101">
-        <v>236.33786749999999</v>
-      </c>
-      <c r="D101">
-        <v>125768006.2</v>
-      </c>
-      <c r="E101">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B102" t="s">
-        <v>40</v>
-      </c>
-      <c r="C102">
-        <v>108.20357921</v>
-      </c>
-      <c r="D102">
-        <v>164469440</v>
-      </c>
-      <c r="E102">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B103" t="s">
-        <v>22</v>
-      </c>
-      <c r="C103">
-        <v>169.89725994</v>
-      </c>
-      <c r="D103">
-        <v>2774755450.3899999</v>
-      </c>
-      <c r="E103">
-        <v>78693</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B104" t="s">
-        <v>23</v>
-      </c>
-      <c r="C104">
-        <v>207.59373528</v>
-      </c>
-      <c r="D104">
-        <v>927872648.64999998</v>
-      </c>
-      <c r="E104">
-        <v>7160</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B105" t="s">
-        <v>24</v>
-      </c>
-      <c r="C105">
-        <v>131.23363684</v>
-      </c>
-      <c r="D105">
-        <v>251796267.63</v>
-      </c>
-      <c r="E105">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B106" t="s">
-        <v>25</v>
-      </c>
-      <c r="C106">
-        <v>161.28463400000001</v>
-      </c>
-      <c r="D106">
-        <v>1187961385.03</v>
-      </c>
-      <c r="E106">
-        <v>12776</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B107" t="s">
-        <v>26</v>
-      </c>
-      <c r="C107">
-        <v>349.62951199999998</v>
-      </c>
-      <c r="D107">
-        <v>2707411558.3099999</v>
-      </c>
-      <c r="E107">
-        <v>37790</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B108" t="s">
-        <v>27</v>
-      </c>
-      <c r="C108">
-        <v>11.79905789</v>
-      </c>
-      <c r="D108">
-        <v>1148623015.5899999</v>
-      </c>
-      <c r="E108">
-        <v>16641</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B109" t="s">
-        <v>28</v>
-      </c>
-      <c r="C109">
-        <v>197.84052919999999</v>
-      </c>
-      <c r="D109">
-        <v>270640934.47000003</v>
-      </c>
-      <c r="E109">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B110" t="s">
-        <v>29</v>
-      </c>
-      <c r="C110">
-        <v>170.1964116</v>
-      </c>
-      <c r="D110">
-        <v>1402076867.8699999</v>
-      </c>
-      <c r="E110">
-        <v>2103</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B111" t="s">
-        <v>32</v>
-      </c>
-      <c r="C111">
-        <v>400.43885283999998</v>
-      </c>
-      <c r="D111">
-        <v>413932498.5</v>
-      </c>
-      <c r="E111">
-        <v>8911</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B112" t="s">
-        <v>33</v>
-      </c>
-      <c r="C112">
-        <v>220.76745099999999</v>
-      </c>
-      <c r="D112">
-        <v>761136369.88999999</v>
-      </c>
-      <c r="E112">
-        <v>7209</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B113" t="s">
-        <v>34</v>
-      </c>
-      <c r="C113">
-        <v>230.49469999999999</v>
-      </c>
-      <c r="D113">
-        <v>109662203.91</v>
-      </c>
-      <c r="E113">
-        <v>4140</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B114" t="s">
-        <v>35</v>
-      </c>
-      <c r="C114">
-        <v>237.84235090000001</v>
-      </c>
-      <c r="D114">
-        <v>127028257.98999999</v>
-      </c>
-      <c r="E114">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B115" t="s">
-        <v>40</v>
-      </c>
-      <c r="C115">
-        <v>109.71508005</v>
-      </c>
-      <c r="D115">
-        <v>167041209</v>
-      </c>
-      <c r="E115">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B116" t="s">
-        <v>22</v>
-      </c>
-      <c r="C116">
-        <v>170.46159245999999</v>
-      </c>
-      <c r="D116">
-        <v>2757505401.1999998</v>
-      </c>
-      <c r="E116">
-        <v>78091</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B117" t="s">
-        <v>23</v>
-      </c>
-      <c r="C117">
-        <v>208.31806234999999</v>
-      </c>
-      <c r="D117">
-        <v>918868055.85000002</v>
-      </c>
-      <c r="E117">
-        <v>7149</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B118" t="s">
-        <v>24</v>
-      </c>
-      <c r="C118">
-        <v>131.6919245</v>
-      </c>
-      <c r="D118">
-        <v>256864855.19</v>
-      </c>
-      <c r="E118">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B119" t="s">
-        <v>25</v>
-      </c>
-      <c r="C119">
-        <v>161.838584</v>
-      </c>
-      <c r="D119">
-        <v>1215687489.1700001</v>
-      </c>
-      <c r="E119">
-        <v>12994</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B120" t="s">
-        <v>26</v>
-      </c>
-      <c r="C120">
-        <v>350.75661400000001</v>
-      </c>
-      <c r="D120">
-        <v>2704117777.5900002</v>
-      </c>
-      <c r="E120">
-        <v>38857</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B121" t="s">
-        <v>27</v>
-      </c>
-      <c r="C121">
-        <v>11.838826660000001</v>
-      </c>
-      <c r="D121">
-        <v>1133807674.1700001</v>
-      </c>
-      <c r="E121">
-        <v>16495</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B122" t="s">
-        <v>28</v>
-      </c>
-      <c r="C122">
-        <v>198.572138</v>
-      </c>
-      <c r="D122">
-        <v>284653202.20999998</v>
-      </c>
-      <c r="E122">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B123" t="s">
-        <v>29</v>
-      </c>
-      <c r="C123">
-        <v>170.7741771</v>
-      </c>
-      <c r="D123">
-        <v>1440431627.4200001</v>
-      </c>
-      <c r="E123">
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B124" t="s">
-        <v>32</v>
-      </c>
-      <c r="C124">
-        <v>402.45125322000001</v>
-      </c>
-      <c r="D124">
-        <v>435072515.97000003</v>
-      </c>
-      <c r="E124">
-        <v>8934</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B125" t="s">
-        <v>33</v>
-      </c>
-      <c r="C125">
-        <v>221.85736299999999</v>
-      </c>
-      <c r="D125">
-        <v>798725071.94000006</v>
-      </c>
-      <c r="E125">
-        <v>7502</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B126" t="s">
-        <v>34</v>
-      </c>
-      <c r="C126">
-        <v>231.2962</v>
-      </c>
-      <c r="D126">
-        <v>113809087.08</v>
-      </c>
-      <c r="E126">
-        <v>4383</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B127" t="s">
-        <v>35</v>
-      </c>
-      <c r="C127">
-        <v>239.07441919999999</v>
-      </c>
-      <c r="D127">
-        <v>130310931.52</v>
-      </c>
-      <c r="E127">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B128" t="s">
-        <v>40</v>
-      </c>
-      <c r="C128">
-        <v>110.61604921999999</v>
-      </c>
-      <c r="D128">
-        <v>167859855</v>
-      </c>
-      <c r="E128">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B129" t="s">
-        <v>22</v>
-      </c>
-      <c r="C129">
-        <v>173.72934685999999</v>
-      </c>
-      <c r="D129">
-        <v>2755029376.04</v>
-      </c>
-      <c r="E129">
-        <v>76508</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B130" t="s">
-        <v>23</v>
-      </c>
-      <c r="C130">
-        <v>212.78308894</v>
-      </c>
-      <c r="D130">
-        <v>913729885.00999999</v>
-      </c>
-      <c r="E130">
-        <v>7226</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B131" t="s">
-        <v>24</v>
-      </c>
-      <c r="C131">
-        <v>134.35108005000001</v>
-      </c>
-      <c r="D131">
-        <v>294070137.10000002</v>
-      </c>
-      <c r="E131">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B132" t="s">
-        <v>25</v>
-      </c>
-      <c r="C132">
-        <v>165.161753</v>
-      </c>
-      <c r="D132">
-        <v>1273986251.6199999</v>
-      </c>
-      <c r="E132">
-        <v>13634</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A133" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B133" t="s">
-        <v>26</v>
-      </c>
-      <c r="C133">
-        <v>357.63221700000003</v>
-      </c>
-      <c r="D133">
-        <v>3155428348.3099999</v>
-      </c>
-      <c r="E133">
-        <v>44078</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A134" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B134" t="s">
-        <v>27</v>
-      </c>
-      <c r="C134">
-        <v>12.079791739999999</v>
-      </c>
-      <c r="D134">
-        <v>1239412685.3499999</v>
-      </c>
-      <c r="E134">
-        <v>16616</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B135" t="s">
-        <v>28</v>
-      </c>
-      <c r="C135">
-        <v>202.4793817</v>
-      </c>
-      <c r="D135">
-        <v>268981492.00999999</v>
-      </c>
-      <c r="E135">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A136" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B136" t="s">
-        <v>29</v>
-      </c>
-      <c r="C136">
-        <v>174.30474280000001</v>
-      </c>
-      <c r="D136">
-        <v>1415523875.99</v>
-      </c>
-      <c r="E136">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A137" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B137" t="s">
-        <v>32</v>
-      </c>
-      <c r="C137">
-        <v>410.65932354</v>
-      </c>
-      <c r="D137">
-        <v>461143127.45999998</v>
-      </c>
-      <c r="E137">
-        <v>8438</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B138" t="s">
-        <v>33</v>
-      </c>
-      <c r="C138">
-        <v>227.20659000000001</v>
-      </c>
-      <c r="D138">
-        <v>841428969.15999997</v>
-      </c>
-      <c r="E138">
-        <v>8102</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A139" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B139" t="s">
-        <v>34</v>
-      </c>
-      <c r="C139">
-        <v>235.39359999999999</v>
-      </c>
-      <c r="D139">
-        <v>104979969.55</v>
-      </c>
-      <c r="E139">
-        <v>4508</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B140" t="s">
-        <v>35</v>
-      </c>
-      <c r="C140">
-        <v>243.78792050000001</v>
-      </c>
-      <c r="D140">
-        <v>127233613.86</v>
-      </c>
-      <c r="E140">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A141" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B141" t="s">
-        <v>40</v>
-      </c>
-      <c r="C141">
-        <v>112.56613378999999</v>
-      </c>
-      <c r="D141">
-        <v>202337625.49000001</v>
-      </c>
-      <c r="E141">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A142" s="1">
-        <v>46234</v>
-      </c>
-      <c r="B142" t="s">
-        <v>22</v>
-      </c>
-      <c r="C142">
-        <v>174.31846501999999</v>
-      </c>
-      <c r="D142">
-        <v>2714460737.9899998</v>
-      </c>
-      <c r="E142">
-        <v>76158</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A143" s="1">
-        <v>46234</v>
-      </c>
-      <c r="B143" t="s">
-        <v>23</v>
-      </c>
-      <c r="C143">
-        <v>213.58180999000001</v>
-      </c>
-      <c r="D143">
-        <v>927883838.01999998</v>
-      </c>
-      <c r="E143">
-        <v>7251</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A144" s="1">
-        <v>46234</v>
-      </c>
-      <c r="B144" t="s">
-        <v>24</v>
-      </c>
-      <c r="C144">
-        <v>134.82905649</v>
-      </c>
-      <c r="D144">
-        <v>309635566.69</v>
-      </c>
-      <c r="E144">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" s="1">
-        <v>46234</v>
-      </c>
-      <c r="B145" t="s">
-        <v>25</v>
-      </c>
-      <c r="C145">
-        <v>165.67208099999999</v>
-      </c>
-      <c r="D145">
-        <v>1300155400.52</v>
-      </c>
-      <c r="E145">
-        <v>13863</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A146" s="1">
-        <v>46234</v>
-      </c>
-      <c r="B146" t="s">
-        <v>26</v>
-      </c>
-      <c r="C146">
-        <v>358.82808499999999</v>
-      </c>
-      <c r="D146">
-        <v>3281456302.8499999</v>
-      </c>
-      <c r="E146">
-        <v>44950</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A147" s="1">
-        <v>46234</v>
-      </c>
-      <c r="B147" t="s">
-        <v>27</v>
-      </c>
-      <c r="C147">
-        <v>12.122606530000001</v>
-      </c>
-      <c r="D147">
-        <v>1234798460.1099999</v>
-      </c>
-      <c r="E147">
-        <v>16736</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A148" s="1">
-        <v>46234</v>
-      </c>
-      <c r="B148" t="s">
-        <v>28</v>
-      </c>
-      <c r="C148">
-        <v>203.14380349999999</v>
-      </c>
-      <c r="D148">
-        <v>194957198.62</v>
-      </c>
-      <c r="E148">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A149" s="1">
-        <v>46234</v>
-      </c>
-      <c r="B149" t="s">
-        <v>29</v>
-      </c>
-      <c r="C149">
-        <v>174.92875620000001</v>
-      </c>
-      <c r="D149">
-        <v>1240583547.5899999</v>
-      </c>
-      <c r="E149">
-        <v>1987</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A150" s="1">
-        <v>46234</v>
-      </c>
-      <c r="B150" t="s">
-        <v>32</v>
-      </c>
-      <c r="C150">
-        <v>411.87582773999998</v>
-      </c>
-      <c r="D150">
-        <v>472879276.06</v>
-      </c>
-      <c r="E150">
-        <v>8522</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A151" s="1">
-        <v>46234</v>
-      </c>
-      <c r="B151" t="s">
-        <v>33</v>
-      </c>
-      <c r="C151">
-        <v>228.37178800000001</v>
-      </c>
-      <c r="D151">
-        <v>859777580.77999997</v>
-      </c>
-      <c r="E151">
-        <v>8250</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A152" s="1">
-        <v>46234</v>
-      </c>
-      <c r="B152" t="s">
-        <v>34</v>
-      </c>
-      <c r="C152">
-        <v>235.62559999999999</v>
-      </c>
-      <c r="D152">
-        <v>105017921.93000001</v>
-      </c>
-      <c r="E152">
-        <v>4553</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A153" s="1">
-        <v>46234</v>
-      </c>
-      <c r="B153" t="s">
-        <v>35</v>
-      </c>
-      <c r="C153">
-        <v>244.45138560000001</v>
-      </c>
-      <c r="D153">
-        <v>129245461.34999999</v>
-      </c>
-      <c r="E153">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A154" s="1">
-        <v>46234</v>
-      </c>
-      <c r="B154" t="s">
-        <v>40</v>
-      </c>
-      <c r="C154">
-        <v>113.10807698000001</v>
-      </c>
-      <c r="D154">
-        <v>152695903.91999999</v>
-      </c>
-      <c r="E154">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A155" s="1">
-        <v>46265</v>
-      </c>
-      <c r="B155" t="s">
-        <v>22</v>
-      </c>
-      <c r="C155">
-        <v>174.92760867999999</v>
-      </c>
-      <c r="D155">
-        <v>2696336296.1199999</v>
-      </c>
-      <c r="E155">
-        <v>75749</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A156" s="1">
-        <v>46265</v>
-      </c>
-      <c r="B156" t="s">
-        <v>23</v>
-      </c>
-      <c r="C156">
-        <v>214.56994126000001</v>
-      </c>
-      <c r="D156">
-        <v>926049973</v>
-      </c>
-      <c r="E156">
-        <v>7226</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A157" s="1">
-        <v>46265</v>
-      </c>
-      <c r="B157" t="s">
-        <v>24</v>
-      </c>
-      <c r="C157">
-        <v>135.32540791</v>
-      </c>
-      <c r="D157">
-        <v>326176641.60000002</v>
-      </c>
-      <c r="E157">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A158" s="1">
-        <v>46265</v>
-      </c>
-      <c r="B158" t="s">
-        <v>25</v>
-      </c>
-      <c r="C158">
-        <v>166.32631599999999</v>
-      </c>
-      <c r="D158">
-        <v>1330545100.6300001</v>
-      </c>
-      <c r="E158">
-        <v>13990</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A159" s="1">
-        <v>46265</v>
-      </c>
-      <c r="B159" t="s">
-        <v>26</v>
-      </c>
-      <c r="C159">
-        <v>360.02621199999999</v>
-      </c>
-      <c r="D159">
-        <v>3386119097.6900001</v>
-      </c>
-      <c r="E159">
-        <v>45517</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A160" s="1">
-        <v>46265</v>
-      </c>
-      <c r="B160" t="s">
-        <v>27</v>
-      </c>
-      <c r="C160">
-        <v>12.165339700000001</v>
-      </c>
-      <c r="D160">
-        <v>1247745597.73</v>
-      </c>
-      <c r="E160">
-        <v>16809</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A161" s="1">
-        <v>46265</v>
-      </c>
-      <c r="B161" t="s">
-        <v>28</v>
-      </c>
-      <c r="C161">
-        <v>203.8672832</v>
-      </c>
-      <c r="D161">
-        <v>184350138.22</v>
-      </c>
-      <c r="E161">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A162" s="1">
-        <v>46265</v>
-      </c>
-      <c r="B162" t="s">
-        <v>29</v>
-      </c>
-      <c r="C162">
-        <v>175.55553359999999</v>
-      </c>
-      <c r="D162">
-        <v>1372214285.01</v>
-      </c>
-      <c r="E162">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A163" s="1">
-        <v>46265</v>
-      </c>
-      <c r="B163" t="s">
-        <v>32</v>
-      </c>
-      <c r="C163">
-        <v>413.52704188000001</v>
-      </c>
-      <c r="D163">
-        <v>476906604.38999999</v>
-      </c>
-      <c r="E163">
-        <v>8499</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A164" s="1">
-        <v>46265</v>
-      </c>
-      <c r="B164" t="s">
-        <v>33</v>
-      </c>
-      <c r="C164">
-        <v>228.46783600000001</v>
-      </c>
-      <c r="D164">
-        <v>846675540.86000001</v>
-      </c>
-      <c r="E164">
-        <v>8334</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A165" s="1">
-        <v>46265</v>
-      </c>
-      <c r="B165" t="s">
-        <v>34</v>
-      </c>
-      <c r="C165">
-        <v>235.76259999999999</v>
-      </c>
-      <c r="D165">
-        <v>99791086.439999998</v>
-      </c>
-      <c r="E165">
-        <v>4511</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A166" s="1">
-        <v>46265</v>
-      </c>
-      <c r="B166" t="s">
-        <v>35</v>
-      </c>
-      <c r="C166">
-        <v>244.73786240000001</v>
-      </c>
-      <c r="D166">
-        <v>128349607.03</v>
-      </c>
-      <c r="E166">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A167" s="1">
-        <v>46265</v>
-      </c>
-      <c r="B167" t="s">
-        <v>40</v>
-      </c>
-      <c r="C167">
-        <v>112.50574435</v>
-      </c>
-      <c r="D167">
-        <v>152164019.24000001</v>
-      </c>
-      <c r="E167">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A168" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B168" t="s">
-        <v>22</v>
-      </c>
-      <c r="C168">
-        <v>175.50838275999999</v>
-      </c>
-      <c r="D168">
-        <v>2705529159.8099999</v>
-      </c>
-      <c r="E168">
-        <v>75292</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A169" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B169" t="s">
-        <v>23</v>
-      </c>
-      <c r="C169">
-        <v>214.47442111000001</v>
-      </c>
-      <c r="D169">
-        <v>917635044.80999994</v>
-      </c>
-      <c r="E169">
-        <v>7147</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A170" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B170" t="s">
-        <v>24</v>
-      </c>
-      <c r="C170">
-        <v>135.79414928</v>
-      </c>
-      <c r="D170">
-        <v>359423998.38</v>
-      </c>
-      <c r="E170">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A171" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B171" t="s">
-        <v>25</v>
-      </c>
-      <c r="C171">
-        <v>166.12638113</v>
-      </c>
-      <c r="D171">
-        <v>1320047031.1900001</v>
-      </c>
-      <c r="E171">
-        <v>13880</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A172" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B172" t="s">
-        <v>26</v>
-      </c>
-      <c r="C172">
-        <v>361.10296736999999</v>
-      </c>
-      <c r="D172">
-        <v>3358169486.3899999</v>
-      </c>
-      <c r="E172">
-        <v>45627</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A173" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B173" t="s">
-        <v>27</v>
-      </c>
-      <c r="C173">
-        <v>12.203462500000001</v>
-      </c>
-      <c r="D173">
-        <v>1253304551.1400001</v>
-      </c>
-      <c r="E173">
-        <v>16925</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A174" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B174" t="s">
-        <v>28</v>
-      </c>
-      <c r="C174">
-        <v>203.7424178</v>
-      </c>
-      <c r="D174">
-        <v>186504024.28999999</v>
-      </c>
-      <c r="E174">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A175" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B175" t="s">
-        <v>29</v>
-      </c>
-      <c r="C175">
-        <v>176.1565659</v>
-      </c>
-      <c r="D175">
-        <v>1543437489.8199999</v>
-      </c>
-      <c r="E175">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A176" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B176" t="s">
-        <v>32</v>
-      </c>
-      <c r="C176">
-        <v>409.07142088000001</v>
-      </c>
-      <c r="D176">
-        <v>445717202.87</v>
-      </c>
-      <c r="E176">
-        <v>8243</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A177" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B177" t="s">
-        <v>33</v>
-      </c>
-      <c r="C177">
-        <v>226.09731866999999</v>
-      </c>
-      <c r="D177">
-        <v>783883688.35000002</v>
-      </c>
-      <c r="E177">
-        <v>8119</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A178" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B178" t="s">
-        <v>34</v>
-      </c>
-      <c r="C178">
-        <v>233.64169999999999</v>
-      </c>
-      <c r="D178">
-        <v>91765003.560000002</v>
-      </c>
-      <c r="E178">
-        <v>4360</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A179" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B179" t="s">
-        <v>35</v>
-      </c>
-      <c r="C179">
-        <v>242.900756</v>
-      </c>
-      <c r="D179">
-        <v>120721586.34</v>
-      </c>
-      <c r="E179">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A180" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B180" t="s">
-        <v>40</v>
-      </c>
-      <c r="C180">
-        <v>110.04027514086383</v>
-      </c>
-      <c r="D180">
-        <v>148829472.12801832</v>
-      </c>
-      <c r="E180">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A181" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B181" t="s">
-        <v>22</v>
-      </c>
-      <c r="C181">
-        <v>175.68375476</v>
-      </c>
-      <c r="D181">
-        <v>2705748233.4099998</v>
-      </c>
-      <c r="E181">
-        <v>75164</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A182" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B182" t="s">
-        <v>23</v>
-      </c>
-      <c r="C182">
-        <v>214.81611819</v>
-      </c>
-      <c r="D182">
-        <v>897019568.54999995</v>
-      </c>
-      <c r="E182">
-        <v>7069</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A183" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B183" t="s">
-        <v>24</v>
-      </c>
-      <c r="C183">
-        <v>135.93525915000001</v>
-      </c>
-      <c r="D183">
-        <v>385465944.74000001</v>
-      </c>
-      <c r="E183">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A184" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B184" t="s">
-        <v>25</v>
-      </c>
-      <c r="C184">
-        <v>166.41805854</v>
-      </c>
-      <c r="D184">
-        <v>1317793069.1300001</v>
-      </c>
-      <c r="E184">
-        <v>13802</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A185" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B185" t="s">
-        <v>26</v>
-      </c>
-      <c r="C185">
-        <v>361.46004819000001</v>
-      </c>
-      <c r="D185">
-        <v>3451869354.6100001</v>
-      </c>
-      <c r="E185">
-        <v>45759</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A186" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B186" t="s">
-        <v>27</v>
-      </c>
-      <c r="C186">
-        <v>12.21523575</v>
-      </c>
-      <c r="D186">
-        <v>1249435239.9400001</v>
-      </c>
-      <c r="E186">
-        <v>16986</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A187" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B187" t="s">
-        <v>28</v>
-      </c>
-      <c r="C187">
-        <v>204.02861960000001</v>
-      </c>
-      <c r="D187">
-        <v>194753456.19999999</v>
-      </c>
-      <c r="E187">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A188" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B188" t="s">
-        <v>29</v>
-      </c>
-      <c r="C188">
+      <c r="B31" s="18">
         <v>176.33114180000001</v>
       </c>
-      <c r="D188">
+      <c r="C31" s="18">
         <v>1666496529.3</v>
       </c>
-      <c r="E188">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A189" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B189" t="s">
-        <v>32</v>
-      </c>
-      <c r="C189">
-        <v>410.30980470999998</v>
-      </c>
-      <c r="D189">
-        <v>435373898.41000003</v>
-      </c>
-      <c r="E189">
-        <v>8142</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A190" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B190" t="s">
-        <v>33</v>
-      </c>
-      <c r="C190">
-        <v>226.63490805999999</v>
-      </c>
-      <c r="D190">
-        <v>768176827.78999996</v>
-      </c>
-      <c r="E190">
-        <v>8043</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A191" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B191" t="s">
-        <v>34</v>
-      </c>
-      <c r="C191">
-        <v>234.13839999999999</v>
-      </c>
-      <c r="D191">
-        <v>87314060.650000006</v>
-      </c>
-      <c r="E191">
-        <v>4305</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A192" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B192" t="s">
-        <v>35</v>
-      </c>
-      <c r="C192">
-        <v>243.4637008</v>
-      </c>
-      <c r="D192">
-        <v>118502088.41</v>
-      </c>
-      <c r="E192">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A193" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B193" t="s">
-        <v>40</v>
-      </c>
-      <c r="C193">
-        <v>110.882600109728</v>
-      </c>
-      <c r="D193">
-        <v>149414303.64785901</v>
-      </c>
-      <c r="E193">
-        <v>547</v>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="B32" s="18">
+        <v>5252.1667370097275</v>
+      </c>
+      <c r="C32" s="18">
+        <v>26058341695.627857</v>
+      </c>
+    </row>
+    <row r="33" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N33" s="20">
+        <f>M26*(1-30%)</f>
+        <v>2.7217259033650899E-2</v>
       </c>
     </row>
   </sheetData>
@@ -5264,6 +4349,3509 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E90F8A8D-E010-4622-BBF4-8117B763A2FF}">
+  <dimension ref="A1:E206"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>44926</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2">
+        <v>144.59971811</v>
+      </c>
+      <c r="D2">
+        <v>1780595701.9300001</v>
+      </c>
+      <c r="E2">
+        <v>71633</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>44926</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3">
+        <v>173.71720182000001</v>
+      </c>
+      <c r="D3">
+        <v>235607692.11000001</v>
+      </c>
+      <c r="E3">
+        <v>6188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>44926</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>111.44877950999999</v>
+      </c>
+      <c r="D4">
+        <v>164874402.99000001</v>
+      </c>
+      <c r="E4">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>44926</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>135.21020648000001</v>
+      </c>
+      <c r="D5">
+        <v>476767647.56</v>
+      </c>
+      <c r="E5">
+        <v>10418</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>44926</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>296.69448505000003</v>
+      </c>
+      <c r="D6">
+        <v>1497806644.1800001</v>
+      </c>
+      <c r="E6">
+        <v>28520</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>44926</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>44926</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>167.8219181</v>
+      </c>
+      <c r="D8">
+        <v>181420233.74000001</v>
+      </c>
+      <c r="E8">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>44926</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9">
+        <v>144.00388140000001</v>
+      </c>
+      <c r="D9">
+        <v>573137696.12</v>
+      </c>
+      <c r="E9">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>44926</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>317.5136152</v>
+      </c>
+      <c r="D10">
+        <v>75204728.650000006</v>
+      </c>
+      <c r="E10">
+        <v>4096</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>44926</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11">
+        <v>177.00756683</v>
+      </c>
+      <c r="D11">
+        <v>329107281.64999998</v>
+      </c>
+      <c r="E11">
+        <v>5181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>44926</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12">
+        <v>186.83269999999999</v>
+      </c>
+      <c r="D12">
+        <v>52576790.329999998</v>
+      </c>
+      <c r="E12">
+        <v>3251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>44926</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13">
+        <v>195.25890920000001</v>
+      </c>
+      <c r="D13">
+        <v>47421040.450000003</v>
+      </c>
+      <c r="E13">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>45291</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14">
+        <v>155.05096872999999</v>
+      </c>
+      <c r="D14">
+        <v>1757718562.8199999</v>
+      </c>
+      <c r="E14">
+        <v>67700</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>45291</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15">
+        <v>187.24948190999999</v>
+      </c>
+      <c r="D15">
+        <v>223875481.59999999</v>
+      </c>
+      <c r="E15">
+        <v>4845</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>45291</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16">
+        <v>119.44997167</v>
+      </c>
+      <c r="D16">
+        <v>87141002.849999994</v>
+      </c>
+      <c r="E16">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>45291</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17">
+        <v>145.55334999999999</v>
+      </c>
+      <c r="D17">
+        <v>477245700.51999998</v>
+      </c>
+      <c r="E17">
+        <v>10554</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>45291</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18">
+        <v>318.38266599999997</v>
+      </c>
+      <c r="D18">
+        <v>1640067045.1600001</v>
+      </c>
+      <c r="E18">
+        <v>30709</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>45291</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19">
+        <v>10.79655926</v>
+      </c>
+      <c r="D19">
+        <v>722718733.80999994</v>
+      </c>
+      <c r="E19">
+        <v>6888</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>45291</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20">
+        <v>179.23148420000001</v>
+      </c>
+      <c r="D20">
+        <v>75646215.840000004</v>
+      </c>
+      <c r="E20">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>45291</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21">
+        <v>154.70245499999999</v>
+      </c>
+      <c r="D21">
+        <v>921797638.79999995</v>
+      </c>
+      <c r="E21">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>45291</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22">
+        <v>350.77003454999999</v>
+      </c>
+      <c r="D22">
+        <v>113231072.78</v>
+      </c>
+      <c r="E22">
+        <v>4407</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>45291</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23">
+        <v>193.46580499999999</v>
+      </c>
+      <c r="D23">
+        <v>322695223.30000001</v>
+      </c>
+      <c r="E23">
+        <v>4544</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>45291</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24">
+        <v>204.38290000000001</v>
+      </c>
+      <c r="D24">
+        <v>48272534.020000003</v>
+      </c>
+      <c r="E24">
+        <v>3225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>45291</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25">
+        <v>210.82617690000001</v>
+      </c>
+      <c r="D25">
+        <v>62212656.939999998</v>
+      </c>
+      <c r="E25">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26">
+        <v>163.61348584999999</v>
+      </c>
+      <c r="D26">
+        <v>2785813379.1700001</v>
+      </c>
+      <c r="E26">
+        <v>75933</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27">
+        <v>197.93033137</v>
+      </c>
+      <c r="D27">
+        <v>487072861.54000002</v>
+      </c>
+      <c r="E27">
+        <v>5732</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28">
+        <v>126.22174136</v>
+      </c>
+      <c r="D28">
+        <v>291604962.11000001</v>
+      </c>
+      <c r="E28">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29">
+        <v>154.47121799999999</v>
+      </c>
+      <c r="D29">
+        <v>876778097.27999997</v>
+      </c>
+      <c r="E29">
+        <v>11126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30">
+        <v>336.16375499999998</v>
+      </c>
+      <c r="D30">
+        <v>2262660758.9099998</v>
+      </c>
+      <c r="E30">
+        <v>33259</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31">
+        <v>11.34850312</v>
+      </c>
+      <c r="D31">
+        <v>1199414211.3900001</v>
+      </c>
+      <c r="E31">
+        <v>15968</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32">
+        <v>190.13847939999999</v>
+      </c>
+      <c r="D32">
+        <v>229196493.75999999</v>
+      </c>
+      <c r="E32">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33">
+        <v>163.48415209999999</v>
+      </c>
+      <c r="D33">
+        <v>1563120388.29</v>
+      </c>
+      <c r="E33">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34">
+        <v>372.77834658</v>
+      </c>
+      <c r="D34">
+        <v>236985701.34999999</v>
+      </c>
+      <c r="E34">
+        <v>6808</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35">
+        <v>207.68079700000001</v>
+      </c>
+      <c r="D35">
+        <v>476508901.11000001</v>
+      </c>
+      <c r="E35">
+        <v>5366</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36">
+        <v>217.68049999999999</v>
+      </c>
+      <c r="D36">
+        <v>59979894.689999998</v>
+      </c>
+      <c r="E36">
+        <v>3421</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>45657</v>
+      </c>
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37">
+        <v>224.39302129999999</v>
+      </c>
+      <c r="D37">
+        <v>109615940.83</v>
+      </c>
+      <c r="E37">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38">
+        <v>167.07511972</v>
+      </c>
+      <c r="D38">
+        <v>3102255970.8000002</v>
+      </c>
+      <c r="E38">
+        <v>80880</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39">
+        <v>203.39865723</v>
+      </c>
+      <c r="D39">
+        <v>713327723.94000006</v>
+      </c>
+      <c r="E39">
+        <v>6867</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B40" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40">
+        <v>128.97037555</v>
+      </c>
+      <c r="D40">
+        <v>298446011.36000001</v>
+      </c>
+      <c r="E40">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41">
+        <v>158.32547199999999</v>
+      </c>
+      <c r="D41">
+        <v>1001694254.91</v>
+      </c>
+      <c r="E41">
+        <v>11741</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42">
+        <v>343.86480699999998</v>
+      </c>
+      <c r="D42">
+        <v>2766838110.2399998</v>
+      </c>
+      <c r="E42">
+        <v>35316</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43">
+        <v>11.597048770000001</v>
+      </c>
+      <c r="D43">
+        <v>1266987358.23</v>
+      </c>
+      <c r="E43">
+        <v>17865</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B44" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44">
+        <v>194.37889050000001</v>
+      </c>
+      <c r="D44">
+        <v>210800593.33000001</v>
+      </c>
+      <c r="E44">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45">
+        <v>167.17190740000001</v>
+      </c>
+      <c r="D45">
+        <v>1345605629.5799999</v>
+      </c>
+      <c r="E45">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46">
+        <v>387.61274229999998</v>
+      </c>
+      <c r="D46">
+        <v>301355442.52999997</v>
+      </c>
+      <c r="E46">
+        <v>8012</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47">
+        <v>215.27327199999999</v>
+      </c>
+      <c r="D47">
+        <v>614074843.98000002</v>
+      </c>
+      <c r="E47">
+        <v>6226</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48">
+        <v>224.72149999999999</v>
+      </c>
+      <c r="D48">
+        <v>76367739.25</v>
+      </c>
+      <c r="E48">
+        <v>3607</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B49" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49">
+        <v>231.62023500000001</v>
+      </c>
+      <c r="D49">
+        <v>108659193.23</v>
+      </c>
+      <c r="E49">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50">
+        <v>104.077</v>
+      </c>
+      <c r="D50">
+        <v>160538836</v>
+      </c>
+      <c r="E50">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51">
+        <v>167.64956842999999</v>
+      </c>
+      <c r="D51">
+        <v>3078642149.5</v>
+      </c>
+      <c r="E51">
+        <v>81044</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B52" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52">
+        <v>204.37856231999999</v>
+      </c>
+      <c r="D52">
+        <v>799486379.04999995</v>
+      </c>
+      <c r="E52">
+        <v>7016</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B53" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53">
+        <v>129.42988886000001</v>
+      </c>
+      <c r="D53">
+        <v>294789962.27999997</v>
+      </c>
+      <c r="E53">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B54" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54">
+        <v>158.988519</v>
+      </c>
+      <c r="D54">
+        <v>1031033582.17</v>
+      </c>
+      <c r="E54">
+        <v>11947</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55">
+        <v>345.110997</v>
+      </c>
+      <c r="D55">
+        <v>2536105970.04</v>
+      </c>
+      <c r="E55">
+        <v>35699</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B56" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56">
+        <v>11.63921322</v>
+      </c>
+      <c r="D56">
+        <v>1251580814.6700001</v>
+      </c>
+      <c r="E56">
+        <v>17766</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57">
+        <v>195.18316189999999</v>
+      </c>
+      <c r="D57">
+        <v>229817708.03</v>
+      </c>
+      <c r="E57">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B58" t="s">
+        <v>29</v>
+      </c>
+      <c r="C58">
+        <v>167.79395239999999</v>
+      </c>
+      <c r="D58">
+        <v>1396545851.9300001</v>
+      </c>
+      <c r="E58">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B59" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59">
+        <v>390.59586528</v>
+      </c>
+      <c r="D59">
+        <v>320206500.63999999</v>
+      </c>
+      <c r="E59">
+        <v>8295</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B60" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60">
+        <v>216.53612899999999</v>
+      </c>
+      <c r="D60">
+        <v>646898858.19000006</v>
+      </c>
+      <c r="E60">
+        <v>6459</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B61" t="s">
+        <v>34</v>
+      </c>
+      <c r="C61">
+        <v>225.9716</v>
+      </c>
+      <c r="D61">
+        <v>85025969.689999998</v>
+      </c>
+      <c r="E61">
+        <v>3704</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B62" t="s">
+        <v>35</v>
+      </c>
+      <c r="C62">
+        <v>232.6416213</v>
+      </c>
+      <c r="D62">
+        <v>112822044.2</v>
+      </c>
+      <c r="E62">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B63" t="s">
+        <v>40</v>
+      </c>
+      <c r="C63">
+        <v>104.78189999999999</v>
+      </c>
+      <c r="D63">
+        <v>161626065.99000001</v>
+      </c>
+      <c r="E63">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B64" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64">
+        <v>168.23558263000001</v>
+      </c>
+      <c r="D64">
+        <v>3015298835.8299999</v>
+      </c>
+      <c r="E64">
+        <v>80761</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B65" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65">
+        <v>205.39002556</v>
+      </c>
+      <c r="D65">
+        <v>897991417.98000002</v>
+      </c>
+      <c r="E65">
+        <v>7099</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66">
+        <v>129.88868518000001</v>
+      </c>
+      <c r="D66">
+        <v>301790271.91000003</v>
+      </c>
+      <c r="E66">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B67" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67">
+        <v>159.74084300000001</v>
+      </c>
+      <c r="D67">
+        <v>1076884783.3499999</v>
+      </c>
+      <c r="E67">
+        <v>12131</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68">
+        <v>346.30228299999999</v>
+      </c>
+      <c r="D68">
+        <v>2617465131.8000002</v>
+      </c>
+      <c r="E68">
+        <v>35775</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B69" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69">
+        <v>11.681476330000001</v>
+      </c>
+      <c r="D69">
+        <v>1217600708.01</v>
+      </c>
+      <c r="E69">
+        <v>17560</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B70" t="s">
+        <v>28</v>
+      </c>
+      <c r="C70">
+        <v>195.87096030000001</v>
+      </c>
+      <c r="D70">
+        <v>277996661.42000002</v>
+      </c>
+      <c r="E70">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B71" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71">
+        <v>168.4135532</v>
+      </c>
+      <c r="D71">
+        <v>1473308890.9300001</v>
+      </c>
+      <c r="E71">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B72" t="s">
+        <v>32</v>
+      </c>
+      <c r="C72">
+        <v>393.76626654</v>
+      </c>
+      <c r="D72">
+        <v>349904163.51999998</v>
+      </c>
+      <c r="E72">
+        <v>8460</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73">
+        <v>217.83012500000001</v>
+      </c>
+      <c r="D73">
+        <v>676057856.75999999</v>
+      </c>
+      <c r="E73">
+        <v>6674</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C74">
+        <v>227.23140000000001</v>
+      </c>
+      <c r="D74">
+        <v>91608131.040000007</v>
+      </c>
+      <c r="E74">
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B75" t="s">
+        <v>35</v>
+      </c>
+      <c r="C75">
+        <v>234.08105040000001</v>
+      </c>
+      <c r="D75">
+        <v>119077037.17</v>
+      </c>
+      <c r="E75">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>45900</v>
+      </c>
+      <c r="B76" t="s">
+        <v>40</v>
+      </c>
+      <c r="C76">
+        <v>105.94927979000001</v>
+      </c>
+      <c r="D76">
+        <v>138263810.13</v>
+      </c>
+      <c r="E76">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77">
+        <v>168.79042254999999</v>
+      </c>
+      <c r="D77">
+        <v>2918602637.7800002</v>
+      </c>
+      <c r="E77">
+        <v>80189</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B78" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78">
+        <v>206.33787049</v>
+      </c>
+      <c r="D78">
+        <v>916202232.72000003</v>
+      </c>
+      <c r="E78">
+        <v>7193</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B79" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79">
+        <v>130.33427861000001</v>
+      </c>
+      <c r="D79">
+        <v>271823785.62</v>
+      </c>
+      <c r="E79">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B80" t="s">
+        <v>25</v>
+      </c>
+      <c r="C80">
+        <v>160.29543200000001</v>
+      </c>
+      <c r="D80">
+        <v>1186789207.8</v>
+      </c>
+      <c r="E80">
+        <v>12368</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81">
+        <v>347.43418400000002</v>
+      </c>
+      <c r="D81">
+        <v>2712754224.9499998</v>
+      </c>
+      <c r="E81">
+        <v>36031</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B82" t="s">
+        <v>27</v>
+      </c>
+      <c r="C82">
+        <v>11.72061527</v>
+      </c>
+      <c r="D82">
+        <v>1201267646.29</v>
+      </c>
+      <c r="E82">
+        <v>17223</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B83" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83">
+        <v>196.5501486</v>
+      </c>
+      <c r="D83">
+        <v>330152510.06999999</v>
+      </c>
+      <c r="E83">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B84" t="s">
+        <v>29</v>
+      </c>
+      <c r="C84">
+        <v>169.00409590000001</v>
+      </c>
+      <c r="D84">
+        <v>1416869051.3599999</v>
+      </c>
+      <c r="E84">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B85" t="s">
+        <v>32</v>
+      </c>
+      <c r="C85">
+        <v>397.25437890000001</v>
+      </c>
+      <c r="D85">
+        <v>379870300.24000001</v>
+      </c>
+      <c r="E85">
+        <v>8738</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B86" t="s">
+        <v>33</v>
+      </c>
+      <c r="C86">
+        <v>219.155531</v>
+      </c>
+      <c r="D86">
+        <v>712552235.21000004</v>
+      </c>
+      <c r="E86">
+        <v>6856</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B87" t="s">
+        <v>34</v>
+      </c>
+      <c r="C87">
+        <v>228.79310000000001</v>
+      </c>
+      <c r="D87">
+        <v>97265531.599999994</v>
+      </c>
+      <c r="E87">
+        <v>3924</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B88" t="s">
+        <v>35</v>
+      </c>
+      <c r="C88">
+        <v>235.7956131</v>
+      </c>
+      <c r="D88">
+        <v>124571303.27</v>
+      </c>
+      <c r="E88">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>45930</v>
+      </c>
+      <c r="B89" t="s">
+        <v>40</v>
+      </c>
+      <c r="C89">
+        <v>107.84736325999999</v>
+      </c>
+      <c r="D89">
+        <v>163658374</v>
+      </c>
+      <c r="E89">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B90" t="s">
+        <v>22</v>
+      </c>
+      <c r="C90">
+        <v>168.95558728</v>
+      </c>
+      <c r="D90">
+        <v>2928603624.1599998</v>
+      </c>
+      <c r="E90">
+        <v>80015</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B91" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91">
+        <v>206.46415440999999</v>
+      </c>
+      <c r="D91">
+        <v>964581522.33000004</v>
+      </c>
+      <c r="E91">
+        <v>7202</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B92" t="s">
+        <v>24</v>
+      </c>
+      <c r="C92">
+        <v>130.46580786999999</v>
+      </c>
+      <c r="D92">
+        <v>293106174.69999999</v>
+      </c>
+      <c r="E92">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B93" t="s">
+        <v>25</v>
+      </c>
+      <c r="C93">
+        <v>160.45289</v>
+      </c>
+      <c r="D93">
+        <v>1210142183.6500001</v>
+      </c>
+      <c r="E93">
+        <v>12450</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94">
+        <v>347.74867799999998</v>
+      </c>
+      <c r="D94">
+        <v>2695835758.3099999</v>
+      </c>
+      <c r="E94">
+        <v>36224</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B95" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95">
+        <v>11.731005850000001</v>
+      </c>
+      <c r="D95">
+        <v>1196654662</v>
+      </c>
+      <c r="E95">
+        <v>17096</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B96" t="s">
+        <v>28</v>
+      </c>
+      <c r="C96">
+        <v>196.71769019999999</v>
+      </c>
+      <c r="D96">
+        <v>325599215.44</v>
+      </c>
+      <c r="E96">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B97" t="s">
+        <v>29</v>
+      </c>
+      <c r="C97">
+        <v>169.17041</v>
+      </c>
+      <c r="D97">
+        <v>1561263617.4000001</v>
+      </c>
+      <c r="E97">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B98" t="s">
+        <v>32</v>
+      </c>
+      <c r="C98">
+        <v>396.93344365000002</v>
+      </c>
+      <c r="D98">
+        <v>386918774.95999998</v>
+      </c>
+      <c r="E98">
+        <v>8808</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B99" t="s">
+        <v>33</v>
+      </c>
+      <c r="C99">
+        <v>218.864071</v>
+      </c>
+      <c r="D99">
+        <v>727217160.51999998</v>
+      </c>
+      <c r="E99">
+        <v>6888</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B100" t="s">
+        <v>34</v>
+      </c>
+      <c r="C100">
+        <v>228.6627</v>
+      </c>
+      <c r="D100">
+        <v>101949300.45</v>
+      </c>
+      <c r="E100">
+        <v>3939</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B101" t="s">
+        <v>35</v>
+      </c>
+      <c r="C101">
+        <v>235.78312320000001</v>
+      </c>
+      <c r="D101">
+        <v>125273127.11</v>
+      </c>
+      <c r="E101">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>45939</v>
+      </c>
+      <c r="B102" t="s">
+        <v>40</v>
+      </c>
+      <c r="C102">
+        <v>107.89952589000001</v>
+      </c>
+      <c r="D102">
+        <v>113833999.81</v>
+      </c>
+      <c r="E102">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B103" t="s">
+        <v>22</v>
+      </c>
+      <c r="C103">
+        <v>169.34801067999999</v>
+      </c>
+      <c r="D103">
+        <v>2881515647.71</v>
+      </c>
+      <c r="E103">
+        <v>79413</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B104" t="s">
+        <v>23</v>
+      </c>
+      <c r="C104">
+        <v>206.89603886</v>
+      </c>
+      <c r="D104">
+        <v>972485492.37</v>
+      </c>
+      <c r="E104">
+        <v>7201</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B105" t="s">
+        <v>24</v>
+      </c>
+      <c r="C105">
+        <v>130.78976039</v>
+      </c>
+      <c r="D105">
+        <v>256081799.15000001</v>
+      </c>
+      <c r="E105">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B106" t="s">
+        <v>25</v>
+      </c>
+      <c r="C106">
+        <v>160.68935400000001</v>
+      </c>
+      <c r="D106">
+        <v>1188379776.6099999</v>
+      </c>
+      <c r="E106">
+        <v>12553</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B107" t="s">
+        <v>26</v>
+      </c>
+      <c r="C107">
+        <v>348.520308</v>
+      </c>
+      <c r="D107">
+        <v>2661416365.75</v>
+      </c>
+      <c r="E107">
+        <v>36809</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B108" t="s">
+        <v>27</v>
+      </c>
+      <c r="C108">
+        <v>11.75824705</v>
+      </c>
+      <c r="D108">
+        <v>1156942034.77</v>
+      </c>
+      <c r="E108">
+        <v>16847</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B109" t="s">
+        <v>28</v>
+      </c>
+      <c r="C109">
+        <v>197.17737410000001</v>
+      </c>
+      <c r="D109">
+        <v>309110107.35000002</v>
+      </c>
+      <c r="E109">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B110" t="s">
+        <v>29</v>
+      </c>
+      <c r="C110">
+        <v>169.5712072</v>
+      </c>
+      <c r="D110">
+        <v>1504501508</v>
+      </c>
+      <c r="E110">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B111" t="s">
+        <v>32</v>
+      </c>
+      <c r="C111">
+        <v>398.47251691000002</v>
+      </c>
+      <c r="D111">
+        <v>396705750.75</v>
+      </c>
+      <c r="E111">
+        <v>8860</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B112" t="s">
+        <v>33</v>
+      </c>
+      <c r="C112">
+        <v>219.630042</v>
+      </c>
+      <c r="D112">
+        <v>734812669.24000001</v>
+      </c>
+      <c r="E112">
+        <v>6997</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B113" t="s">
+        <v>34</v>
+      </c>
+      <c r="C113">
+        <v>229.2867</v>
+      </c>
+      <c r="D113">
+        <v>103939528.25</v>
+      </c>
+      <c r="E113">
+        <v>3972</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B114" t="s">
+        <v>35</v>
+      </c>
+      <c r="C114">
+        <v>236.33786749999999</v>
+      </c>
+      <c r="D114">
+        <v>125768006.2</v>
+      </c>
+      <c r="E114">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>45961</v>
+      </c>
+      <c r="B115" t="s">
+        <v>40</v>
+      </c>
+      <c r="C115">
+        <v>108.20357921</v>
+      </c>
+      <c r="D115">
+        <v>164469440</v>
+      </c>
+      <c r="E115">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B116" t="s">
+        <v>22</v>
+      </c>
+      <c r="C116">
+        <v>169.89725994</v>
+      </c>
+      <c r="D116">
+        <v>2774755450.3899999</v>
+      </c>
+      <c r="E116">
+        <v>78693</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B117" t="s">
+        <v>23</v>
+      </c>
+      <c r="C117">
+        <v>207.59373528</v>
+      </c>
+      <c r="D117">
+        <v>927872648.64999998</v>
+      </c>
+      <c r="E117">
+        <v>7160</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B118" t="s">
+        <v>24</v>
+      </c>
+      <c r="C118">
+        <v>131.23363684</v>
+      </c>
+      <c r="D118">
+        <v>251796267.63</v>
+      </c>
+      <c r="E118">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B119" t="s">
+        <v>25</v>
+      </c>
+      <c r="C119">
+        <v>161.28463400000001</v>
+      </c>
+      <c r="D119">
+        <v>1187961385.03</v>
+      </c>
+      <c r="E119">
+        <v>12776</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B120" t="s">
+        <v>26</v>
+      </c>
+      <c r="C120">
+        <v>349.62951199999998</v>
+      </c>
+      <c r="D120">
+        <v>2707411558.3099999</v>
+      </c>
+      <c r="E120">
+        <v>37790</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B121" t="s">
+        <v>27</v>
+      </c>
+      <c r="C121">
+        <v>11.79905789</v>
+      </c>
+      <c r="D121">
+        <v>1148623015.5899999</v>
+      </c>
+      <c r="E121">
+        <v>16641</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B122" t="s">
+        <v>28</v>
+      </c>
+      <c r="C122">
+        <v>197.84052919999999</v>
+      </c>
+      <c r="D122">
+        <v>270640934.47000003</v>
+      </c>
+      <c r="E122">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C123">
+        <v>170.1964116</v>
+      </c>
+      <c r="D123">
+        <v>1402076867.8699999</v>
+      </c>
+      <c r="E123">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B124" t="s">
+        <v>32</v>
+      </c>
+      <c r="C124">
+        <v>400.43885283999998</v>
+      </c>
+      <c r="D124">
+        <v>413932498.5</v>
+      </c>
+      <c r="E124">
+        <v>8911</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B125" t="s">
+        <v>33</v>
+      </c>
+      <c r="C125">
+        <v>220.76745099999999</v>
+      </c>
+      <c r="D125">
+        <v>761136369.88999999</v>
+      </c>
+      <c r="E125">
+        <v>7209</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B126" t="s">
+        <v>34</v>
+      </c>
+      <c r="C126">
+        <v>230.49469999999999</v>
+      </c>
+      <c r="D126">
+        <v>109662203.91</v>
+      </c>
+      <c r="E126">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B127" t="s">
+        <v>35</v>
+      </c>
+      <c r="C127">
+        <v>237.84235090000001</v>
+      </c>
+      <c r="D127">
+        <v>127028257.98999999</v>
+      </c>
+      <c r="E127">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B128" t="s">
+        <v>40</v>
+      </c>
+      <c r="C128">
+        <v>109.71508005</v>
+      </c>
+      <c r="D128">
+        <v>167041209</v>
+      </c>
+      <c r="E128">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B129" t="s">
+        <v>22</v>
+      </c>
+      <c r="C129">
+        <v>170.46159245999999</v>
+      </c>
+      <c r="D129">
+        <v>2757505401.1999998</v>
+      </c>
+      <c r="E129">
+        <v>78091</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B130" t="s">
+        <v>23</v>
+      </c>
+      <c r="C130">
+        <v>208.31806234999999</v>
+      </c>
+      <c r="D130">
+        <v>918868055.85000002</v>
+      </c>
+      <c r="E130">
+        <v>7149</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B131" t="s">
+        <v>24</v>
+      </c>
+      <c r="C131">
+        <v>131.6919245</v>
+      </c>
+      <c r="D131">
+        <v>256864855.19</v>
+      </c>
+      <c r="E131">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B132" t="s">
+        <v>25</v>
+      </c>
+      <c r="C132">
+        <v>161.838584</v>
+      </c>
+      <c r="D132">
+        <v>1215687489.1700001</v>
+      </c>
+      <c r="E132">
+        <v>12994</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B133" t="s">
+        <v>26</v>
+      </c>
+      <c r="C133">
+        <v>350.75661400000001</v>
+      </c>
+      <c r="D133">
+        <v>2704117777.5900002</v>
+      </c>
+      <c r="E133">
+        <v>38857</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B134" t="s">
+        <v>27</v>
+      </c>
+      <c r="C134">
+        <v>11.838826660000001</v>
+      </c>
+      <c r="D134">
+        <v>1133807674.1700001</v>
+      </c>
+      <c r="E134">
+        <v>16495</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B135" t="s">
+        <v>28</v>
+      </c>
+      <c r="C135">
+        <v>198.572138</v>
+      </c>
+      <c r="D135">
+        <v>284653202.20999998</v>
+      </c>
+      <c r="E135">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B136" t="s">
+        <v>29</v>
+      </c>
+      <c r="C136">
+        <v>170.7741771</v>
+      </c>
+      <c r="D136">
+        <v>1440431627.4200001</v>
+      </c>
+      <c r="E136">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B137" t="s">
+        <v>32</v>
+      </c>
+      <c r="C137">
+        <v>402.45125322000001</v>
+      </c>
+      <c r="D137">
+        <v>435072515.97000003</v>
+      </c>
+      <c r="E137">
+        <v>8934</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C138">
+        <v>221.85736299999999</v>
+      </c>
+      <c r="D138">
+        <v>798725071.94000006</v>
+      </c>
+      <c r="E138">
+        <v>7502</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B139" t="s">
+        <v>34</v>
+      </c>
+      <c r="C139">
+        <v>231.2962</v>
+      </c>
+      <c r="D139">
+        <v>113809087.08</v>
+      </c>
+      <c r="E139">
+        <v>4383</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B140" t="s">
+        <v>35</v>
+      </c>
+      <c r="C140">
+        <v>239.07441919999999</v>
+      </c>
+      <c r="D140">
+        <v>130310931.52</v>
+      </c>
+      <c r="E140">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B141" t="s">
+        <v>40</v>
+      </c>
+      <c r="C141">
+        <v>110.61604921999999</v>
+      </c>
+      <c r="D141">
+        <v>167859855</v>
+      </c>
+      <c r="E141">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B142" t="s">
+        <v>22</v>
+      </c>
+      <c r="C142">
+        <v>173.72934685999999</v>
+      </c>
+      <c r="D142">
+        <v>2755029376.04</v>
+      </c>
+      <c r="E142">
+        <v>76508</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B143" t="s">
+        <v>23</v>
+      </c>
+      <c r="C143">
+        <v>212.78308894</v>
+      </c>
+      <c r="D143">
+        <v>913729885.00999999</v>
+      </c>
+      <c r="E143">
+        <v>7226</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B144" t="s">
+        <v>24</v>
+      </c>
+      <c r="C144">
+        <v>134.35108005000001</v>
+      </c>
+      <c r="D144">
+        <v>294070137.10000002</v>
+      </c>
+      <c r="E144">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B145" t="s">
+        <v>25</v>
+      </c>
+      <c r="C145">
+        <v>165.161753</v>
+      </c>
+      <c r="D145">
+        <v>1273986251.6199999</v>
+      </c>
+      <c r="E145">
+        <v>13634</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B146" t="s">
+        <v>26</v>
+      </c>
+      <c r="C146">
+        <v>357.63221700000003</v>
+      </c>
+      <c r="D146">
+        <v>3155428348.3099999</v>
+      </c>
+      <c r="E146">
+        <v>44078</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B147" t="s">
+        <v>27</v>
+      </c>
+      <c r="C147">
+        <v>12.079791739999999</v>
+      </c>
+      <c r="D147">
+        <v>1239412685.3499999</v>
+      </c>
+      <c r="E147">
+        <v>16616</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B148" t="s">
+        <v>28</v>
+      </c>
+      <c r="C148">
+        <v>202.4793817</v>
+      </c>
+      <c r="D148">
+        <v>268981492.00999999</v>
+      </c>
+      <c r="E148">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B149" t="s">
+        <v>29</v>
+      </c>
+      <c r="C149">
+        <v>174.30474280000001</v>
+      </c>
+      <c r="D149">
+        <v>1415523875.99</v>
+      </c>
+      <c r="E149">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B150" t="s">
+        <v>32</v>
+      </c>
+      <c r="C150">
+        <v>410.65932354</v>
+      </c>
+      <c r="D150">
+        <v>461143127.45999998</v>
+      </c>
+      <c r="E150">
+        <v>8438</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B151" t="s">
+        <v>33</v>
+      </c>
+      <c r="C151">
+        <v>227.20659000000001</v>
+      </c>
+      <c r="D151">
+        <v>841428969.15999997</v>
+      </c>
+      <c r="E151">
+        <v>8102</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B152" t="s">
+        <v>34</v>
+      </c>
+      <c r="C152">
+        <v>235.39359999999999</v>
+      </c>
+      <c r="D152">
+        <v>104979969.55</v>
+      </c>
+      <c r="E152">
+        <v>4508</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B153" t="s">
+        <v>35</v>
+      </c>
+      <c r="C153">
+        <v>243.78792050000001</v>
+      </c>
+      <c r="D153">
+        <v>127233613.86</v>
+      </c>
+      <c r="E153">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B154" t="s">
+        <v>40</v>
+      </c>
+      <c r="C154">
+        <v>112.56613378999999</v>
+      </c>
+      <c r="D154">
+        <v>202337625.49000001</v>
+      </c>
+      <c r="E154">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B155" t="s">
+        <v>22</v>
+      </c>
+      <c r="C155">
+        <v>174.31846501999999</v>
+      </c>
+      <c r="D155">
+        <v>2714460737.9899998</v>
+      </c>
+      <c r="E155">
+        <v>76158</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B156" t="s">
+        <v>23</v>
+      </c>
+      <c r="C156">
+        <v>213.58180999000001</v>
+      </c>
+      <c r="D156">
+        <v>927883838.01999998</v>
+      </c>
+      <c r="E156">
+        <v>7251</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B157" t="s">
+        <v>24</v>
+      </c>
+      <c r="C157">
+        <v>134.82905649</v>
+      </c>
+      <c r="D157">
+        <v>309635566.69</v>
+      </c>
+      <c r="E157">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B158" t="s">
+        <v>25</v>
+      </c>
+      <c r="C158">
+        <v>165.67208099999999</v>
+      </c>
+      <c r="D158">
+        <v>1300155400.52</v>
+      </c>
+      <c r="E158">
+        <v>13863</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B159" t="s">
+        <v>26</v>
+      </c>
+      <c r="C159">
+        <v>358.82808499999999</v>
+      </c>
+      <c r="D159">
+        <v>3281456302.8499999</v>
+      </c>
+      <c r="E159">
+        <v>44950</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B160" t="s">
+        <v>27</v>
+      </c>
+      <c r="C160">
+        <v>12.122606530000001</v>
+      </c>
+      <c r="D160">
+        <v>1234798460.1099999</v>
+      </c>
+      <c r="E160">
+        <v>16736</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A161" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B161" t="s">
+        <v>28</v>
+      </c>
+      <c r="C161">
+        <v>203.14380349999999</v>
+      </c>
+      <c r="D161">
+        <v>194957198.62</v>
+      </c>
+      <c r="E161">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B162" t="s">
+        <v>29</v>
+      </c>
+      <c r="C162">
+        <v>174.92875620000001</v>
+      </c>
+      <c r="D162">
+        <v>1240583547.5899999</v>
+      </c>
+      <c r="E162">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B163" t="s">
+        <v>32</v>
+      </c>
+      <c r="C163">
+        <v>411.87582773999998</v>
+      </c>
+      <c r="D163">
+        <v>472879276.06</v>
+      </c>
+      <c r="E163">
+        <v>8522</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B164" t="s">
+        <v>33</v>
+      </c>
+      <c r="C164">
+        <v>228.37178800000001</v>
+      </c>
+      <c r="D164">
+        <v>859777580.77999997</v>
+      </c>
+      <c r="E164">
+        <v>8250</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B165" t="s">
+        <v>34</v>
+      </c>
+      <c r="C165">
+        <v>235.62559999999999</v>
+      </c>
+      <c r="D165">
+        <v>105017921.93000001</v>
+      </c>
+      <c r="E165">
+        <v>4553</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B166" t="s">
+        <v>35</v>
+      </c>
+      <c r="C166">
+        <v>244.45138560000001</v>
+      </c>
+      <c r="D166">
+        <v>129245461.34999999</v>
+      </c>
+      <c r="E166">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B167" t="s">
+        <v>40</v>
+      </c>
+      <c r="C167">
+        <v>113.10807698000001</v>
+      </c>
+      <c r="D167">
+        <v>152695903.91999999</v>
+      </c>
+      <c r="E167">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B168" t="s">
+        <v>22</v>
+      </c>
+      <c r="C168">
+        <v>174.92760867999999</v>
+      </c>
+      <c r="D168">
+        <v>2696336296.1199999</v>
+      </c>
+      <c r="E168">
+        <v>75749</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B169" t="s">
+        <v>23</v>
+      </c>
+      <c r="C169">
+        <v>214.56994126000001</v>
+      </c>
+      <c r="D169">
+        <v>926049973</v>
+      </c>
+      <c r="E169">
+        <v>7226</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B170" t="s">
+        <v>24</v>
+      </c>
+      <c r="C170">
+        <v>135.32540791</v>
+      </c>
+      <c r="D170">
+        <v>326176641.60000002</v>
+      </c>
+      <c r="E170">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B171" t="s">
+        <v>25</v>
+      </c>
+      <c r="C171">
+        <v>166.32631599999999</v>
+      </c>
+      <c r="D171">
+        <v>1330545100.6300001</v>
+      </c>
+      <c r="E171">
+        <v>13990</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B172" t="s">
+        <v>26</v>
+      </c>
+      <c r="C172">
+        <v>360.02621199999999</v>
+      </c>
+      <c r="D172">
+        <v>3386119097.6900001</v>
+      </c>
+      <c r="E172">
+        <v>45517</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B173" t="s">
+        <v>27</v>
+      </c>
+      <c r="C173">
+        <v>12.165339700000001</v>
+      </c>
+      <c r="D173">
+        <v>1247745597.73</v>
+      </c>
+      <c r="E173">
+        <v>16809</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B174" t="s">
+        <v>28</v>
+      </c>
+      <c r="C174">
+        <v>203.8672832</v>
+      </c>
+      <c r="D174">
+        <v>184350138.22</v>
+      </c>
+      <c r="E174">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B175" t="s">
+        <v>29</v>
+      </c>
+      <c r="C175">
+        <v>175.55553359999999</v>
+      </c>
+      <c r="D175">
+        <v>1372214285.01</v>
+      </c>
+      <c r="E175">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B176" t="s">
+        <v>32</v>
+      </c>
+      <c r="C176">
+        <v>413.52704188000001</v>
+      </c>
+      <c r="D176">
+        <v>476906604.38999999</v>
+      </c>
+      <c r="E176">
+        <v>8499</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B177" t="s">
+        <v>33</v>
+      </c>
+      <c r="C177">
+        <v>228.46783600000001</v>
+      </c>
+      <c r="D177">
+        <v>846675540.86000001</v>
+      </c>
+      <c r="E177">
+        <v>8334</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B178" t="s">
+        <v>34</v>
+      </c>
+      <c r="C178">
+        <v>235.76259999999999</v>
+      </c>
+      <c r="D178">
+        <v>99791086.439999998</v>
+      </c>
+      <c r="E178">
+        <v>4511</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B179" t="s">
+        <v>35</v>
+      </c>
+      <c r="C179">
+        <v>244.73786240000001</v>
+      </c>
+      <c r="D179">
+        <v>128349607.03</v>
+      </c>
+      <c r="E179">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B180" t="s">
+        <v>40</v>
+      </c>
+      <c r="C180">
+        <v>112.50574435</v>
+      </c>
+      <c r="D180">
+        <v>152164019.24000001</v>
+      </c>
+      <c r="E180">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A181" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B181" t="s">
+        <v>22</v>
+      </c>
+      <c r="C181">
+        <v>175.50838275999999</v>
+      </c>
+      <c r="D181">
+        <v>2705529159.8099999</v>
+      </c>
+      <c r="E181">
+        <v>75292</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A182" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B182" t="s">
+        <v>23</v>
+      </c>
+      <c r="C182">
+        <v>214.47442111000001</v>
+      </c>
+      <c r="D182">
+        <v>917635044.80999994</v>
+      </c>
+      <c r="E182">
+        <v>7147</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A183" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B183" t="s">
+        <v>24</v>
+      </c>
+      <c r="C183">
+        <v>135.79414928</v>
+      </c>
+      <c r="D183">
+        <v>359423998.38</v>
+      </c>
+      <c r="E183">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A184" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B184" t="s">
+        <v>25</v>
+      </c>
+      <c r="C184">
+        <v>166.12638113</v>
+      </c>
+      <c r="D184">
+        <v>1320047031.1900001</v>
+      </c>
+      <c r="E184">
+        <v>13880</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A185" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B185" t="s">
+        <v>26</v>
+      </c>
+      <c r="C185">
+        <v>361.10296736999999</v>
+      </c>
+      <c r="D185">
+        <v>3358169486.3899999</v>
+      </c>
+      <c r="E185">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A186" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B186" t="s">
+        <v>27</v>
+      </c>
+      <c r="C186">
+        <v>12.203462500000001</v>
+      </c>
+      <c r="D186">
+        <v>1253304551.1400001</v>
+      </c>
+      <c r="E186">
+        <v>16925</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A187" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B187" t="s">
+        <v>28</v>
+      </c>
+      <c r="C187">
+        <v>203.7424178</v>
+      </c>
+      <c r="D187">
+        <v>186504024.28999999</v>
+      </c>
+      <c r="E187">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A188" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B188" t="s">
+        <v>29</v>
+      </c>
+      <c r="C188">
+        <v>176.1565659</v>
+      </c>
+      <c r="D188">
+        <v>1543437489.8199999</v>
+      </c>
+      <c r="E188">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A189" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B189" t="s">
+        <v>32</v>
+      </c>
+      <c r="C189">
+        <v>409.07142088000001</v>
+      </c>
+      <c r="D189">
+        <v>445717202.87</v>
+      </c>
+      <c r="E189">
+        <v>8243</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A190" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B190" t="s">
+        <v>33</v>
+      </c>
+      <c r="C190">
+        <v>226.09731866999999</v>
+      </c>
+      <c r="D190">
+        <v>783883688.35000002</v>
+      </c>
+      <c r="E190">
+        <v>8119</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A191" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B191" t="s">
+        <v>34</v>
+      </c>
+      <c r="C191">
+        <v>233.64169999999999</v>
+      </c>
+      <c r="D191">
+        <v>91765003.560000002</v>
+      </c>
+      <c r="E191">
+        <v>4360</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A192" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B192" t="s">
+        <v>35</v>
+      </c>
+      <c r="C192">
+        <v>242.900756</v>
+      </c>
+      <c r="D192">
+        <v>120721586.34</v>
+      </c>
+      <c r="E192">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A193" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B193" t="s">
+        <v>40</v>
+      </c>
+      <c r="C193">
+        <v>110.04027514086383</v>
+      </c>
+      <c r="D193">
+        <v>148829472.12801832</v>
+      </c>
+      <c r="E193">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A194" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B194" t="s">
+        <v>22</v>
+      </c>
+      <c r="C194">
+        <v>175.68375476</v>
+      </c>
+      <c r="D194">
+        <v>2705748233.4099998</v>
+      </c>
+      <c r="E194">
+        <v>75164</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A195" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B195" t="s">
+        <v>23</v>
+      </c>
+      <c r="C195">
+        <v>214.81611819</v>
+      </c>
+      <c r="D195">
+        <v>897019568.54999995</v>
+      </c>
+      <c r="E195">
+        <v>7069</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A196" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B196" t="s">
+        <v>24</v>
+      </c>
+      <c r="C196">
+        <v>135.93525915000001</v>
+      </c>
+      <c r="D196">
+        <v>385465944.74000001</v>
+      </c>
+      <c r="E196">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A197" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B197" t="s">
+        <v>25</v>
+      </c>
+      <c r="C197">
+        <v>166.41805854</v>
+      </c>
+      <c r="D197">
+        <v>1317793069.1300001</v>
+      </c>
+      <c r="E197">
+        <v>13802</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A198" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B198" t="s">
+        <v>26</v>
+      </c>
+      <c r="C198">
+        <v>361.46004819000001</v>
+      </c>
+      <c r="D198">
+        <v>3451869354.6100001</v>
+      </c>
+      <c r="E198">
+        <v>45759</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A199" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B199" t="s">
+        <v>27</v>
+      </c>
+      <c r="C199">
+        <v>12.21523575</v>
+      </c>
+      <c r="D199">
+        <v>1249435239.9400001</v>
+      </c>
+      <c r="E199">
+        <v>16986</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A200" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B200" t="s">
+        <v>28</v>
+      </c>
+      <c r="C200">
+        <v>204.02861960000001</v>
+      </c>
+      <c r="D200">
+        <v>194753456.19999999</v>
+      </c>
+      <c r="E200">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A201" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B201" t="s">
+        <v>29</v>
+      </c>
+      <c r="C201">
+        <v>176.33114180000001</v>
+      </c>
+      <c r="D201">
+        <v>1666496529.3</v>
+      </c>
+      <c r="E201">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A202" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B202" t="s">
+        <v>32</v>
+      </c>
+      <c r="C202">
+        <v>410.30980470999998</v>
+      </c>
+      <c r="D202">
+        <v>435373898.41000003</v>
+      </c>
+      <c r="E202">
+        <v>8142</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A203" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B203" t="s">
+        <v>33</v>
+      </c>
+      <c r="C203">
+        <v>226.63490805999999</v>
+      </c>
+      <c r="D203">
+        <v>768176827.78999996</v>
+      </c>
+      <c r="E203">
+        <v>8043</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A204" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B204" t="s">
+        <v>34</v>
+      </c>
+      <c r="C204">
+        <v>234.13839999999999</v>
+      </c>
+      <c r="D204">
+        <v>87314060.650000006</v>
+      </c>
+      <c r="E204">
+        <v>4305</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A205" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B205" t="s">
+        <v>35</v>
+      </c>
+      <c r="C205">
+        <v>243.4637008</v>
+      </c>
+      <c r="D205">
+        <v>118502088.41</v>
+      </c>
+      <c r="E205">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A206" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B206" t="s">
+        <v>40</v>
+      </c>
+      <c r="C206">
+        <v>110.882600109728</v>
+      </c>
+      <c r="D206">
+        <v>149414303.64785901</v>
+      </c>
+      <c r="E206">
+        <v>547</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F03A5C34-5D1E-4F67-8251-B418B0F38380}">
   <dimension ref="B1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5534,7 +8122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A2D3046-C98B-4F65-9E3A-6D8A29B21B00}">
   <dimension ref="A1:Q339"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/FondosMutuos/BaseFFMM.xlsx
+++ b/FondosMutuos/BaseFFMM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\FondosMutuos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE771B8-2A24-44EF-8CFB-69D8E3D877FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DEEDAE-5E81-45C9-BF0A-7CF692168983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{837DD3E0-4F9E-4033-A113-A4241C8EE115}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="406">
   <si>
     <t>ID</t>
   </si>
@@ -1395,7 +1395,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1443,6 +1443,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1464,7 +1465,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="LENOVO" refreshedDate="46311.469485069443" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="205" xr:uid="{52DEB751-7A25-4BD3-836B-51C73697F048}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:E206" sheet="Data"/>
+    <worksheetSource ref="A1:E271" sheet="Data"/>
   </cacheSource>
   <cacheFields count="8">
     <cacheField name="Fecha" numFmtId="14">
@@ -4350,7 +4351,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E90F8A8D-E010-4622-BBF4-8117B763A2FF}">
-  <dimension ref="A1:E206"/>
+  <dimension ref="A1:E271"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -6743,1106 +6744,2211 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="B142" t="s">
         <v>22</v>
       </c>
       <c r="C142">
-        <v>173.72934685999999</v>
+        <v>171.02995018999999</v>
       </c>
       <c r="D142">
-        <v>2755029376.04</v>
+        <v>2769789323.1599998</v>
       </c>
       <c r="E142">
-        <v>76508</v>
+        <v>77713</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="B143" t="s">
         <v>23</v>
       </c>
       <c r="C143">
-        <v>212.78308894</v>
+        <v>209.35727355</v>
       </c>
       <c r="D143">
-        <v>913729885.00999999</v>
+        <v>948054761.87</v>
       </c>
       <c r="E143">
-        <v>7226</v>
+        <v>7228</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="B144" t="s">
         <v>24</v>
       </c>
       <c r="C144">
-        <v>134.35108005000001</v>
+        <v>132.14481548000001</v>
       </c>
       <c r="D144">
-        <v>294070137.10000002</v>
+        <v>250908393.58000001</v>
       </c>
       <c r="E144">
-        <v>559</v>
+        <v>518</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="B145" t="s">
         <v>25</v>
       </c>
       <c r="C145">
-        <v>165.161753</v>
+        <v>162.52818600000001</v>
       </c>
       <c r="D145">
-        <v>1273986251.6199999</v>
+        <v>1251311163.75</v>
       </c>
       <c r="E145">
-        <v>13634</v>
+        <v>13198</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="B146" t="s">
         <v>26</v>
       </c>
       <c r="C146">
-        <v>357.63221700000003</v>
+        <v>351.96363200000002</v>
       </c>
       <c r="D146">
-        <v>3155428348.3099999</v>
+        <v>2742090456.1100001</v>
       </c>
       <c r="E146">
-        <v>44078</v>
+        <v>39825</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="B147" t="s">
         <v>27</v>
       </c>
       <c r="C147">
-        <v>12.079791739999999</v>
+        <v>11.884595190000001</v>
       </c>
       <c r="D147">
-        <v>1239412685.3499999</v>
+        <v>1133474038.6800001</v>
       </c>
       <c r="E147">
-        <v>16616</v>
+        <v>16226</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="B148" t="s">
         <v>28</v>
       </c>
       <c r="C148">
-        <v>202.4793817</v>
+        <v>199.39653469999999</v>
       </c>
       <c r="D148">
-        <v>268981492.00999999</v>
+        <v>310788098.92000002</v>
       </c>
       <c r="E148">
-        <v>909</v>
+        <v>918</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="B149" t="s">
         <v>29</v>
       </c>
       <c r="C149">
-        <v>174.30474280000001</v>
+        <v>171.45064619999999</v>
       </c>
       <c r="D149">
-        <v>1415523875.99</v>
+        <v>1505159651.4200001</v>
       </c>
       <c r="E149">
-        <v>2017</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="B150" t="s">
         <v>32</v>
       </c>
       <c r="C150">
-        <v>410.65932354</v>
+        <v>404.55440390000001</v>
       </c>
       <c r="D150">
-        <v>461143127.45999998</v>
+        <v>464639503.13</v>
       </c>
       <c r="E150">
-        <v>8438</v>
+        <v>8989</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="B151" t="s">
         <v>33</v>
       </c>
       <c r="C151">
-        <v>227.20659000000001</v>
+        <v>223.126869</v>
       </c>
       <c r="D151">
-        <v>841428969.15999997</v>
+        <v>828997058.11000001</v>
       </c>
       <c r="E151">
-        <v>8102</v>
+        <v>7686</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="B152" t="s">
         <v>34</v>
       </c>
       <c r="C152">
-        <v>235.39359999999999</v>
+        <v>232.62530000000001</v>
       </c>
       <c r="D152">
-        <v>104979969.55</v>
+        <v>114791567.48</v>
       </c>
       <c r="E152">
-        <v>4508</v>
+        <v>4526</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="B153" t="s">
         <v>35</v>
       </c>
       <c r="C153">
-        <v>243.78792050000001</v>
+        <v>240.5238555</v>
       </c>
       <c r="D153">
-        <v>127233613.86</v>
+        <v>132005986.44</v>
       </c>
       <c r="E153">
-        <v>888</v>
+        <v>922</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="B154" t="s">
         <v>40</v>
       </c>
       <c r="C154">
-        <v>112.56613378999999</v>
-      </c>
-      <c r="D154">
-        <v>202337625.49000001</v>
+        <v>111.64530344000001</v>
+      </c>
+      <c r="D154" s="21">
+        <v>171096427.52000001</v>
       </c>
       <c r="E154">
-        <v>449</v>
+        <v>360</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
-        <v>46234</v>
+        <v>46081</v>
       </c>
       <c r="B155" t="s">
         <v>22</v>
       </c>
       <c r="C155">
-        <v>174.31846501999999</v>
+        <v>171.51920490000001</v>
       </c>
       <c r="D155">
-        <v>2714460737.9899998</v>
+        <v>2760102537.9200001</v>
       </c>
       <c r="E155">
-        <v>76158</v>
+        <v>77535</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
-        <v>46234</v>
+        <v>46081</v>
       </c>
       <c r="B156" t="s">
         <v>23</v>
       </c>
       <c r="C156">
-        <v>213.58180999000001</v>
+        <v>210.11623319</v>
       </c>
       <c r="D156">
-        <v>927883838.01999998</v>
+        <v>967078061.39999998</v>
       </c>
       <c r="E156">
-        <v>7251</v>
+        <v>7337</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
-        <v>46234</v>
+        <v>46081</v>
       </c>
       <c r="B157" t="s">
         <v>24</v>
       </c>
       <c r="C157">
-        <v>134.82905649</v>
+        <v>132.54790410999999</v>
       </c>
       <c r="D157">
-        <v>309635566.69</v>
+        <v>243198553.69999999</v>
       </c>
       <c r="E157">
-        <v>564</v>
+        <v>510</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
-        <v>46234</v>
+        <v>46081</v>
       </c>
       <c r="B158" t="s">
         <v>25</v>
       </c>
       <c r="C158">
-        <v>165.67208099999999</v>
+        <v>163.04280900000001</v>
       </c>
       <c r="D158">
-        <v>1300155400.52</v>
+        <v>1305521836.0699999</v>
       </c>
       <c r="E158">
-        <v>13863</v>
+        <v>13470</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
-        <v>46234</v>
+        <v>46081</v>
       </c>
       <c r="B159" t="s">
         <v>26</v>
       </c>
       <c r="C159">
-        <v>358.82808499999999</v>
+        <v>352.93574599999999</v>
       </c>
       <c r="D159">
-        <v>3281456302.8499999</v>
+        <v>2730394671.73</v>
       </c>
       <c r="E159">
-        <v>44950</v>
+        <v>40490</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
-        <v>46234</v>
+        <v>46081</v>
       </c>
       <c r="B160" t="s">
         <v>27</v>
       </c>
       <c r="C160">
-        <v>12.122606530000001</v>
+        <v>11.917306140000001</v>
       </c>
       <c r="D160">
-        <v>1234798460.1099999</v>
+        <v>1153635866.1700001</v>
       </c>
       <c r="E160">
-        <v>16736</v>
+        <v>16227</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
-        <v>46234</v>
+        <v>46081</v>
       </c>
       <c r="B161" t="s">
         <v>28</v>
       </c>
       <c r="C161">
-        <v>203.14380349999999</v>
+        <v>200.05883850000001</v>
       </c>
       <c r="D161">
-        <v>194957198.62</v>
+        <v>309551670.10000002</v>
       </c>
       <c r="E161">
-        <v>909</v>
+        <v>925</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
-        <v>46234</v>
+        <v>46081</v>
       </c>
       <c r="B162" t="s">
         <v>29</v>
       </c>
       <c r="C162">
-        <v>174.92875620000001</v>
+        <v>171.93200049999999</v>
       </c>
       <c r="D162">
-        <v>1240583547.5899999</v>
+        <v>1387673680.3599999</v>
       </c>
       <c r="E162">
-        <v>1987</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
-        <v>46234</v>
+        <v>46081</v>
       </c>
       <c r="B163" t="s">
         <v>32</v>
       </c>
       <c r="C163">
-        <v>411.87582773999998</v>
+        <v>406.08190055</v>
       </c>
       <c r="D163">
-        <v>472879276.06</v>
+        <v>496981766.69</v>
       </c>
       <c r="E163">
-        <v>8522</v>
+        <v>9131</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
-        <v>46234</v>
+        <v>46081</v>
       </c>
       <c r="B164" t="s">
         <v>33</v>
       </c>
       <c r="C164">
-        <v>228.37178800000001</v>
+        <v>224.07479599999999</v>
       </c>
       <c r="D164">
-        <v>859777580.77999997</v>
+        <v>876753033.20000005</v>
       </c>
       <c r="E164">
-        <v>8250</v>
+        <v>7994</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
-        <v>46234</v>
+        <v>46081</v>
       </c>
       <c r="B165" t="s">
         <v>34</v>
       </c>
       <c r="C165">
-        <v>235.62559999999999</v>
+        <v>233.3922</v>
       </c>
       <c r="D165">
-        <v>105017921.93000001</v>
+        <v>124712405.39</v>
       </c>
       <c r="E165">
-        <v>4553</v>
+        <v>4736</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
-        <v>46234</v>
+        <v>46081</v>
       </c>
       <c r="B166" t="s">
         <v>35</v>
       </c>
       <c r="C166">
-        <v>244.45138560000001</v>
+        <v>240.97338930000001</v>
       </c>
       <c r="D166">
-        <v>129245461.34999999</v>
+        <v>133580155.59999999</v>
       </c>
       <c r="E166">
-        <v>882</v>
+        <v>924</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
-        <v>46234</v>
+        <v>46081</v>
       </c>
       <c r="B167" t="s">
         <v>40</v>
       </c>
       <c r="C167">
-        <v>113.10807698000001</v>
+        <v>111.71105032</v>
       </c>
       <c r="D167">
-        <v>152695903.91999999</v>
+        <v>172593572.74000001</v>
       </c>
       <c r="E167">
-        <v>449</v>
+        <v>398</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="B168" t="s">
         <v>22</v>
       </c>
       <c r="C168">
-        <v>174.92760867999999</v>
+        <v>172.04416921999999</v>
       </c>
       <c r="D168">
-        <v>2696336296.1199999</v>
+        <v>2795406593.8000002</v>
       </c>
       <c r="E168">
-        <v>75749</v>
+        <v>77351</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="B169" t="s">
         <v>23</v>
       </c>
       <c r="C169">
-        <v>214.56994126000001</v>
+        <v>210.09646728000001</v>
       </c>
       <c r="D169">
-        <v>926049973</v>
+        <v>965670176.30999994</v>
       </c>
       <c r="E169">
-        <v>7226</v>
+        <v>7309</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="B170" t="s">
         <v>24</v>
       </c>
       <c r="C170">
-        <v>135.32540791</v>
+        <v>132.99207010000001</v>
       </c>
       <c r="D170">
-        <v>326176641.60000002</v>
+        <v>272938995.32999998</v>
       </c>
       <c r="E170">
-        <v>566</v>
+        <v>517</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="B171" t="s">
         <v>25</v>
       </c>
       <c r="C171">
-        <v>166.32631599999999</v>
+        <v>162.99623299999999</v>
       </c>
       <c r="D171">
-        <v>1330545100.6300001</v>
+        <v>1310044225.79</v>
       </c>
       <c r="E171">
-        <v>13990</v>
+        <v>13493</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="B172" t="s">
         <v>26</v>
       </c>
       <c r="C172">
-        <v>360.02621199999999</v>
+        <v>354.04114800000002</v>
       </c>
       <c r="D172">
-        <v>3386119097.6900001</v>
+        <v>2878841374.4099998</v>
       </c>
       <c r="E172">
-        <v>45517</v>
+        <v>41592</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="B173" t="s">
         <v>27</v>
       </c>
       <c r="C173">
-        <v>12.165339700000001</v>
+        <v>11.94849765</v>
       </c>
       <c r="D173">
-        <v>1247745597.73</v>
+        <v>1195433069.5899999</v>
       </c>
       <c r="E173">
-        <v>16809</v>
+        <v>16331</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="B174" t="s">
         <v>28</v>
       </c>
       <c r="C174">
-        <v>203.8672832</v>
+        <v>199.91493370000001</v>
       </c>
       <c r="D174">
-        <v>184350138.22</v>
+        <v>250387309.88</v>
       </c>
       <c r="E174">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="B175" t="s">
         <v>29</v>
       </c>
       <c r="C175">
-        <v>175.55553359999999</v>
+        <v>172.43487279999999</v>
       </c>
       <c r="D175">
-        <v>1372214285.01</v>
+        <v>1342700355.78</v>
       </c>
       <c r="E175">
-        <v>1957</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="B176" t="s">
         <v>32</v>
       </c>
       <c r="C176">
-        <v>413.52704188000001</v>
+        <v>401.44983323000002</v>
       </c>
       <c r="D176">
-        <v>476906604.38999999</v>
+        <v>481830541.19</v>
       </c>
       <c r="E176">
-        <v>8499</v>
+        <v>8721</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="B177" t="s">
         <v>33</v>
       </c>
       <c r="C177">
-        <v>228.46783600000001</v>
+        <v>221.98569599999999</v>
       </c>
       <c r="D177">
-        <v>846675540.86000001</v>
+        <v>827238094.24000001</v>
       </c>
       <c r="E177">
-        <v>8334</v>
+        <v>8005</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="B178" t="s">
         <v>34</v>
       </c>
       <c r="C178">
-        <v>235.76259999999999</v>
+        <v>230.80369999999999</v>
       </c>
       <c r="D178">
-        <v>99791086.439999998</v>
+        <v>111684808.62</v>
       </c>
       <c r="E178">
-        <v>4511</v>
+        <v>4579</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="B179" t="s">
         <v>35</v>
       </c>
       <c r="C179">
-        <v>244.73786240000001</v>
+        <v>238.5323176</v>
       </c>
       <c r="D179">
-        <v>128349607.03</v>
+        <v>128323465.92</v>
       </c>
       <c r="E179">
-        <v>859</v>
+        <v>913</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="B180" t="s">
         <v>40</v>
       </c>
       <c r="C180">
-        <v>112.50574435</v>
+        <v>107.91394041</v>
       </c>
       <c r="D180">
-        <v>152164019.24000001</v>
+        <v>191277459.38</v>
       </c>
       <c r="E180">
-        <v>518</v>
+        <v>338</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="B181" t="s">
         <v>22</v>
       </c>
       <c r="C181">
-        <v>175.50838275999999</v>
+        <v>172.59621182999999</v>
       </c>
       <c r="D181">
-        <v>2705529159.8099999</v>
+        <v>2759700883.4200001</v>
       </c>
       <c r="E181">
-        <v>75292</v>
+        <v>77141</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="B182" t="s">
         <v>23</v>
       </c>
       <c r="C182">
-        <v>214.47442111000001</v>
+        <v>211.12221948999999</v>
       </c>
       <c r="D182">
-        <v>917635044.80999994</v>
+        <v>902080220.38999999</v>
       </c>
       <c r="E182">
-        <v>7147</v>
+        <v>7289</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="B183" t="s">
         <v>24</v>
       </c>
       <c r="C183">
-        <v>135.79414928</v>
+        <v>133.42620184</v>
       </c>
       <c r="D183">
-        <v>359423998.38</v>
+        <v>288208407.72000003</v>
       </c>
       <c r="E183">
-        <v>597</v>
+        <v>534</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="B184" t="s">
         <v>25</v>
       </c>
       <c r="C184">
-        <v>166.12638113</v>
+        <v>163.721102</v>
       </c>
       <c r="D184">
-        <v>1320047031.1900001</v>
+        <v>1307610404.8299999</v>
       </c>
       <c r="E184">
-        <v>13880</v>
+        <v>13523</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="B185" t="s">
         <v>26</v>
       </c>
       <c r="C185">
-        <v>361.10296736999999</v>
+        <v>355.20415800000001</v>
       </c>
       <c r="D185">
-        <v>3358169486.3899999</v>
+        <v>3087724539.8400002</v>
       </c>
       <c r="E185">
-        <v>45627</v>
+        <v>42706</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="B186" t="s">
         <v>27</v>
       </c>
       <c r="C186">
-        <v>12.203462500000001</v>
+        <v>11.99146614</v>
       </c>
       <c r="D186">
-        <v>1253304551.1400001</v>
+        <v>1274040463.7</v>
       </c>
       <c r="E186">
-        <v>16925</v>
+        <v>16547</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="B187" t="s">
         <v>28</v>
       </c>
       <c r="C187">
-        <v>203.7424178</v>
+        <v>200.90346869999999</v>
       </c>
       <c r="D187">
-        <v>186504024.28999999</v>
+        <v>272687667.14999998</v>
       </c>
       <c r="E187">
-        <v>881</v>
+        <v>928</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="B188" t="s">
         <v>29</v>
       </c>
       <c r="C188">
-        <v>176.1565659</v>
+        <v>173.0471919</v>
       </c>
       <c r="D188">
-        <v>1543437489.8199999</v>
+        <v>1439807645.1400001</v>
       </c>
       <c r="E188">
-        <v>1953</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="B189" t="s">
         <v>32</v>
       </c>
       <c r="C189">
-        <v>409.07142088000001</v>
+        <v>406.12916368999998</v>
       </c>
       <c r="D189">
-        <v>445717202.87</v>
+        <v>471196456.31</v>
       </c>
       <c r="E189">
-        <v>8243</v>
+        <v>8591</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="B190" t="s">
         <v>33</v>
       </c>
       <c r="C190">
-        <v>226.09731866999999</v>
+        <v>223.68921</v>
       </c>
       <c r="D190">
-        <v>783883688.35000002</v>
+        <v>808650918.29999995</v>
       </c>
       <c r="E190">
-        <v>8119</v>
+        <v>7994</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="B191" t="s">
         <v>34</v>
       </c>
       <c r="C191">
-        <v>233.64169999999999</v>
+        <v>233.01339999999999</v>
       </c>
       <c r="D191">
-        <v>91765003.560000002</v>
+        <v>107904311.04000001</v>
       </c>
       <c r="E191">
-        <v>4360</v>
+        <v>4544</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="B192" t="s">
         <v>35</v>
       </c>
       <c r="C192">
-        <v>242.900756</v>
+        <v>240.5918016</v>
       </c>
       <c r="D192">
-        <v>120721586.34</v>
+        <v>127936675.83</v>
       </c>
       <c r="E192">
-        <v>838</v>
+        <v>910</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="B193" t="s">
         <v>40</v>
       </c>
       <c r="C193">
-        <v>110.04027514086383</v>
+        <v>109.30136435999999</v>
       </c>
       <c r="D193">
-        <v>148829472.12801832</v>
+        <v>194009921.74000001</v>
       </c>
       <c r="E193">
-        <v>547</v>
+        <v>446</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
-        <v>46304</v>
+        <v>46173</v>
       </c>
       <c r="B194" t="s">
         <v>22</v>
       </c>
       <c r="C194">
-        <v>175.68375476</v>
+        <v>173.16881229000001</v>
       </c>
       <c r="D194">
-        <v>2705748233.4099998</v>
+        <v>2772031059.21</v>
       </c>
       <c r="E194">
-        <v>75164</v>
+        <v>76924</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
-        <v>46304</v>
+        <v>46173</v>
       </c>
       <c r="B195" t="s">
         <v>23</v>
       </c>
       <c r="C195">
-        <v>214.81611819</v>
+        <v>211.85907018</v>
       </c>
       <c r="D195">
-        <v>897019568.54999995</v>
+        <v>893652789.94000006</v>
       </c>
       <c r="E195">
-        <v>7069</v>
+        <v>7233</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
-        <v>46304</v>
+        <v>46173</v>
       </c>
       <c r="B196" t="s">
         <v>24</v>
       </c>
       <c r="C196">
-        <v>135.93525915000001</v>
+        <v>133.89353187</v>
       </c>
       <c r="D196">
-        <v>385465944.74000001</v>
+        <v>280697176.42000002</v>
       </c>
       <c r="E196">
-        <v>610</v>
+        <v>546</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
-        <v>46304</v>
+        <v>46173</v>
       </c>
       <c r="B197" t="s">
         <v>25</v>
       </c>
       <c r="C197">
-        <v>166.41805854</v>
+        <v>164.404876</v>
       </c>
       <c r="D197">
-        <v>1317793069.1300001</v>
+        <v>1295591395.8900001</v>
       </c>
       <c r="E197">
-        <v>13802</v>
+        <v>13608</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
-        <v>46304</v>
+        <v>46173</v>
       </c>
       <c r="B198" t="s">
         <v>26</v>
       </c>
       <c r="C198">
-        <v>361.46004819000001</v>
+        <v>356.45455700000002</v>
       </c>
       <c r="D198">
-        <v>3451869354.6100001</v>
+        <v>3111790686.29</v>
       </c>
       <c r="E198">
-        <v>45759</v>
+        <v>43571</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
-        <v>46304</v>
+        <v>46173</v>
       </c>
       <c r="B199" t="s">
         <v>27</v>
       </c>
       <c r="C199">
-        <v>12.21523575</v>
+        <v>12.0347916</v>
       </c>
       <c r="D199">
-        <v>1249435239.9400001</v>
+        <v>1218790462.6600001</v>
       </c>
       <c r="E199">
-        <v>16986</v>
+        <v>16642</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
-        <v>46304</v>
+        <v>46173</v>
       </c>
       <c r="B200" t="s">
         <v>28</v>
       </c>
       <c r="C200">
-        <v>204.02861960000001</v>
+        <v>201.6821104</v>
       </c>
       <c r="D200">
-        <v>194753456.19999999</v>
+        <v>271193571.19999999</v>
       </c>
       <c r="E200">
-        <v>877</v>
+        <v>917</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
-        <v>46304</v>
+        <v>46173</v>
       </c>
       <c r="B201" t="s">
         <v>29</v>
       </c>
       <c r="C201">
-        <v>176.33114180000001</v>
+        <v>173.6554299</v>
       </c>
       <c r="D201">
-        <v>1666496529.3</v>
+        <v>1483540707.6099999</v>
       </c>
       <c r="E201">
-        <v>1979</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
-        <v>46304</v>
+        <v>46173</v>
       </c>
       <c r="B202" t="s">
         <v>32</v>
       </c>
       <c r="C202">
-        <v>410.30980470999998</v>
+        <v>407.73720405</v>
       </c>
       <c r="D202">
-        <v>435373898.41000003</v>
+        <v>460394151.76999998</v>
       </c>
       <c r="E202">
-        <v>8142</v>
+        <v>8504</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
-        <v>46304</v>
+        <v>46173</v>
       </c>
       <c r="B203" t="s">
         <v>33</v>
       </c>
       <c r="C203">
-        <v>226.63490805999999</v>
+        <v>225.18913699999999</v>
       </c>
       <c r="D203">
-        <v>768176827.78999996</v>
+        <v>821868199</v>
       </c>
       <c r="E203">
-        <v>8043</v>
+        <v>8009</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
-        <v>46304</v>
+        <v>46173</v>
       </c>
       <c r="B204" t="s">
         <v>34</v>
       </c>
       <c r="C204">
-        <v>234.13839999999999</v>
+        <v>233.82660000000001</v>
       </c>
       <c r="D204">
-        <v>87314060.650000006</v>
+        <v>106268092.8</v>
       </c>
       <c r="E204">
-        <v>4305</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
-        <v>46304</v>
+        <v>46173</v>
       </c>
       <c r="B205" t="s">
         <v>35</v>
       </c>
       <c r="C205">
-        <v>243.4637008</v>
+        <v>241.93932409999999</v>
       </c>
       <c r="D205">
-        <v>118502088.41</v>
+        <v>126604346.67</v>
       </c>
       <c r="E205">
-        <v>835</v>
+        <v>900</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
-        <v>46304</v>
+        <v>46173</v>
       </c>
       <c r="B206" t="s">
         <v>40</v>
       </c>
       <c r="C206">
+        <v>110.21059455</v>
+      </c>
+      <c r="D206">
+        <v>198103543.71000001</v>
+      </c>
+      <c r="E206">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A207" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B207" t="s">
+        <v>22</v>
+      </c>
+      <c r="C207">
+        <v>173.72934685999999</v>
+      </c>
+      <c r="D207">
+        <v>2755029376.04</v>
+      </c>
+      <c r="E207">
+        <v>76508</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A208" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B208" t="s">
+        <v>23</v>
+      </c>
+      <c r="C208">
+        <v>212.78308894</v>
+      </c>
+      <c r="D208">
+        <v>913729885.00999999</v>
+      </c>
+      <c r="E208">
+        <v>7226</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A209" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B209" t="s">
+        <v>24</v>
+      </c>
+      <c r="C209">
+        <v>134.35108005000001</v>
+      </c>
+      <c r="D209">
+        <v>294070137.10000002</v>
+      </c>
+      <c r="E209">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A210" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B210" t="s">
+        <v>25</v>
+      </c>
+      <c r="C210">
+        <v>165.161753</v>
+      </c>
+      <c r="D210">
+        <v>1273986251.6199999</v>
+      </c>
+      <c r="E210">
+        <v>13634</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A211" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B211" t="s">
+        <v>26</v>
+      </c>
+      <c r="C211">
+        <v>357.63221700000003</v>
+      </c>
+      <c r="D211">
+        <v>3155428348.3099999</v>
+      </c>
+      <c r="E211">
+        <v>44078</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A212" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B212" t="s">
+        <v>27</v>
+      </c>
+      <c r="C212">
+        <v>12.079791739999999</v>
+      </c>
+      <c r="D212">
+        <v>1239412685.3499999</v>
+      </c>
+      <c r="E212">
+        <v>16616</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A213" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B213" t="s">
+        <v>28</v>
+      </c>
+      <c r="C213">
+        <v>202.4793817</v>
+      </c>
+      <c r="D213">
+        <v>268981492.00999999</v>
+      </c>
+      <c r="E213">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A214" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B214" t="s">
+        <v>29</v>
+      </c>
+      <c r="C214">
+        <v>174.30474280000001</v>
+      </c>
+      <c r="D214">
+        <v>1415523875.99</v>
+      </c>
+      <c r="E214">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A215" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B215" t="s">
+        <v>32</v>
+      </c>
+      <c r="C215">
+        <v>410.65932354</v>
+      </c>
+      <c r="D215">
+        <v>461143127.45999998</v>
+      </c>
+      <c r="E215">
+        <v>8438</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A216" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B216" t="s">
+        <v>33</v>
+      </c>
+      <c r="C216">
+        <v>227.20659000000001</v>
+      </c>
+      <c r="D216">
+        <v>841428969.15999997</v>
+      </c>
+      <c r="E216">
+        <v>8102</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A217" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B217" t="s">
+        <v>34</v>
+      </c>
+      <c r="C217">
+        <v>235.39359999999999</v>
+      </c>
+      <c r="D217">
+        <v>104979969.55</v>
+      </c>
+      <c r="E217">
+        <v>4508</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A218" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B218" t="s">
+        <v>35</v>
+      </c>
+      <c r="C218">
+        <v>243.78792050000001</v>
+      </c>
+      <c r="D218">
+        <v>127233613.86</v>
+      </c>
+      <c r="E218">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A219" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B219" t="s">
+        <v>40</v>
+      </c>
+      <c r="C219">
+        <v>112.56613378999999</v>
+      </c>
+      <c r="D219">
+        <v>202337625.49000001</v>
+      </c>
+      <c r="E219">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A220" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B220" t="s">
+        <v>22</v>
+      </c>
+      <c r="C220">
+        <v>174.31846501999999</v>
+      </c>
+      <c r="D220">
+        <v>2714460737.9899998</v>
+      </c>
+      <c r="E220">
+        <v>76158</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A221" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B221" t="s">
+        <v>23</v>
+      </c>
+      <c r="C221">
+        <v>213.58180999000001</v>
+      </c>
+      <c r="D221">
+        <v>927883838.01999998</v>
+      </c>
+      <c r="E221">
+        <v>7251</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A222" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B222" t="s">
+        <v>24</v>
+      </c>
+      <c r="C222">
+        <v>134.82905649</v>
+      </c>
+      <c r="D222">
+        <v>309635566.69</v>
+      </c>
+      <c r="E222">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A223" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B223" t="s">
+        <v>25</v>
+      </c>
+      <c r="C223">
+        <v>165.67208099999999</v>
+      </c>
+      <c r="D223">
+        <v>1300155400.52</v>
+      </c>
+      <c r="E223">
+        <v>13863</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A224" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B224" t="s">
+        <v>26</v>
+      </c>
+      <c r="C224">
+        <v>358.82808499999999</v>
+      </c>
+      <c r="D224">
+        <v>3281456302.8499999</v>
+      </c>
+      <c r="E224">
+        <v>44950</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A225" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B225" t="s">
+        <v>27</v>
+      </c>
+      <c r="C225">
+        <v>12.122606530000001</v>
+      </c>
+      <c r="D225">
+        <v>1234798460.1099999</v>
+      </c>
+      <c r="E225">
+        <v>16736</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A226" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B226" t="s">
+        <v>28</v>
+      </c>
+      <c r="C226">
+        <v>203.14380349999999</v>
+      </c>
+      <c r="D226">
+        <v>194957198.62</v>
+      </c>
+      <c r="E226">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A227" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B227" t="s">
+        <v>29</v>
+      </c>
+      <c r="C227">
+        <v>174.92875620000001</v>
+      </c>
+      <c r="D227">
+        <v>1240583547.5899999</v>
+      </c>
+      <c r="E227">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A228" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B228" t="s">
+        <v>32</v>
+      </c>
+      <c r="C228">
+        <v>411.87582773999998</v>
+      </c>
+      <c r="D228">
+        <v>472879276.06</v>
+      </c>
+      <c r="E228">
+        <v>8522</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A229" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B229" t="s">
+        <v>33</v>
+      </c>
+      <c r="C229">
+        <v>228.37178800000001</v>
+      </c>
+      <c r="D229">
+        <v>859777580.77999997</v>
+      </c>
+      <c r="E229">
+        <v>8250</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A230" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B230" t="s">
+        <v>34</v>
+      </c>
+      <c r="C230">
+        <v>235.62559999999999</v>
+      </c>
+      <c r="D230">
+        <v>105017921.93000001</v>
+      </c>
+      <c r="E230">
+        <v>4553</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A231" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B231" t="s">
+        <v>35</v>
+      </c>
+      <c r="C231">
+        <v>244.45138560000001</v>
+      </c>
+      <c r="D231">
+        <v>129245461.34999999</v>
+      </c>
+      <c r="E231">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A232" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B232" t="s">
+        <v>40</v>
+      </c>
+      <c r="C232">
+        <v>113.10807698000001</v>
+      </c>
+      <c r="D232">
+        <v>152695903.91999999</v>
+      </c>
+      <c r="E232">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A233" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B233" t="s">
+        <v>22</v>
+      </c>
+      <c r="C233">
+        <v>174.92760867999999</v>
+      </c>
+      <c r="D233">
+        <v>2696336296.1199999</v>
+      </c>
+      <c r="E233">
+        <v>75749</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A234" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B234" t="s">
+        <v>23</v>
+      </c>
+      <c r="C234">
+        <v>214.56994126000001</v>
+      </c>
+      <c r="D234">
+        <v>926049973</v>
+      </c>
+      <c r="E234">
+        <v>7226</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A235" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B235" t="s">
+        <v>24</v>
+      </c>
+      <c r="C235">
+        <v>135.32540791</v>
+      </c>
+      <c r="D235">
+        <v>326176641.60000002</v>
+      </c>
+      <c r="E235">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A236" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B236" t="s">
+        <v>25</v>
+      </c>
+      <c r="C236">
+        <v>166.32631599999999</v>
+      </c>
+      <c r="D236">
+        <v>1330545100.6300001</v>
+      </c>
+      <c r="E236">
+        <v>13990</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A237" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B237" t="s">
+        <v>26</v>
+      </c>
+      <c r="C237">
+        <v>360.02621199999999</v>
+      </c>
+      <c r="D237">
+        <v>3386119097.6900001</v>
+      </c>
+      <c r="E237">
+        <v>45517</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A238" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B238" t="s">
+        <v>27</v>
+      </c>
+      <c r="C238">
+        <v>12.165339700000001</v>
+      </c>
+      <c r="D238">
+        <v>1247745597.73</v>
+      </c>
+      <c r="E238">
+        <v>16809</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A239" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B239" t="s">
+        <v>28</v>
+      </c>
+      <c r="C239">
+        <v>203.8672832</v>
+      </c>
+      <c r="D239">
+        <v>184350138.22</v>
+      </c>
+      <c r="E239">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A240" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B240" t="s">
+        <v>29</v>
+      </c>
+      <c r="C240">
+        <v>175.55553359999999</v>
+      </c>
+      <c r="D240">
+        <v>1372214285.01</v>
+      </c>
+      <c r="E240">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A241" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B241" t="s">
+        <v>32</v>
+      </c>
+      <c r="C241">
+        <v>413.52704188000001</v>
+      </c>
+      <c r="D241">
+        <v>476906604.38999999</v>
+      </c>
+      <c r="E241">
+        <v>8499</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A242" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B242" t="s">
+        <v>33</v>
+      </c>
+      <c r="C242">
+        <v>228.46783600000001</v>
+      </c>
+      <c r="D242">
+        <v>846675540.86000001</v>
+      </c>
+      <c r="E242">
+        <v>8334</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A243" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B243" t="s">
+        <v>34</v>
+      </c>
+      <c r="C243">
+        <v>235.76259999999999</v>
+      </c>
+      <c r="D243">
+        <v>99791086.439999998</v>
+      </c>
+      <c r="E243">
+        <v>4511</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A244" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B244" t="s">
+        <v>35</v>
+      </c>
+      <c r="C244">
+        <v>244.73786240000001</v>
+      </c>
+      <c r="D244">
+        <v>128349607.03</v>
+      </c>
+      <c r="E244">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A245" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B245" t="s">
+        <v>40</v>
+      </c>
+      <c r="C245">
+        <v>112.50574435</v>
+      </c>
+      <c r="D245">
+        <v>152164019.24000001</v>
+      </c>
+      <c r="E245">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A246" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B246" t="s">
+        <v>22</v>
+      </c>
+      <c r="C246">
+        <v>175.50838275999999</v>
+      </c>
+      <c r="D246">
+        <v>2705529159.8099999</v>
+      </c>
+      <c r="E246">
+        <v>75292</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A247" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B247" t="s">
+        <v>23</v>
+      </c>
+      <c r="C247">
+        <v>214.47442111000001</v>
+      </c>
+      <c r="D247">
+        <v>917635044.80999994</v>
+      </c>
+      <c r="E247">
+        <v>7147</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A248" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B248" t="s">
+        <v>24</v>
+      </c>
+      <c r="C248">
+        <v>135.79414928</v>
+      </c>
+      <c r="D248">
+        <v>359423998.38</v>
+      </c>
+      <c r="E248">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A249" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B249" t="s">
+        <v>25</v>
+      </c>
+      <c r="C249">
+        <v>166.12638113</v>
+      </c>
+      <c r="D249">
+        <v>1320047031.1900001</v>
+      </c>
+      <c r="E249">
+        <v>13880</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A250" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B250" t="s">
+        <v>26</v>
+      </c>
+      <c r="C250">
+        <v>361.10296736999999</v>
+      </c>
+      <c r="D250">
+        <v>3358169486.3899999</v>
+      </c>
+      <c r="E250">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A251" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B251" t="s">
+        <v>27</v>
+      </c>
+      <c r="C251">
+        <v>12.203462500000001</v>
+      </c>
+      <c r="D251">
+        <v>1253304551.1400001</v>
+      </c>
+      <c r="E251">
+        <v>16925</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A252" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B252" t="s">
+        <v>28</v>
+      </c>
+      <c r="C252">
+        <v>203.7424178</v>
+      </c>
+      <c r="D252">
+        <v>186504024.28999999</v>
+      </c>
+      <c r="E252">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A253" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B253" t="s">
+        <v>29</v>
+      </c>
+      <c r="C253">
+        <v>176.1565659</v>
+      </c>
+      <c r="D253">
+        <v>1543437489.8199999</v>
+      </c>
+      <c r="E253">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A254" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B254" t="s">
+        <v>32</v>
+      </c>
+      <c r="C254">
+        <v>409.07142088000001</v>
+      </c>
+      <c r="D254">
+        <v>445717202.87</v>
+      </c>
+      <c r="E254">
+        <v>8243</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A255" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B255" t="s">
+        <v>33</v>
+      </c>
+      <c r="C255">
+        <v>226.09731866999999</v>
+      </c>
+      <c r="D255">
+        <v>783883688.35000002</v>
+      </c>
+      <c r="E255">
+        <v>8119</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A256" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B256" t="s">
+        <v>34</v>
+      </c>
+      <c r="C256">
+        <v>233.64169999999999</v>
+      </c>
+      <c r="D256">
+        <v>91765003.560000002</v>
+      </c>
+      <c r="E256">
+        <v>4360</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A257" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B257" t="s">
+        <v>35</v>
+      </c>
+      <c r="C257">
+        <v>242.900756</v>
+      </c>
+      <c r="D257">
+        <v>120721586.34</v>
+      </c>
+      <c r="E257">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A258" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B258" t="s">
+        <v>40</v>
+      </c>
+      <c r="C258">
+        <v>110.04027514086383</v>
+      </c>
+      <c r="D258">
+        <v>148829472.12801832</v>
+      </c>
+      <c r="E258">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A259" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B259" t="s">
+        <v>22</v>
+      </c>
+      <c r="C259">
+        <v>175.68375476</v>
+      </c>
+      <c r="D259">
+        <v>2705748233.4099998</v>
+      </c>
+      <c r="E259">
+        <v>75164</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A260" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B260" t="s">
+        <v>23</v>
+      </c>
+      <c r="C260">
+        <v>214.81611819</v>
+      </c>
+      <c r="D260">
+        <v>897019568.54999995</v>
+      </c>
+      <c r="E260">
+        <v>7069</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A261" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B261" t="s">
+        <v>24</v>
+      </c>
+      <c r="C261">
+        <v>135.93525915000001</v>
+      </c>
+      <c r="D261">
+        <v>385465944.74000001</v>
+      </c>
+      <c r="E261">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A262" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B262" t="s">
+        <v>25</v>
+      </c>
+      <c r="C262">
+        <v>166.41805854</v>
+      </c>
+      <c r="D262">
+        <v>1317793069.1300001</v>
+      </c>
+      <c r="E262">
+        <v>13802</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A263" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B263" t="s">
+        <v>26</v>
+      </c>
+      <c r="C263">
+        <v>361.46004819000001</v>
+      </c>
+      <c r="D263">
+        <v>3451869354.6100001</v>
+      </c>
+      <c r="E263">
+        <v>45759</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A264" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B264" t="s">
+        <v>27</v>
+      </c>
+      <c r="C264">
+        <v>12.21523575</v>
+      </c>
+      <c r="D264">
+        <v>1249435239.9400001</v>
+      </c>
+      <c r="E264">
+        <v>16986</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A265" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B265" t="s">
+        <v>28</v>
+      </c>
+      <c r="C265">
+        <v>204.02861960000001</v>
+      </c>
+      <c r="D265">
+        <v>194753456.19999999</v>
+      </c>
+      <c r="E265">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A266" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B266" t="s">
+        <v>29</v>
+      </c>
+      <c r="C266">
+        <v>176.33114180000001</v>
+      </c>
+      <c r="D266">
+        <v>1666496529.3</v>
+      </c>
+      <c r="E266">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A267" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B267" t="s">
+        <v>32</v>
+      </c>
+      <c r="C267">
+        <v>410.30980470999998</v>
+      </c>
+      <c r="D267">
+        <v>435373898.41000003</v>
+      </c>
+      <c r="E267">
+        <v>8142</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A268" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B268" t="s">
+        <v>33</v>
+      </c>
+      <c r="C268">
+        <v>226.63490805999999</v>
+      </c>
+      <c r="D268">
+        <v>768176827.78999996</v>
+      </c>
+      <c r="E268">
+        <v>8043</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A269" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B269" t="s">
+        <v>34</v>
+      </c>
+      <c r="C269">
+        <v>234.13839999999999</v>
+      </c>
+      <c r="D269">
+        <v>87314060.650000006</v>
+      </c>
+      <c r="E269">
+        <v>4305</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A270" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B270" t="s">
+        <v>35</v>
+      </c>
+      <c r="C270">
+        <v>243.4637008</v>
+      </c>
+      <c r="D270">
+        <v>118502088.41</v>
+      </c>
+      <c r="E270">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A271" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B271" t="s">
+        <v>40</v>
+      </c>
+      <c r="C271">
         <v>110.882600109728</v>
       </c>
-      <c r="D206">
+      <c r="D271">
         <v>149414303.64785901</v>
       </c>
-      <c r="E206">
+      <c r="E271">
         <v>547</v>
       </c>
     </row>

--- a/FondosMutuos/BaseFFMM.xlsx
+++ b/FondosMutuos/BaseFFMM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\FondosMutuos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DEEDAE-5E81-45C9-BF0A-7CF692168983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6B33CD-AB63-4547-B2A8-A6FF34CE905E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{837DD3E0-4F9E-4033-A113-A4241C8EE115}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="407">
   <si>
     <t>ID</t>
   </si>
@@ -1264,6 +1264,9 @@
   </si>
   <si>
     <t>MCP</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -4351,7 +4354,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E90F8A8D-E010-4622-BBF4-8117B763A2FF}">
-  <dimension ref="A1:E271"/>
+  <dimension ref="A1:R271"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -7609,7 +7612,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>46142</v>
       </c>
@@ -7626,7 +7629,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>46173</v>
       </c>
@@ -7643,7 +7646,7 @@
         <v>76924</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>46173</v>
       </c>
@@ -7660,7 +7663,7 @@
         <v>7233</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>46173</v>
       </c>
@@ -7677,7 +7680,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>46173</v>
       </c>
@@ -7694,7 +7697,7 @@
         <v>13608</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>46173</v>
       </c>
@@ -7711,7 +7714,7 @@
         <v>43571</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>46173</v>
       </c>
@@ -7727,8 +7730,38 @@
       <c r="E199">
         <v>16642</v>
       </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I199">
+        <v>1.98</v>
+      </c>
+      <c r="J199">
+        <v>3.17</v>
+      </c>
+      <c r="K199">
+        <v>3.47</v>
+      </c>
+      <c r="L199">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="M199">
+        <v>3.64</v>
+      </c>
+      <c r="N199">
+        <v>3.76</v>
+      </c>
+      <c r="O199">
+        <v>3.95</v>
+      </c>
+      <c r="P199">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="Q199">
+        <v>4.53</v>
+      </c>
+      <c r="R199">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>46173</v>
       </c>
@@ -7744,8 +7777,38 @@
       <c r="E200">
         <v>917</v>
       </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I200" t="s">
+        <v>406</v>
+      </c>
+      <c r="J200">
+        <v>0.82</v>
+      </c>
+      <c r="K200">
+        <v>2.11</v>
+      </c>
+      <c r="L200">
+        <v>3.5</v>
+      </c>
+      <c r="M200">
+        <v>4.33</v>
+      </c>
+      <c r="N200">
+        <v>3.12</v>
+      </c>
+      <c r="O200">
+        <v>4.43</v>
+      </c>
+      <c r="P200">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>406</v>
+      </c>
+      <c r="R200">
+        <v>4.92</v>
+      </c>
+    </row>
+    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>46173</v>
       </c>
@@ -7761,8 +7824,38 @@
       <c r="E201">
         <v>2017</v>
       </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I201">
+        <v>2.97</v>
+      </c>
+      <c r="J201">
+        <v>3.14</v>
+      </c>
+      <c r="K201">
+        <v>3.16</v>
+      </c>
+      <c r="L201">
+        <v>2.84</v>
+      </c>
+      <c r="M201">
+        <v>2.71</v>
+      </c>
+      <c r="N201">
+        <v>3.92</v>
+      </c>
+      <c r="O201">
+        <v>4.08</v>
+      </c>
+      <c r="P201">
+        <v>4.34</v>
+      </c>
+      <c r="Q201">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="R201">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>46173</v>
       </c>
@@ -7778,8 +7871,38 @@
       <c r="E202">
         <v>8504</v>
       </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I202" t="s">
+        <v>406</v>
+      </c>
+      <c r="J202">
+        <v>3.73</v>
+      </c>
+      <c r="K202">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="L202">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="M202">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N202">
+        <v>2.96</v>
+      </c>
+      <c r="O202">
+        <v>3.47</v>
+      </c>
+      <c r="P202" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q202">
+        <v>3.52</v>
+      </c>
+      <c r="R202">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>46173</v>
       </c>
@@ -7795,8 +7918,38 @@
       <c r="E203">
         <v>8009</v>
       </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I203">
+        <v>2.94</v>
+      </c>
+      <c r="J203">
+        <v>3.93</v>
+      </c>
+      <c r="K203">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="L203">
+        <v>4.37</v>
+      </c>
+      <c r="M203">
+        <v>3.96</v>
+      </c>
+      <c r="N203">
+        <v>4.07</v>
+      </c>
+      <c r="O203">
+        <v>4.2</v>
+      </c>
+      <c r="P203">
+        <v>4.22</v>
+      </c>
+      <c r="Q203">
+        <v>3.88</v>
+      </c>
+      <c r="R203">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>46173</v>
       </c>
@@ -7812,8 +7965,38 @@
       <c r="E204">
         <v>4494</v>
       </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I204">
+        <v>1.58</v>
+      </c>
+      <c r="J204">
+        <v>2.99</v>
+      </c>
+      <c r="K204">
+        <v>3.1</v>
+      </c>
+      <c r="L204">
+        <v>3.44</v>
+      </c>
+      <c r="M204">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="N204">
+        <v>3.73</v>
+      </c>
+      <c r="O204">
+        <v>3.9</v>
+      </c>
+      <c r="P204">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Q204">
+        <v>3</v>
+      </c>
+      <c r="R204">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>46173</v>
       </c>
@@ -7829,8 +8012,38 @@
       <c r="E205">
         <v>900</v>
       </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I205" t="s">
+        <v>406</v>
+      </c>
+      <c r="J205" t="s">
+        <v>406</v>
+      </c>
+      <c r="K205" t="s">
+        <v>406</v>
+      </c>
+      <c r="L205" t="s">
+        <v>406</v>
+      </c>
+      <c r="M205" t="s">
+        <v>406</v>
+      </c>
+      <c r="N205">
+        <v>2.92</v>
+      </c>
+      <c r="O205">
+        <v>2.83</v>
+      </c>
+      <c r="P205" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>406</v>
+      </c>
+      <c r="R205" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>46173</v>
       </c>
@@ -7846,8 +8059,38 @@
       <c r="E206">
         <v>449</v>
       </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I206" t="s">
+        <v>406</v>
+      </c>
+      <c r="J206">
+        <v>3.88</v>
+      </c>
+      <c r="K206">
+        <v>3.79</v>
+      </c>
+      <c r="L206">
+        <v>3.88</v>
+      </c>
+      <c r="M206">
+        <v>4.34</v>
+      </c>
+      <c r="N206">
+        <v>3.85</v>
+      </c>
+      <c r="O206">
+        <v>4.13</v>
+      </c>
+      <c r="P206">
+        <v>4.34</v>
+      </c>
+      <c r="Q206">
+        <v>4.5</v>
+      </c>
+      <c r="R206">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>46203</v>
       </c>
@@ -7863,8 +8106,38 @@
       <c r="E207">
         <v>76508</v>
       </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I207">
+        <v>2.12</v>
+      </c>
+      <c r="J207">
+        <v>2.68</v>
+      </c>
+      <c r="K207">
+        <v>2.67</v>
+      </c>
+      <c r="L207">
+        <v>3.15</v>
+      </c>
+      <c r="M207">
+        <v>4.87</v>
+      </c>
+      <c r="N207">
+        <v>4.05</v>
+      </c>
+      <c r="O207">
+        <v>4.24</v>
+      </c>
+      <c r="P207">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="Q207">
+        <v>4.12</v>
+      </c>
+      <c r="R207">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>46203</v>
       </c>
@@ -7880,8 +8153,38 @@
       <c r="E208">
         <v>7226</v>
       </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I208" t="s">
+        <v>406</v>
+      </c>
+      <c r="J208">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="K208">
+        <v>5.07</v>
+      </c>
+      <c r="L208">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="M208">
+        <v>4.18</v>
+      </c>
+      <c r="N208">
+        <v>3.99</v>
+      </c>
+      <c r="O208">
+        <v>4.13</v>
+      </c>
+      <c r="P208">
+        <v>4.43</v>
+      </c>
+      <c r="Q208">
+        <v>4.47</v>
+      </c>
+      <c r="R208">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>46203</v>
       </c>
@@ -7897,8 +8200,38 @@
       <c r="E209">
         <v>559</v>
       </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I209">
+        <v>0.1</v>
+      </c>
+      <c r="J209">
+        <v>0.87</v>
+      </c>
+      <c r="K209">
+        <v>3.04</v>
+      </c>
+      <c r="L209">
+        <v>3.43</v>
+      </c>
+      <c r="M209">
+        <v>3.61</v>
+      </c>
+      <c r="N209">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="O209">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="P209" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q209">
+        <v>4.33</v>
+      </c>
+      <c r="R209">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>46203</v>
       </c>
@@ -7914,8 +8247,38 @@
       <c r="E210">
         <v>13634</v>
       </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I210">
+        <v>4.07</v>
+      </c>
+      <c r="J210">
+        <v>4.47</v>
+      </c>
+      <c r="K210">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="L210">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M210" t="s">
+        <v>406</v>
+      </c>
+      <c r="N210">
+        <v>3.87</v>
+      </c>
+      <c r="O210">
+        <v>4.22</v>
+      </c>
+      <c r="P210">
+        <v>4.33</v>
+      </c>
+      <c r="Q210">
+        <v>4.62</v>
+      </c>
+      <c r="R210">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>46203</v>
       </c>
@@ -7931,8 +8294,38 @@
       <c r="E211">
         <v>44078</v>
       </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I211" t="s">
+        <v>406</v>
+      </c>
+      <c r="J211" t="s">
+        <v>406</v>
+      </c>
+      <c r="K211">
+        <v>3.08</v>
+      </c>
+      <c r="L211">
+        <v>4</v>
+      </c>
+      <c r="M211">
+        <v>3.98</v>
+      </c>
+      <c r="N211" t="s">
+        <v>406</v>
+      </c>
+      <c r="O211" t="s">
+        <v>406</v>
+      </c>
+      <c r="P211" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>406</v>
+      </c>
+      <c r="R211" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>46203</v>
       </c>
@@ -7948,8 +8341,38 @@
       <c r="E212">
         <v>16616</v>
       </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I212">
+        <v>2.31</v>
+      </c>
+      <c r="J212">
+        <v>2.85</v>
+      </c>
+      <c r="K212">
+        <v>2.16</v>
+      </c>
+      <c r="L212">
+        <v>3.97</v>
+      </c>
+      <c r="M212">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N212" t="s">
+        <v>406</v>
+      </c>
+      <c r="O212" t="s">
+        <v>406</v>
+      </c>
+      <c r="P212" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>406</v>
+      </c>
+      <c r="R212">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>46203</v>
       </c>
@@ -7965,8 +8388,38 @@
       <c r="E213">
         <v>909</v>
       </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I213" t="s">
+        <v>406</v>
+      </c>
+      <c r="J213" t="s">
+        <v>406</v>
+      </c>
+      <c r="K213" t="s">
+        <v>406</v>
+      </c>
+      <c r="L213" t="s">
+        <v>406</v>
+      </c>
+      <c r="M213" t="s">
+        <v>406</v>
+      </c>
+      <c r="N213">
+        <v>4.03</v>
+      </c>
+      <c r="O213">
+        <v>4.34</v>
+      </c>
+      <c r="P213">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>406</v>
+      </c>
+      <c r="R213" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>46203</v>
       </c>
@@ -7982,8 +8435,38 @@
       <c r="E214">
         <v>2017</v>
       </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I214" t="s">
+        <v>406</v>
+      </c>
+      <c r="J214" t="s">
+        <v>406</v>
+      </c>
+      <c r="K214" t="s">
+        <v>406</v>
+      </c>
+      <c r="L214" t="s">
+        <v>406</v>
+      </c>
+      <c r="M214" t="s">
+        <v>406</v>
+      </c>
+      <c r="N214">
+        <v>3.6</v>
+      </c>
+      <c r="O214">
+        <v>4.2</v>
+      </c>
+      <c r="P214">
+        <v>4.3</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>406</v>
+      </c>
+      <c r="R214" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>46203</v>
       </c>
@@ -7999,8 +8482,38 @@
       <c r="E215">
         <v>8438</v>
       </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I215" t="s">
+        <v>406</v>
+      </c>
+      <c r="J215" t="s">
+        <v>406</v>
+      </c>
+      <c r="K215" t="s">
+        <v>406</v>
+      </c>
+      <c r="L215" t="s">
+        <v>406</v>
+      </c>
+      <c r="M215" t="s">
+        <v>406</v>
+      </c>
+      <c r="N215">
+        <v>3.94</v>
+      </c>
+      <c r="O215">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="P215">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="Q215">
+        <v>4.78</v>
+      </c>
+      <c r="R215">
+        <v>4.92</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>46203</v>
       </c>
@@ -8016,8 +8529,38 @@
       <c r="E216">
         <v>8102</v>
       </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I216">
+        <v>0.5</v>
+      </c>
+      <c r="J216">
+        <v>0.68</v>
+      </c>
+      <c r="K216">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="L216">
+        <v>4.67</v>
+      </c>
+      <c r="M216">
+        <v>4.66</v>
+      </c>
+      <c r="N216">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="O216">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="P216">
+        <v>0.5</v>
+      </c>
+      <c r="Q216">
+        <v>3.99</v>
+      </c>
+      <c r="R216">
+        <v>4.6100000000000003</v>
+      </c>
+    </row>
+    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>46203</v>
       </c>
@@ -8033,8 +8576,38 @@
       <c r="E217">
         <v>4508</v>
       </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I217">
+        <v>0.8</v>
+      </c>
+      <c r="J217">
+        <v>3.45</v>
+      </c>
+      <c r="K217">
+        <v>3.65</v>
+      </c>
+      <c r="L217">
+        <v>3.74</v>
+      </c>
+      <c r="M217">
+        <v>3.26</v>
+      </c>
+      <c r="N217">
+        <v>4.3</v>
+      </c>
+      <c r="O217">
+        <v>4.43</v>
+      </c>
+      <c r="P217">
+        <v>4.46</v>
+      </c>
+      <c r="Q217">
+        <v>4.63</v>
+      </c>
+      <c r="R217">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>46203</v>
       </c>
@@ -8050,8 +8623,38 @@
       <c r="E218">
         <v>888</v>
       </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I218" t="s">
+        <v>406</v>
+      </c>
+      <c r="J218">
+        <v>4.5</v>
+      </c>
+      <c r="K218">
+        <v>4.76</v>
+      </c>
+      <c r="L218">
+        <v>5.07</v>
+      </c>
+      <c r="M218">
+        <v>5.58</v>
+      </c>
+      <c r="N218" t="s">
+        <v>406</v>
+      </c>
+      <c r="O218" t="s">
+        <v>406</v>
+      </c>
+      <c r="P218" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>406</v>
+      </c>
+      <c r="R218">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>46203</v>
       </c>
@@ -8067,8 +8670,38 @@
       <c r="E219">
         <v>449</v>
       </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I219">
+        <v>3.45</v>
+      </c>
+      <c r="J219">
+        <v>3.53</v>
+      </c>
+      <c r="K219">
+        <v>3.32</v>
+      </c>
+      <c r="L219">
+        <v>3.63</v>
+      </c>
+      <c r="M219">
+        <v>3.92</v>
+      </c>
+      <c r="N219">
+        <v>3.88</v>
+      </c>
+      <c r="O219">
+        <v>4.12</v>
+      </c>
+      <c r="P219">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="Q219">
+        <v>4.18</v>
+      </c>
+      <c r="R219">
+        <v>4.5199999999999996</v>
+      </c>
+    </row>
+    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>46234</v>
       </c>
@@ -8085,7 +8718,7 @@
         <v>76158</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>46234</v>
       </c>
@@ -8102,7 +8735,7 @@
         <v>7251</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>46234</v>
       </c>
@@ -8119,7 +8752,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>46234</v>
       </c>
@@ -8136,7 +8769,7 @@
         <v>13863</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>46234</v>
       </c>
